--- a/dados.xlsx
+++ b/dados.xlsx
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 382 item(s) at 2026-09-29</t>
+          <t>Displaying 383 item(s) at 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -243,17 +243,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1629476</t>
+          <t>1656641</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1629476</t>
+          <t>1656641</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2345208</t>
+          <t>2373305</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1630623</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1630623</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2345252</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1589792</t>
+          <t>1656622</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1589792</t>
+          <t>1656622</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2238681</t>
+          <t>2373315</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1498747</t>
+          <t>1629750</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1498747</t>
+          <t>1629750</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2246541</t>
+          <t>2345525</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1498563</t>
+          <t>1629628</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1498563</t>
+          <t>1629628</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2246545</t>
+          <t>2345042</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1510800</t>
+          <t>1656642</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1510800</t>
+          <t>1656642</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2253143</t>
+          <t>2373307</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,22 +525,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1664875</t>
+          <t>1633586</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1664875</t>
+          <t>1633586</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>A_583262</t>
+          <t>2335890</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t/>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1510807</t>
+          <t>1656619</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1510807</t>
+          <t>1656619</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2256009</t>
+          <t>2373311</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1629628</t>
+          <t>1587583</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1629628</t>
+          <t>1587583</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2345042</t>
+          <t>2288720</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1656617</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1656617</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2373308</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,22 +713,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1664874</t>
+          <t>1629610</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1664874</t>
+          <t>1629610</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A_583261</t>
+          <t>2345074</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0930</t>
+          <t/>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1630139</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1630139</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2345317</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0919</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1630132</t>
+          <t>1601246</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1630132</t>
+          <t>1601246</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2345575</t>
+          <t>2299701</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0919</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1630119</t>
+          <t>1587554</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1630119</t>
+          <t>1587554</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2345431</t>
+          <t>2288724</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1629568</t>
+          <t>1605350</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1629568</t>
+          <t>1605350</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2345132</t>
+          <t>2335933</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1511923</t>
+          <t>1593502</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1511923</t>
+          <t>1593502</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2249278</t>
+          <t>2304248</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1630623</t>
+          <t>1630119</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1630623</t>
+          <t>1630119</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2345252</t>
+          <t>2345431</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1629710</t>
+          <t>1567445</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1629710</t>
+          <t>1567445</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2345221</t>
+          <t>2238575</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1656622</t>
+          <t>1629444</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1656622</t>
+          <t>1629444</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2373315</t>
+          <t>2345021</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1511908</t>
+          <t>1568609</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1511908</t>
+          <t>1568609</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2248683</t>
+          <t>2246573</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1567445</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1567445</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2238575</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0918</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1511883</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1511883</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2248643</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1656617</t>
+          <t>1511908</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1656617</t>
+          <t>1511908</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2373308</t>
+          <t>2248683</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1656641</t>
+          <t>1630090</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1656641</t>
+          <t>1630090</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2373305</t>
+          <t>2345355</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1630170</t>
+          <t>1511449</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1630170</t>
+          <t>1511449</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2345238</t>
+          <t>2243573</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1510980</t>
+          <t>1511000</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1510980</t>
+          <t>1511000</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2256016</t>
+          <t>2253151</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1605350</t>
+          <t>1511928</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1605350</t>
+          <t>1511928</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2335933</t>
+          <t>2249259</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1571487</t>
+          <t>1511923</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1571487</t>
+          <t>1511923</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2303916</t>
+          <t>2249278</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1511007</t>
+          <t>1511883</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1511007</t>
+          <t>1511883</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2253122</t>
+          <t>2248643</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1633586</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1633586</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2335890</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1656619</t>
+          <t>1629924</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1656619</t>
+          <t>1629924</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2373311</t>
+          <t>2345403</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1630090</t>
+          <t>1510945</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1630090</t>
+          <t>1510945</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2345355</t>
+          <t>2254643</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1547804</t>
+          <t>1510984</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1547804</t>
+          <t>1510984</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2298363</t>
+          <t>2254717</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1511928</t>
+          <t>1630170</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1511928</t>
+          <t>1630170</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2249259</t>
+          <t>2345238</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1510937</t>
+          <t>1511889</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1510937</t>
+          <t>1511889</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2256017</t>
+          <t>2248655</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1569770</t>
+          <t>1511900</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1569770</t>
+          <t>1511900</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2230146</t>
+          <t>2248672</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1510990</t>
+          <t>1569486</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1510990</t>
+          <t>1569486</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2256011</t>
+          <t>1832892</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1629571</t>
+          <t>1629858</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1629571</t>
+          <t>1629858</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2345161</t>
+          <t>2345365</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1629750</t>
+          <t>1510941</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1629750</t>
+          <t>1510941</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2345525</t>
+          <t>2256013</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1656642</t>
+          <t>1510828</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1656642</t>
+          <t>1510828</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2373307</t>
+          <t>2255838</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2123,17 +2123,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1511900</t>
+          <t>1630139</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1511900</t>
+          <t>1630139</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2248672</t>
+          <t>2345317</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1629913</t>
+          <t>1511007</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1629913</t>
+          <t>1511007</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2345485</t>
+          <t>2253122</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1511882</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1511882</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2248638</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1587554</t>
+          <t>1547804</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1587554</t>
+          <t>1547804</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2288724</t>
+          <t>2298363</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1510924</t>
+          <t>1629582</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1510924</t>
+          <t>1629582</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2255835</t>
+          <t>2345085</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1510924</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1510924</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2255835</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1511889</t>
+          <t>1510815</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1511889</t>
+          <t>1510815</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2248655</t>
+          <t>2253174</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1629723</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1629723</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2345032</t>
+          <t>2345192</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2499,17 +2499,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1656629</t>
+          <t>1510990</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1656629</t>
+          <t>1510990</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2373313</t>
+          <t>2256011</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2546,17 +2546,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1511449</t>
+          <t>1510980</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1511449</t>
+          <t>1510980</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2243573</t>
+          <t>2256016</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1629699</t>
+          <t>1510934</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1629699</t>
+          <t>1510934</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2345544</t>
+          <t>2255727</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1510920</t>
+          <t>1510994</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1510920</t>
+          <t>1510994</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2254612</t>
+          <t>2254674</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0917</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1571226</t>
+          <t>1510977</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1571226</t>
+          <t>1510977</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2303494</t>
+          <t>2254622</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2734,17 +2734,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1510918</t>
+          <t>1630562</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1510918</t>
+          <t>1630562</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2256020</t>
+          <t>2345292</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2781,17 +2781,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1629582</t>
+          <t>1593508</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1629582</t>
+          <t>1593508</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2345085</t>
+          <t>2303304</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2828,17 +2828,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1510976</t>
+          <t>1510840</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1510976</t>
+          <t>1510840</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2255726</t>
+          <t>2254661</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2875,17 +2875,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1511882</t>
+          <t>1510800</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1511882</t>
+          <t>1510800</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2248638</t>
+          <t>2253143</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2922,17 +2922,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1630562</t>
+          <t>1629699</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1630562</t>
+          <t>1629699</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2345292</t>
+          <t>2345544</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1511000</t>
+          <t>1656629</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1511000</t>
+          <t>1656629</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2253151</t>
+          <t>2373313</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3016,17 +3016,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1629610</t>
+          <t>1510976</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1629610</t>
+          <t>1510976</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2345074</t>
+          <t>2255726</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1510906</t>
+          <t>1510910</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1510906</t>
+          <t>1510910</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2255729</t>
+          <t>2255840</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3110,17 +3110,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1629444</t>
+          <t>1510937</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1629444</t>
+          <t>1510937</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2345021</t>
+          <t>2256017</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3157,17 +3157,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1510820</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1510820</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2253171</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1510994</t>
+          <t>1589792</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1510994</t>
+          <t>1589792</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2254674</t>
+          <t>2238681</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1510941</t>
+          <t>1630012</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1510941</t>
+          <t>1630012</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2256013</t>
+          <t>2345497</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1510977</t>
+          <t>1510834</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1510977</t>
+          <t>1510834</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2254622</t>
+          <t>2255836</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3345,17 +3345,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1629924</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1629924</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2345403</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3392,17 +3392,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1510934</t>
+          <t>1629618</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1510934</t>
+          <t>1629618</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2255727</t>
+          <t>2344989</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1601246</t>
+          <t>1630132</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1601246</t>
+          <t>1630132</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2299701</t>
+          <t>2345575</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3486,17 +3486,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1593508</t>
+          <t>1510920</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1593508</t>
+          <t>1510920</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2303304</t>
+          <t>2254612</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3533,17 +3533,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>1510848</t>
+          <t>1510817</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1510848</t>
+          <t>1510817</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2254709</t>
+          <t>2256022</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3580,17 +3580,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>1510984</t>
+          <t>1510906</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1510984</t>
+          <t>1510906</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2254717</t>
+          <t>2255729</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3627,17 +3627,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1629723</t>
+          <t>1571487</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>1629723</t>
+          <t>1571487</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2345192</t>
+          <t>2303916</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3674,17 +3674,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1510910</t>
+          <t>1510820</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1510910</t>
+          <t>1510820</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2255840</t>
+          <t>2253171</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3721,17 +3721,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1629913</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1629913</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2345485</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3768,17 +3768,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1593502</t>
+          <t>1510848</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1593502</t>
+          <t>1510848</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2304248</t>
+          <t>2254709</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1510945</t>
+          <t>1498747</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1510945</t>
+          <t>1498747</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2254643</t>
+          <t>2246541</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3862,17 +3862,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1510828</t>
+          <t>1629661</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1510828</t>
+          <t>1629661</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2255838</t>
+          <t>2345625</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3909,17 +3909,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1629710</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1629710</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2345221</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3956,17 +3956,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1629661</t>
+          <t>1510807</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1629661</t>
+          <t>1510807</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2345625</t>
+          <t>2256009</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4003,17 +4003,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1510834</t>
+          <t>1508077</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>1510834</t>
+          <t>1508077</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2255836</t>
+          <t>2193983</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4050,17 +4050,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1510918</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1510918</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2256020</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0916</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4097,17 +4097,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1510815</t>
+          <t>1499444</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1510815</t>
+          <t>1499444</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2253174</t>
+          <t>2246529</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1510817</t>
+          <t>1510798</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>1510817</t>
+          <t>1510798</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2256022</t>
+          <t>2255839</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4191,17 +4191,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>1587583</t>
+          <t>1629571</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>1587583</t>
+          <t>1629571</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2288720</t>
+          <t>2345161</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>1569486</t>
+          <t>1571226</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>1569486</t>
+          <t>1571226</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>1832892</t>
+          <t>2303494</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4285,17 +4285,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1510840</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>1510840</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2254661</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4332,17 +4332,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>1499444</t>
+          <t>1500517</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1499444</t>
+          <t>1500517</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2246529</t>
+          <t>2246497</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4379,17 +4379,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>1629618</t>
+          <t>1629568</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>1629618</t>
+          <t>1629568</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2344989</t>
+          <t>2345132</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4426,17 +4426,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>1498710</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>1498710</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2246543</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -4473,17 +4473,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>1630012</t>
+          <t>1629588</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1630012</t>
+          <t>1629588</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2345497</t>
+          <t>2345032</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4520,17 +4520,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>1500517</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>1500517</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2246497</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4567,17 +4567,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1498563</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1498563</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2246545</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -4614,17 +4614,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>1510798</t>
+          <t>1498710</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1510798</t>
+          <t>1498710</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2255839</t>
+          <t>2246543</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>1508077</t>
+          <t>1569770</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>1508077</t>
+          <t>1569770</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2193983</t>
+          <t>2230146</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4708,17 +4708,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1629476</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1629476</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2345208</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>1629858</t>
+          <t>1481061</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>1629858</t>
+          <t>1481061</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>2345365</t>
+          <t>2245184</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -4802,37 +4802,37 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>1568609</t>
+          <t>1665364</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>1568609</t>
+          <t>1665364</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>2246573</t>
+          <t>36306891</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1031</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Sep-29 1031</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>1481061</t>
+          <t>1665341</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>1481061</t>
+          <t>1665341</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>2245184</t>
+          <t>A_583393</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0915</t>
+          <t>26-Sep-29 1030</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Sep-29 1030</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 383 item(s) at 2026-09-29</t>
+          <t>Displaying 380 item(s) at 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -243,37 +243,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1656641</t>
+          <t>1665668</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1656641</t>
+          <t>1665668</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2373305</t>
+          <t>E_421073</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-in</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1104</t>
+          <t>26-Sep-29 1112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Sep-29 1112</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -290,37 +290,37 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1630623</t>
+          <t>1665667</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1630623</t>
+          <t>1665667</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2345252</t>
+          <t>PE_421073</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1104</t>
+          <t>26-Sep-29 1112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Sep-29 1112</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1656622</t>
+          <t>1656641</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1656622</t>
+          <t>1656641</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2373315</t>
+          <t>2373305</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1629750</t>
+          <t>1630623</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1629750</t>
+          <t>1630623</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2345525</t>
+          <t>2345252</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1629628</t>
+          <t>1656622</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1629628</t>
+          <t>1656622</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2345042</t>
+          <t>2373315</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1103</t>
+          <t>26-Sep-29 1104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1656642</t>
+          <t>1629750</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1656642</t>
+          <t>1629750</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2373307</t>
+          <t>2345525</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1103</t>
+          <t>26-Sep-29 1104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1633586</t>
+          <t>1629628</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1633586</t>
+          <t>1629628</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2335890</t>
+          <t>2345042</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1656619</t>
+          <t>1656642</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1656619</t>
+          <t>1656642</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2373311</t>
+          <t>2373307</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1587583</t>
+          <t>1633586</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1587583</t>
+          <t>1633586</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2288720</t>
+          <t>2335890</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1656617</t>
+          <t>1656619</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1656617</t>
+          <t>1656619</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2373308</t>
+          <t>2373311</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1629610</t>
+          <t>1587583</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1629610</t>
+          <t>1587583</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2345074</t>
+          <t>2288720</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1656617</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1656617</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2373308</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1601246</t>
+          <t>1629610</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1601246</t>
+          <t>1629610</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2299701</t>
+          <t>2345074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1587554</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1587554</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2288724</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1605350</t>
+          <t>1601246</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1605350</t>
+          <t>1601246</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2335933</t>
+          <t>2299701</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1102</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1593502</t>
+          <t>1587554</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1593502</t>
+          <t>1587554</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2304248</t>
+          <t>2288724</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1102</t>
+          <t>26-Sep-29 1103</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1630119</t>
+          <t>1605350</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1630119</t>
+          <t>1605350</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2345431</t>
+          <t>2335933</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1567445</t>
+          <t>1593502</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1567445</t>
+          <t>1593502</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2238575</t>
+          <t>2304248</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1629444</t>
+          <t>1630119</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1629444</t>
+          <t>1630119</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2345021</t>
+          <t>2345431</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1568609</t>
+          <t>1567445</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1568609</t>
+          <t>1567445</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2246573</t>
+          <t>2238575</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1629444</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1629444</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2345021</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1568609</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1568609</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2246573</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1511908</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1511908</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2248683</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1630090</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1630090</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2345355</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1511449</t>
+          <t>1511908</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1511449</t>
+          <t>1511908</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2243573</t>
+          <t>2248683</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1511000</t>
+          <t>1630090</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1511000</t>
+          <t>1630090</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2253151</t>
+          <t>2345355</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1511928</t>
+          <t>1511449</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1511928</t>
+          <t>1511449</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2249259</t>
+          <t>2243573</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1511923</t>
+          <t>1511000</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1511923</t>
+          <t>1511000</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2249278</t>
+          <t>2253151</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1511883</t>
+          <t>1511928</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1511883</t>
+          <t>1511928</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2248643</t>
+          <t>2249259</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1511923</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1511923</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2249278</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1629924</t>
+          <t>1511883</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1629924</t>
+          <t>1511883</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2345403</t>
+          <t>2248643</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1510945</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1510945</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2254643</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1510984</t>
+          <t>1629924</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1510984</t>
+          <t>1629924</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2254717</t>
+          <t>2345403</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1630170</t>
+          <t>1510945</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1630170</t>
+          <t>1510945</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2345238</t>
+          <t>2254643</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1511889</t>
+          <t>1510984</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1511889</t>
+          <t>1510984</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2248655</t>
+          <t>2254717</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1511900</t>
+          <t>1630170</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1511900</t>
+          <t>1630170</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2248672</t>
+          <t>2345238</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1569486</t>
+          <t>1511889</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1569486</t>
+          <t>1511889</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>1832892</t>
+          <t>2248655</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1629858</t>
+          <t>1511900</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1629858</t>
+          <t>1511900</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2345365</t>
+          <t>2248672</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1510941</t>
+          <t>1569486</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1510941</t>
+          <t>1569486</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2256013</t>
+          <t>1832892</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1510828</t>
+          <t>1629858</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1510828</t>
+          <t>1629858</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2255838</t>
+          <t>2345365</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2123,17 +2123,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1630139</t>
+          <t>1510941</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1630139</t>
+          <t>1510941</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2345317</t>
+          <t>2256013</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1511007</t>
+          <t>1510828</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1511007</t>
+          <t>1510828</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2253122</t>
+          <t>2255838</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1511882</t>
+          <t>1630139</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1511882</t>
+          <t>1630139</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2248638</t>
+          <t>2345317</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1101</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1547804</t>
+          <t>1511007</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1547804</t>
+          <t>1511007</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2298363</t>
+          <t>2253122</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1101</t>
+          <t>26-Sep-29 1102</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1629582</t>
+          <t>1511882</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1629582</t>
+          <t>1511882</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2345085</t>
+          <t>2248638</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1510924</t>
+          <t>1547804</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1510924</t>
+          <t>1547804</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2255835</t>
+          <t>2298363</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1510815</t>
+          <t>1629582</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1510815</t>
+          <t>1629582</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2253174</t>
+          <t>2345085</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1629723</t>
+          <t>1510924</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1629723</t>
+          <t>1510924</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2345192</t>
+          <t>2255835</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2499,17 +2499,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1510990</t>
+          <t>1510815</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1510990</t>
+          <t>1510815</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2256011</t>
+          <t>2253174</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2546,17 +2546,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1510980</t>
+          <t>1629723</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1510980</t>
+          <t>1629723</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>2256016</t>
+          <t>2345192</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1510934</t>
+          <t>1510990</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1510934</t>
+          <t>1510990</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2255727</t>
+          <t>2256011</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1510994</t>
+          <t>1510980</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1510994</t>
+          <t>1510980</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2254674</t>
+          <t>2256016</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1510977</t>
+          <t>1510934</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1510977</t>
+          <t>1510934</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2254622</t>
+          <t>2255727</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2734,17 +2734,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1630562</t>
+          <t>1510994</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1630562</t>
+          <t>1510994</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2345292</t>
+          <t>2254674</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2781,17 +2781,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1593508</t>
+          <t>1510977</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1593508</t>
+          <t>1510977</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2303304</t>
+          <t>2254622</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2828,17 +2828,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1510840</t>
+          <t>1630562</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1510840</t>
+          <t>1630562</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2254661</t>
+          <t>2345292</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2875,17 +2875,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1510800</t>
+          <t>1593508</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1510800</t>
+          <t>1593508</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2253143</t>
+          <t>2303304</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2922,17 +2922,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1629699</t>
+          <t>1510840</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1629699</t>
+          <t>1510840</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2345544</t>
+          <t>2254661</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1656629</t>
+          <t>1510800</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1656629</t>
+          <t>1510800</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2373313</t>
+          <t>2253143</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3016,17 +3016,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1510976</t>
+          <t>1629699</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1510976</t>
+          <t>1629699</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2255726</t>
+          <t>2345544</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1510910</t>
+          <t>1656629</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1510910</t>
+          <t>1656629</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2255840</t>
+          <t>2373313</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3110,17 +3110,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1510937</t>
+          <t>1510976</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1510937</t>
+          <t>1510976</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2256017</t>
+          <t>2255726</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3157,17 +3157,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1510910</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1510910</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2255840</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1589792</t>
+          <t>1510937</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1589792</t>
+          <t>1510937</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2238681</t>
+          <t>2256017</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1630012</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1630012</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2345497</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1510834</t>
+          <t>1589792</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1510834</t>
+          <t>1589792</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2255836</t>
+          <t>2238681</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3345,17 +3345,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1630012</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1630012</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2345497</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3392,17 +3392,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1629618</t>
+          <t>1510834</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1629618</t>
+          <t>1510834</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2344989</t>
+          <t>2255836</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1630132</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1630132</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2345575</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3486,17 +3486,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1510920</t>
+          <t>1629618</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1510920</t>
+          <t>1629618</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2254612</t>
+          <t>2344989</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3533,17 +3533,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>1510817</t>
+          <t>1630132</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1510817</t>
+          <t>1630132</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2256022</t>
+          <t>2345575</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3580,17 +3580,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>1510906</t>
+          <t>1510920</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1510906</t>
+          <t>1510920</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2255729</t>
+          <t>2254612</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3627,17 +3627,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1571487</t>
+          <t>1510817</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>1571487</t>
+          <t>1510817</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2303916</t>
+          <t>2256022</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3674,17 +3674,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1510820</t>
+          <t>1510906</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1510820</t>
+          <t>1510906</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2253171</t>
+          <t>2255729</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3721,17 +3721,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1629913</t>
+          <t>1571487</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1629913</t>
+          <t>1571487</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2345485</t>
+          <t>2303916</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3768,17 +3768,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1510848</t>
+          <t>1510820</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1510848</t>
+          <t>1510820</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2254709</t>
+          <t>2253171</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1498747</t>
+          <t>1629913</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1498747</t>
+          <t>1629913</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2246541</t>
+          <t>2345485</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3862,17 +3862,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1629661</t>
+          <t>1510848</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1629661</t>
+          <t>1510848</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2345625</t>
+          <t>2254709</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3909,17 +3909,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1629710</t>
+          <t>1498747</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1629710</t>
+          <t>1498747</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2345221</t>
+          <t>2246541</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1100</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3956,17 +3956,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1510807</t>
+          <t>1629661</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1510807</t>
+          <t>1629661</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2256009</t>
+          <t>2345625</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1100</t>
+          <t>26-Sep-29 1101</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4003,17 +4003,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1508077</t>
+          <t>1629710</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>1508077</t>
+          <t>1629710</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2193983</t>
+          <t>2345221</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4050,17 +4050,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>1510918</t>
+          <t>1510807</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1510918</t>
+          <t>1510807</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2256020</t>
+          <t>2256009</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4097,17 +4097,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1499444</t>
+          <t>1508077</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1499444</t>
+          <t>1508077</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2246529</t>
+          <t>2193983</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1510798</t>
+          <t>1510918</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>1510798</t>
+          <t>1510918</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2255839</t>
+          <t>2256020</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4191,17 +4191,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>1629571</t>
+          <t>1499444</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>1629571</t>
+          <t>1499444</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2345161</t>
+          <t>2246529</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>1571226</t>
+          <t>1510798</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>1571226</t>
+          <t>1510798</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>2303494</t>
+          <t>2255839</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4285,17 +4285,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1629571</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1629571</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2345161</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4332,17 +4332,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>1500517</t>
+          <t>1571226</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1500517</t>
+          <t>1571226</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2246497</t>
+          <t>2303494</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4379,17 +4379,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>1629568</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>1629568</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2345132</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4426,17 +4426,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1500517</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1500517</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2246497</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4473,17 +4473,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1629568</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1629568</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2345032</t>
+          <t>2345132</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4520,17 +4520,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4567,17 +4567,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>1498563</t>
+          <t>1629588</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>1498563</t>
+          <t>1629588</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>2246545</t>
+          <t>2345032</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4614,17 +4614,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>1498710</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1498710</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2246543</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>1569770</t>
+          <t>1498563</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>1569770</t>
+          <t>1498563</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2230146</t>
+          <t>2246545</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4708,17 +4708,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>1629476</t>
+          <t>1498710</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>1629476</t>
+          <t>1498710</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2345208</t>
+          <t>2246543</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>1481061</t>
+          <t>1569770</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>1481061</t>
+          <t>1569770</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>2245184</t>
+          <t>2230146</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4802,37 +4802,37 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>1665364</t>
+          <t>1629476</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>1665364</t>
+          <t>1629476</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>36306891</t>
+          <t>2345208</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1031</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1031</t>
+          <t/>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>1665341</t>
+          <t>1481061</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>1665341</t>
+          <t>1481061</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>A_583393</t>
+          <t>2245184</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1030</t>
+          <t>26-Sep-29 1100</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 1030</t>
+          <t/>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>1664772</t>
+          <t>1665341</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>1664772</t>
+          <t>1665341</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>2316463</t>
+          <t>A_583393</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0904</t>
+          <t>26-Sep-29 1030</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Sep-29 1030</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -4943,17 +4943,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>1664556</t>
+          <t>1664772</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>1664556</t>
+          <t>1664772</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>2373556</t>
+          <t>2316463</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0748</t>
+          <t>26-Sep-29 0904</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4990,17 +4990,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>1664447</t>
+          <t>1664556</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>1664447</t>
+          <t>1664556</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>2373565</t>
+          <t>2373556</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0648</t>
+          <t>26-Sep-29 0748</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5037,17 +5037,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>1664341</t>
+          <t>1664447</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>1664341</t>
+          <t>1664447</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>2373451</t>
+          <t>2373565</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0633</t>
+          <t>26-Sep-29 0648</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5084,17 +5084,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>1664254</t>
+          <t>1664341</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>1664254</t>
+          <t>1664341</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>2378882</t>
+          <t>2373451</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0433</t>
+          <t>26-Sep-29 0633</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -5131,37 +5131,37 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>1664127</t>
+          <t>1664254</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>1664127</t>
+          <t>1664254</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>36293848</t>
+          <t>2378882</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0308</t>
+          <t>26-Sep-29 0433</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0308</t>
+          <t/>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -5272,42 +5272,42 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>1663689</t>
+          <t>1663614</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>1663689</t>
+          <t>1663614</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>PE_420837</t>
+          <t>A_582120</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0111</t>
+          <t>26-Sep-28 2335</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-29 0111</t>
+          <t/>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Sep-28 2335</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5319,22 +5319,22 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1475805</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1475805</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>A_582120</t>
+          <t>2246552</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2335</t>
+          <t>26-Sep-28 2334</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2335</t>
+          <t/>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>1475805</t>
+          <t>1475510</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>1475805</t>
+          <t>1475510</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>2246552</t>
+          <t>2246524</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2334</t>
+          <t>26-Sep-28 2333</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>1475510</t>
+          <t>1475324</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>1475510</t>
+          <t>1475324</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>2246524</t>
+          <t>2246525</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5460,17 +5460,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>1475324</t>
+          <t>1475791</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>1475324</t>
+          <t>1475791</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>2246525</t>
+          <t>2246530</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5507,17 +5507,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>1475791</t>
+          <t>1475775</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>1475791</t>
+          <t>1475775</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>2246530</t>
+          <t>2246532</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5554,17 +5554,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>1475775</t>
+          <t>1475040</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>1475775</t>
+          <t>1475040</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>2246532</t>
+          <t>2246513</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5601,17 +5601,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>1475040</t>
+          <t>1475664</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>1475040</t>
+          <t>1475664</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>2246513</t>
+          <t>2246534</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5648,17 +5648,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>1475664</t>
+          <t>1475253</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>1475664</t>
+          <t>1475253</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>2246534</t>
+          <t>2246547</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5695,17 +5695,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>1475253</t>
+          <t>1474959</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>1475253</t>
+          <t>1474959</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>2246547</t>
+          <t>2246502</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5742,17 +5742,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>1474959</t>
+          <t>1475556</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>1474959</t>
+          <t>1475556</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>2246502</t>
+          <t>2246537</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -5789,17 +5789,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>1475556</t>
+          <t>1475886</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>1475556</t>
+          <t>1475886</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>2246537</t>
+          <t>2246482</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2333</t>
+          <t>26-Sep-28 2332</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5836,17 +5836,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>1475886</t>
+          <t>1469664</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>1475886</t>
+          <t>1469664</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>2246482</t>
+          <t>2238693</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5883,17 +5883,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>1469664</t>
+          <t>1469693</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>1469664</t>
+          <t>1469693</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>2238693</t>
+          <t>2238604</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5930,17 +5930,17 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>1469693</t>
+          <t>1475284</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>1469693</t>
+          <t>1475284</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>2238604</t>
+          <t>2246539</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5977,17 +5977,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>1475284</t>
+          <t>1474897</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>1475284</t>
+          <t>1474897</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>2246539</t>
+          <t>2246506</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>1474897</t>
+          <t>1474579</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>1474897</t>
+          <t>1474579</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>2246506</t>
+          <t>2246480</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -6071,17 +6071,17 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>1474579</t>
+          <t>1469662</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>1474579</t>
+          <t>1469662</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>2246480</t>
+          <t>2238619</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>1469662</t>
+          <t>1475003</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>1469662</t>
+          <t>1475003</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>2238619</t>
+          <t>2243551</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -6165,17 +6165,17 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>1475003</t>
+          <t>1469588</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>1475003</t>
+          <t>1469588</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>2243551</t>
+          <t>2238617</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -6212,17 +6212,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>1469588</t>
+          <t>1474967</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>1469588</t>
+          <t>1474967</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>2238617</t>
+          <t>2246501</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -6259,17 +6259,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>1474967</t>
+          <t>1469531</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>1474967</t>
+          <t>1469531</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>2246501</t>
+          <t>2238622</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -6306,17 +6306,17 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>1469531</t>
+          <t>1475209</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>1469531</t>
+          <t>1475209</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>2238622</t>
+          <t>2246553</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6353,17 +6353,17 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>1475209</t>
+          <t>1474270</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>1475209</t>
+          <t>1474270</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>2246553</t>
+          <t>2246510</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -6400,17 +6400,17 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>1474270</t>
+          <t>1469656</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>1474270</t>
+          <t>1469656</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>2246510</t>
+          <t>2238602</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6447,17 +6447,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>1469656</t>
+          <t>1469753</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>1469656</t>
+          <t>1469753</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>2238602</t>
+          <t>2238683</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6494,17 +6494,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>1469753</t>
+          <t>1474935</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>1469753</t>
+          <t>1474935</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>2238683</t>
+          <t>2246504</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6541,17 +6541,17 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>1474935</t>
+          <t>1469570</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>1474935</t>
+          <t>1469570</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>2246504</t>
+          <t>2238626</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6588,17 +6588,17 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>1469570</t>
+          <t>1469756</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>1469570</t>
+          <t>1469756</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>2238626</t>
+          <t>2238609</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6635,17 +6635,17 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>1469756</t>
+          <t>1474510</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>1469756</t>
+          <t>1474510</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>2238609</t>
+          <t>2246479</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6682,17 +6682,17 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>1474510</t>
+          <t>1469468</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>1474510</t>
+          <t>1469468</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>2246479</t>
+          <t>2238620</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -6729,17 +6729,17 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>1469468</t>
+          <t>1473806</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>1469468</t>
+          <t>1473806</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>2238620</t>
+          <t>2246485</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6776,17 +6776,17 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>1473806</t>
+          <t>1473505</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>1473806</t>
+          <t>1473505</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>2246485</t>
+          <t>2246523</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6823,17 +6823,17 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>1473505</t>
+          <t>1469550</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>1473505</t>
+          <t>1469550</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>2246523</t>
+          <t>2238636</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6870,17 +6870,17 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>1469550</t>
+          <t>1474690</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>1469550</t>
+          <t>1474690</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>2238636</t>
+          <t>2246484</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6917,17 +6917,17 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>1474690</t>
+          <t>1469742</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>1474690</t>
+          <t>1469742</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>2246484</t>
+          <t>2238697</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6964,17 +6964,17 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>1469742</t>
+          <t>1469524</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>1469742</t>
+          <t>1469524</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>2238697</t>
+          <t>2238666</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -7011,17 +7011,17 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>1469524</t>
+          <t>1474151</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>1469524</t>
+          <t>1474151</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>2238666</t>
+          <t>2246486</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -7058,17 +7058,17 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>1474151</t>
+          <t>1468667</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>1474151</t>
+          <t>1468667</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>2246486</t>
+          <t>2239218</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -7105,17 +7105,17 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>1468667</t>
+          <t>1473525</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>1468667</t>
+          <t>1473525</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>2239218</t>
+          <t>2243585</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -7152,17 +7152,17 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>1473525</t>
+          <t>1472251</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>1473525</t>
+          <t>1472251</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>2243585</t>
+          <t>2243875</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -7199,17 +7199,17 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>1472251</t>
+          <t>1469543</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>1472251</t>
+          <t>1469543</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>2243875</t>
+          <t>2238671</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -7246,17 +7246,17 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>1469543</t>
+          <t>1474598</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>1469543</t>
+          <t>1474598</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>2238671</t>
+          <t>2246475</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2332</t>
+          <t>26-Sep-28 2331</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -7293,17 +7293,17 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>1474598</t>
+          <t>1469613</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>1474598</t>
+          <t>1469613</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>2246475</t>
+          <t>2238649</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -7340,17 +7340,17 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>1469613</t>
+          <t>1474122</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>1469613</t>
+          <t>1474122</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>2238649</t>
+          <t>2246514</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -7387,17 +7387,17 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>1474122</t>
+          <t>1461581</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>1474122</t>
+          <t>1461581</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>2246514</t>
+          <t>2213804</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -7434,17 +7434,17 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>1461581</t>
+          <t>1469777</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>1461581</t>
+          <t>1469777</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>2213804</t>
+          <t>2238672</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -7481,17 +7481,17 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>1469777</t>
+          <t>1469660</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>1469777</t>
+          <t>1469660</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>2238672</t>
+          <t>2238677</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>1469660</t>
+          <t>1461498</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>1469660</t>
+          <t>1461498</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>2238677</t>
+          <t>2211107</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7575,17 +7575,17 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>1461498</t>
+          <t>1474467</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>1461498</t>
+          <t>1474467</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>2211107</t>
+          <t>2246507</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -7622,17 +7622,17 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>1474467</t>
+          <t>1461514</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>1474467</t>
+          <t>1461514</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>2246507</t>
+          <t>2211114</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>1461514</t>
+          <t>1471496</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>1461514</t>
+          <t>1471496</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>2211114</t>
+          <t>2243570</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -7716,17 +7716,17 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>1471496</t>
+          <t>1461523</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>1471496</t>
+          <t>1461523</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>2243570</t>
+          <t>2211047</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -7763,17 +7763,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>1461523</t>
+          <t>1469521</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>1461523</t>
+          <t>1469521</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>2211047</t>
+          <t>2238674</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -7810,17 +7810,17 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>1469521</t>
+          <t>1469771</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>1469521</t>
+          <t>1469771</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>2238674</t>
+          <t>2238695</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7857,17 +7857,17 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>1469771</t>
+          <t>1461192</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>1469771</t>
+          <t>1461192</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>2238695</t>
+          <t>2211032</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7904,17 +7904,17 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>1461192</t>
+          <t>1469315</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>1461192</t>
+          <t>1469315</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>2211032</t>
+          <t>2238624</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7951,17 +7951,17 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>1469315</t>
+          <t>1473975</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>1469315</t>
+          <t>1473975</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>2238624</t>
+          <t>2134816</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7998,17 +7998,17 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>1473975</t>
+          <t>1461117</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>1473975</t>
+          <t>1461117</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>2134816</t>
+          <t>2211040</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -8045,17 +8045,17 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>1461117</t>
+          <t>1469298</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>1461117</t>
+          <t>1469298</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>2211040</t>
+          <t>2238634</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -8092,17 +8092,17 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>1469298</t>
+          <t>1469906</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>1469298</t>
+          <t>1469906</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>2238634</t>
+          <t>2238642</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -8139,17 +8139,17 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>1469906</t>
+          <t>1461122</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>1469906</t>
+          <t>1461122</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>2238642</t>
+          <t>2211029</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -8186,17 +8186,17 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>1461122</t>
+          <t>1469767</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>1461122</t>
+          <t>1469767</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>2211029</t>
+          <t>2238606</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -8233,17 +8233,17 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>1469767</t>
+          <t>1461476</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>1469767</t>
+          <t>1461476</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>2238606</t>
+          <t>2136033</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -8280,17 +8280,17 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>1461476</t>
+          <t>1461064</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>1461476</t>
+          <t>1461064</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>2136033</t>
+          <t>2211089</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -8327,17 +8327,17 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>1461064</t>
+          <t>1473776</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>1461064</t>
+          <t>1473776</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>2211089</t>
+          <t>2246517</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -8374,17 +8374,17 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>1473776</t>
+          <t>1473686</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>1473776</t>
+          <t>1473686</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>2246517</t>
+          <t>2246490</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -8421,17 +8421,17 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>1473686</t>
+          <t>1473630</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>1473686</t>
+          <t>1473630</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>2246490</t>
+          <t>2239169</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -8468,17 +8468,17 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>1473630</t>
+          <t>1461074</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>1473630</t>
+          <t>1461074</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>2239169</t>
+          <t>2211092</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -8515,17 +8515,17 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>1461074</t>
+          <t>1461069</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>1461074</t>
+          <t>1461069</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>2211092</t>
+          <t>2211085</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -8562,17 +8562,17 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>1461069</t>
+          <t>1469782</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>1461069</t>
+          <t>1469782</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>2211085</t>
+          <t>2238651</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>1469782</t>
+          <t>1461114</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>1469782</t>
+          <t>1461114</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>2238651</t>
+          <t>2211053</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -8656,17 +8656,17 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>1461114</t>
+          <t>1461027</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>1461114</t>
+          <t>1461027</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>2211053</t>
+          <t>2211063</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2331</t>
+          <t>26-Sep-28 2330</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -8703,17 +8703,17 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>1461027</t>
+          <t>1461127</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>1461027</t>
+          <t>1461127</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>2211063</t>
+          <t>2211027</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -8750,17 +8750,17 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>1461127</t>
+          <t>1469738</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>1461127</t>
+          <t>1469738</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>2211027</t>
+          <t>2238662</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8797,17 +8797,17 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>1469738</t>
+          <t>1473500</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>1469738</t>
+          <t>1473500</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>2238662</t>
+          <t>2246551</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8844,17 +8844,17 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>1473500</t>
+          <t>1473320</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>1473500</t>
+          <t>1473320</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>2246551</t>
+          <t>2243465</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8891,17 +8891,17 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>1473320</t>
+          <t>1472273</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>1473320</t>
+          <t>1472273</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>2243465</t>
+          <t>2243881</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8938,17 +8938,17 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>1472273</t>
+          <t>1461055</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>1472273</t>
+          <t>1461055</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>2243881</t>
+          <t>2211051</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8985,17 +8985,17 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>1461055</t>
+          <t>1461056</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>1461055</t>
+          <t>1461056</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>2211051</t>
+          <t>2211094</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -9032,17 +9032,17 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>1461056</t>
+          <t>1469759</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>1461056</t>
+          <t>1469759</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>2211094</t>
+          <t>2238680</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -9079,17 +9079,17 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>1469759</t>
+          <t>1461084</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>1469759</t>
+          <t>1461084</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>2238680</t>
+          <t>2211083</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -9126,17 +9126,17 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>1461084</t>
+          <t>1461022</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>1461084</t>
+          <t>1461022</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>2211083</t>
+          <t>2211079</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -9173,17 +9173,17 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>1461022</t>
+          <t>1461097</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>1461022</t>
+          <t>1461097</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>2211079</t>
+          <t>2211061</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -9220,17 +9220,17 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>1461097</t>
+          <t>1469630</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>1461097</t>
+          <t>1469630</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>2211061</t>
+          <t>2238685</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -9267,17 +9267,17 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>1469630</t>
+          <t>1472256</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>1469630</t>
+          <t>1472256</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>2238685</t>
+          <t>2243879</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -9314,17 +9314,17 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>1472256</t>
+          <t>1472234</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>1472256</t>
+          <t>1472234</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>2243879</t>
+          <t>2243873</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -9361,17 +9361,17 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>1472234</t>
+          <t>1472220</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>1472234</t>
+          <t>1472220</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>2243873</t>
+          <t>2243876</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -9408,17 +9408,17 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>1472220</t>
+          <t>1461013</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>1472220</t>
+          <t>1461013</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>2243876</t>
+          <t>2211121</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -9455,17 +9455,17 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>1461013</t>
+          <t>1461046</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>1461013</t>
+          <t>1461046</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>2211121</t>
+          <t>2211056</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -9502,17 +9502,17 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>1461046</t>
+          <t>1469764</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>1461046</t>
+          <t>1469764</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>2211056</t>
+          <t>2238655</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -9549,17 +9549,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>1469764</t>
+          <t>1469891</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>1469764</t>
+          <t>1469891</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>2238655</t>
+          <t>2238660</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -9596,17 +9596,17 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>1469891</t>
+          <t>1461007</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>1469891</t>
+          <t>1461007</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>2238660</t>
+          <t>2211123</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -9643,17 +9643,17 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>1461007</t>
+          <t>1461004</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>1461007</t>
+          <t>1461004</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>2211123</t>
+          <t>2211103</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -9690,17 +9690,17 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>1461004</t>
+          <t>1460984</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>1461004</t>
+          <t>1460984</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>2211103</t>
+          <t>2211044</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -9737,17 +9737,17 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>1460984</t>
+          <t>1469737</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>1460984</t>
+          <t>1469737</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>2211044</t>
+          <t>2238702</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -9784,17 +9784,17 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>1469737</t>
+          <t>1461063</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>1469737</t>
+          <t>1461063</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>2238702</t>
+          <t>2211100</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -9831,17 +9831,17 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>1461063</t>
+          <t>1469765</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>1461063</t>
+          <t>1469765</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>2211100</t>
+          <t>2238700</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9878,17 +9878,17 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>1469765</t>
+          <t>1461016</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>1469765</t>
+          <t>1461016</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>2238700</t>
+          <t>2211082</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>1461016</t>
+          <t>1469680</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>1461016</t>
+          <t>1469680</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>2211082</t>
+          <t>2238611</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9972,17 +9972,17 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>1469680</t>
+          <t>1461002</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>1469680</t>
+          <t>1461002</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>2238611</t>
+          <t>2211106</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -10019,17 +10019,17 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>1461002</t>
+          <t>1663395</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>1461002</t>
+          <t>1663395</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>2211106</t>
+          <t>2373374</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2330</t>
+          <t>26-Sep-28 2218</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -10066,17 +10066,17 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>1663395</t>
+          <t>1663332</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>1663395</t>
+          <t>1663332</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>2373374</t>
+          <t>2368169</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2218</t>
+          <t>26-Sep-28 2204</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -10113,17 +10113,17 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>1663332</t>
+          <t>1662675</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>1663332</t>
+          <t>1662675</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>2368169</t>
+          <t>2378638</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2204</t>
+          <t>26-Sep-28 2013</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -10160,17 +10160,17 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>1662675</t>
+          <t>1662672</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>1662675</t>
+          <t>1662672</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>2378638</t>
+          <t>2373386</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2013</t>
+          <t>26-Sep-28 2012</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -10207,17 +10207,17 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>1662672</t>
+          <t>1662631</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>1662672</t>
+          <t>1662631</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>2373386</t>
+          <t>2378620</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2012</t>
+          <t>26-Sep-28 2005</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -10254,17 +10254,17 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>1662631</t>
+          <t>1662618</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>1662631</t>
+          <t>1662618</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>2378620</t>
+          <t>2378637</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2005</t>
+          <t>26-Sep-28 2003</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>1662618</t>
+          <t>1662579</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>1662618</t>
+          <t>1662579</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>2378637</t>
+          <t>2378614</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 2003</t>
+          <t>26-Sep-28 1957</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -10348,17 +10348,17 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>1662579</t>
+          <t>1662268</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>1662579</t>
+          <t>1662268</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>2378614</t>
+          <t>2377839</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 1957</t>
+          <t>26-Sep-28 1828</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -10395,17 +10395,17 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>1662268</t>
+          <t>1592453</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>1662268</t>
+          <t>1592453</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>2377839</t>
+          <t>2336319</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 1828</t>
+          <t>26-Sep-28 1751</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -10435,24 +10435,24 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>f987d3bb-f44f-4462-84e7-b546970e954b</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>1592453</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>1592453</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>2336319</t>
+          <t>2021736</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -10482,24 +10482,24 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>f987d3bb-f44f-4462-84e7-b546970e954b</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -10536,17 +10536,17 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1613860</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1613860</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>2341659</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -10576,24 +10576,24 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>89ba0802-2ad4-4e59-a011-827a3efaa14f</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>1613860</t>
+          <t>1661998</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>1613860</t>
+          <t>1661998</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>2341659</t>
+          <t>2373413</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 1751</t>
+          <t>26-Sep-28 1750</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -10623,39 +10623,39 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>89ba0802-2ad4-4e59-a011-827a3efaa14f</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>1661998</t>
+          <t>1658906</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>1661998</t>
+          <t>RYV5J98</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>2373413</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 1750</t>
+          <t>26-Sep-28 1006</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -10677,32 +10677,32 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>1658906</t>
+          <t>1461360</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>RYV5J98</t>
+          <t>1461360</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>2211058</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>credenciamento-veiculos</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-28 1006</t>
+          <t>26-Sep-26 0146</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -10724,17 +10724,17 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>1461360</t>
+          <t>1472148</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>1461360</t>
+          <t>1472148</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>2211058</t>
+          <t>2210694</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-26 0146</t>
+          <t>26-Sep-26 0132</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -10771,17 +10771,17 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>1472148</t>
+          <t>1461623</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>1472148</t>
+          <t>1461623</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>2210694</t>
+          <t>2089850</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-26 0132</t>
+          <t>26-Sep-24 1747</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -10818,17 +10818,17 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>1461623</t>
+          <t>1469594</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>1461623</t>
+          <t>1469594</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>2089850</t>
+          <t>2238657</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -10865,17 +10865,17 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>1469594</t>
+          <t>1469269</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>1469594</t>
+          <t>1469269</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>2238657</t>
+          <t>2238639</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-24 1747</t>
+          <t>26-Sep-24 1732</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -10912,17 +10912,17 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>1469269</t>
+          <t>1469557</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>1469269</t>
+          <t>1469557</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>2238639</t>
+          <t>2238668</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -10959,17 +10959,17 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>1469557</t>
+          <t>1461547</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>1469557</t>
+          <t>1461547</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>2238668</t>
+          <t>2211031</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-24 1732</t>
+          <t>26-Sep-24 1731</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -11006,17 +11006,17 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>1461547</t>
+          <t>1473611</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>1461547</t>
+          <t>1473611</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>2211031</t>
+          <t>2246492</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -11053,17 +11053,17 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>1473611</t>
+          <t>1469831</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>1473611</t>
+          <t>1469831</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>2246492</t>
+          <t>2238644</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -11100,17 +11100,17 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>1469831</t>
+          <t>1475031</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>1469831</t>
+          <t>1475031</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>2238644</t>
+          <t>2239463</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-24 1731</t>
+          <t>26-Sep-24 1730</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
@@ -11147,17 +11147,17 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>1475031</t>
+          <t>1469673</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>1475031</t>
+          <t>1469673</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>2239463</t>
+          <t>2238690</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -11194,17 +11194,17 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>1469673</t>
+          <t>1473707</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>1469673</t>
+          <t>1473707</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>2238690</t>
+          <t>2246522</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-24 1730</t>
+          <t>26-Sep-22 1615</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
@@ -11241,17 +11241,17 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>1473707</t>
+          <t>1473696</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>1473707</t>
+          <t>1473696</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>2246522</t>
+          <t>2246550</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-22 1615</t>
+          <t>26-Sep-22 1611</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -11288,17 +11288,17 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>1473696</t>
+          <t>1473435</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>1473696</t>
+          <t>1473435</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>2246550</t>
+          <t>2246487</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-22 1611</t>
+          <t>26-Sep-22 1610</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -11335,17 +11335,17 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>1473435</t>
+          <t>1469890</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>1473435</t>
+          <t>1469890</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>2246487</t>
+          <t>2238653</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-22 1610</t>
+          <t>26-Sep-22 1546</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -11382,17 +11382,17 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>1469890</t>
+          <t>1469839</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>1469890</t>
+          <t>1469839</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>2238653</t>
+          <t>2238667</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-22 1546</t>
+          <t>26-Sep-22 1545</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -11429,17 +11429,17 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>1469839</t>
+          <t>1461139</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>1469839</t>
+          <t>1461139</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>2238667</t>
+          <t>2211059</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-22 1545</t>
+          <t>26-Sep-21 1946</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
@@ -11476,17 +11476,17 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>1461139</t>
+          <t>1461135</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>1461139</t>
+          <t>1461135</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>2211059</t>
+          <t>2211065</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -11523,17 +11523,17 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>1461135</t>
+          <t>1461327</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>1461135</t>
+          <t>1461327</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>2211065</t>
+          <t>2211075</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-21 1946</t>
+          <t>26-Sep-21 1901</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
@@ -11570,17 +11570,17 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>1461327</t>
+          <t>1461183</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>1461327</t>
+          <t>1461183</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>2211075</t>
+          <t>2211097</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-21 1901</t>
+          <t>26-Sep-21 1602</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -11617,17 +11617,17 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>1461183</t>
+          <t>1469610</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>1461183</t>
+          <t>1469610</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>2211097</t>
+          <t>2238613</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -11664,17 +11664,17 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>1469610</t>
+          <t>1469585</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>1469610</t>
+          <t>1469585</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>2238613</t>
+          <t>2238630</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-21 1602</t>
+          <t>26-Sep-21 1547</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -11711,17 +11711,17 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>1469585</t>
+          <t>1469580</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>1469585</t>
+          <t>1469580</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>2238630</t>
+          <t>2238608</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-21 1547</t>
+          <t>26-Sep-21 1545</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -11758,17 +11758,17 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>1469580</t>
+          <t>1469556</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>1469580</t>
+          <t>1469556</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>2238608</t>
+          <t>2238633</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-21 1545</t>
+          <t>26-Sep-21 1533</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -11805,17 +11805,17 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>1469556</t>
+          <t>1469541</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>1469556</t>
+          <t>1469541</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>2238633</t>
+          <t>2238659</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-21 1533</t>
+          <t>26-Sep-21 1517</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
@@ -11852,17 +11852,17 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>1469541</t>
+          <t>1461113</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>1469541</t>
+          <t>1461113</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>2238659</t>
+          <t>2211071</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-21 1517</t>
+          <t>26-Sep-16 0146</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
@@ -11899,17 +11899,17 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>1461113</t>
+          <t>1461384</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>1461113</t>
+          <t>1461384</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>2211071</t>
+          <t>2211046</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-16 0146</t>
+          <t>26-Sep-06 0747</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
@@ -11946,17 +11946,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>1461384</t>
+          <t>1460995</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>1461384</t>
+          <t>1460995</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>2211046</t>
+          <t>2211119</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-06 0747</t>
+          <t>26-Sep-06 0746</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
@@ -11993,17 +11993,17 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>1460995</t>
+          <t>1460964</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>1460995</t>
+          <t>1460964</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>2211119</t>
+          <t>2211069</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-06 0746</t>
+          <t>26-Sep-06 0745</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -12040,17 +12040,17 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>1460964</t>
+          <t>1460977</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>1460964</t>
+          <t>1460977</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>2211069</t>
+          <t>2211115</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -12087,17 +12087,17 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>1460977</t>
+          <t>1461009</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>1460977</t>
+          <t>1461009</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>2211115</t>
+          <t>2211073</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -12134,17 +12134,17 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>1461009</t>
+          <t>1460950</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>1461009</t>
+          <t>1460950</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>2211073</t>
+          <t>2211102</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -12181,17 +12181,17 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>1460950</t>
+          <t>1414408</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>1460950</t>
+          <t>1414408</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>2211102</t>
+          <t>2211126</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -12228,17 +12228,17 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>1414408</t>
+          <t>1460983</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>1414408</t>
+          <t>1460983</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>2211126</t>
+          <t>2211110</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -12275,17 +12275,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>1460983</t>
+          <t>1460955</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>1460983</t>
+          <t>1460955</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>2211110</t>
+          <t>2211087</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -12322,17 +12322,17 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>1460955</t>
+          <t>1460961</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>1460955</t>
+          <t>1460961</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>2211087</t>
+          <t>2211111</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -12369,17 +12369,17 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>1460961</t>
+          <t>1469493</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>1460961</t>
+          <t>1469493</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>2211111</t>
+          <t>2238628</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>26-Sep-06 0745</t>
+          <t>26-Aug-30 1748</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
@@ -12416,17 +12416,17 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>1469493</t>
+          <t>1461179</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>1469493</t>
+          <t>1461179</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>2238628</t>
+          <t>2211041</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -12463,17 +12463,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>1461179</t>
+          <t>1461184</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>1461179</t>
+          <t>1461184</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>2211041</t>
+          <t>2211096</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-30 1748</t>
+          <t>26-Aug-30 1746</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -12510,17 +12510,17 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>1461184</t>
+          <t>1460959</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>1461184</t>
+          <t>1460959</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>2211096</t>
+          <t>2211118</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-30 1746</t>
+          <t>26-Aug-30 1745</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -12557,17 +12557,17 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>1460959</t>
+          <t>1414386</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>1460959</t>
+          <t>1414386</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>2211118</t>
+          <t>2211130</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -12604,17 +12604,17 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>1414386</t>
+          <t>1319752</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>1414386</t>
+          <t>1319752</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>2211130</t>
+          <t>2151069</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-30 1745</t>
+          <t>26-Aug-25 0713</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -12651,17 +12651,17 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>1319752</t>
+          <t>1327453</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>1319752</t>
+          <t>1327453</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>2151069</t>
+          <t>2138019</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0713</t>
+          <t>26-Aug-25 0712</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -12698,17 +12698,17 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>1327453</t>
+          <t>1318569</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>1327453</t>
+          <t>1318569</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>2138019</t>
+          <t>2151095</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -12745,17 +12745,17 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>1318569</t>
+          <t>1306973</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>1318569</t>
+          <t>1306973</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>2151095</t>
+          <t>2170260</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0712</t>
+          <t>26-Aug-25 0711</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -12792,17 +12792,17 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>1306973</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>1306973</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>2170260</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0711</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -12839,17 +12839,17 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1334650</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1334650</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>2190599</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -12886,17 +12886,17 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>1334650</t>
+          <t>1393948</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>1334650</t>
+          <t>1393948</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>2190599</t>
+          <t>2209715</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Aug-25 0642</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -12933,17 +12933,17 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>1393948</t>
+          <t>1343918</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>1393948</t>
+          <t>1343918</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>2209715</t>
+          <t>2164151</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0642</t>
+          <t>26-Aug-25 0641</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -12980,17 +12980,17 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>1343918</t>
+          <t>1393937</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>1343918</t>
+          <t>1393937</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>2164151</t>
+          <t>2209843</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0641</t>
+          <t>26-Aug-25 0623</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -13027,17 +13027,17 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>1393937</t>
+          <t>1348434</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>1393937</t>
+          <t>1348434</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>2209843</t>
+          <t>2163873</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -13074,17 +13074,17 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>1348434</t>
+          <t>1344113</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>1348434</t>
+          <t>1344113</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>2163873</t>
+          <t>2190597</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0623</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -13121,17 +13121,17 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>1344113</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>1344113</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>2190597</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -13168,17 +13168,17 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1334753</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1334753</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2190603</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Aug-25 0617</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -13215,17 +13215,17 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>1334753</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>1334753</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>2190603</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0617</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -13262,17 +13262,17 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -13309,17 +13309,17 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1302291</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1302291</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2164232</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Aug-25 0610</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -13356,17 +13356,17 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>1302291</t>
+          <t>1301981</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>1302291</t>
+          <t>1301981</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>2164232</t>
+          <t>2164205</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0610</t>
+          <t>26-Aug-25 0608</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -13403,17 +13403,17 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>1301981</t>
+          <t>1301772</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>1301981</t>
+          <t>1301772</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>2164205</t>
+          <t>2164196</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0608</t>
+          <t>26-Aug-25 0607</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -13450,17 +13450,17 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>1301772</t>
+          <t>1301890</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>1301772</t>
+          <t>1301890</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>2164196</t>
+          <t>2164207</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -13497,17 +13497,17 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>1301890</t>
+          <t>1301257</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>1301890</t>
+          <t>1301257</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>2164207</t>
+          <t>2164155</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0607</t>
+          <t>26-Aug-25 0606</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -13544,17 +13544,17 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>1301257</t>
+          <t>1301948</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>1301257</t>
+          <t>1301948</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>2164155</t>
+          <t>2164210</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0606</t>
+          <t>26-Aug-25 0602</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -13591,17 +13591,17 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>1301948</t>
+          <t>1301648</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>1301948</t>
+          <t>1301648</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>2164210</t>
+          <t>2164184</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -13638,17 +13638,17 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>1301648</t>
+          <t>1301476</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>1301648</t>
+          <t>1301476</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>2164184</t>
+          <t>2164176</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0602</t>
+          <t>26-Aug-25 0601</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -13685,17 +13685,17 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>1301476</t>
+          <t>1301808</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>1301476</t>
+          <t>1301808</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>2164176</t>
+          <t>2164194</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0601</t>
+          <t>26-Aug-25 0600</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -13732,17 +13732,17 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>1301808</t>
+          <t>1301443</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>1301808</t>
+          <t>1301443</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>2164194</t>
+          <t>2164165</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -13779,17 +13779,17 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>1301443</t>
+          <t>1301251</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>1301443</t>
+          <t>1301251</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>2164165</t>
+          <t>2164153</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0600</t>
+          <t>26-Aug-25 0559</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -13826,17 +13826,17 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>1301251</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>1301251</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>2164153</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0559</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -13873,17 +13873,17 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1253696</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1253696</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2138028</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -13920,17 +13920,17 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>1253696</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>1253696</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>2138028</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -13967,17 +13967,17 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1282394</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1282394</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>2140641</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -14014,17 +14014,17 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>1282394</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>1282394</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>2140641</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -14061,17 +14061,17 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1253676</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1253676</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>2138015</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -14108,17 +14108,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>1253676</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>1253676</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>2138015</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -14155,17 +14155,17 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1213460</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1213460</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>2118692</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Aug-25 0554</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
@@ -14202,17 +14202,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>1213460</t>
+          <t>1343931</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>1213460</t>
+          <t>1343931</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>2118692</t>
+          <t>2164142</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0554</t>
+          <t>26-Aug-25 0548</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
@@ -14249,17 +14249,17 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>1343931</t>
+          <t>1302445</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>1343931</t>
+          <t>1302445</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>2164142</t>
+          <t>2164238</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0548</t>
+          <t>26-Aug-25 0544</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
@@ -14296,17 +14296,17 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>1302445</t>
+          <t>1302173</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>1302445</t>
+          <t>1302173</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>2164238</t>
+          <t>2164225</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0544</t>
+          <t>26-Aug-25 0543</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
@@ -14343,17 +14343,17 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>1302173</t>
+          <t>1302164</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>1302173</t>
+          <t>1302164</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>2164225</t>
+          <t>2164216</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -14390,17 +14390,17 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>1302164</t>
+          <t>1114887</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>1302164</t>
+          <t>1114887</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>2164216</t>
+          <t>2068506</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0543</t>
+          <t>26-Aug-25 0539</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
@@ -14437,17 +14437,17 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>1114887</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>1114887</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>2068506</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0539</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
@@ -14484,17 +14484,17 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
@@ -14531,17 +14531,17 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1334668</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1334668</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>2190601</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Aug-25 0532</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>1334668</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>1334668</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>2190601</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0532</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
@@ -14625,17 +14625,17 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1334802</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1334802</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>2190611</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -14672,17 +14672,17 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>1334802</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>1334802</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>2190611</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
@@ -14719,17 +14719,17 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1302310</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1302310</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>2164221</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -14766,17 +14766,17 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>1302310</t>
+          <t>1301539</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>1302310</t>
+          <t>1301539</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>2164221</t>
+          <t>2164177</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Aug-25 0525</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
@@ -14813,17 +14813,17 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>1301539</t>
+          <t>1301451</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>1301539</t>
+          <t>1301451</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>2164177</t>
+          <t>2164164</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0525</t>
+          <t>26-Aug-25 0524</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
@@ -14860,17 +14860,17 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>1301451</t>
+          <t>1301323</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>1301451</t>
+          <t>1301323</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>2164164</t>
+          <t>2164157</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0524</t>
+          <t>26-Aug-25 0520</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
@@ -14907,17 +14907,17 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>1301323</t>
+          <t>1301172</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>1301323</t>
+          <t>1301172</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>2164157</t>
+          <t>2164149</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0520</t>
+          <t>26-Aug-25 0518</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
@@ -14954,17 +14954,17 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>1301172</t>
+          <t>1253764</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>1301172</t>
+          <t>1253764</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>2164149</t>
+          <t>2138007</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0518</t>
+          <t>26-Aug-25 0516</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
@@ -15001,17 +15001,17 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>1253764</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>1253764</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>2138007</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0516</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
@@ -15048,17 +15048,17 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1113018</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1113018</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>2075961</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Aug-25 0508</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
@@ -15095,17 +15095,17 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>1113018</t>
+          <t>1302005</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>1113018</t>
+          <t>1302005</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>2075961</t>
+          <t>2164214</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0508</t>
+          <t>26-Aug-25 0502</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
@@ -15142,17 +15142,17 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>1302005</t>
+          <t>1301701</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>1302005</t>
+          <t>1301701</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>2164214</t>
+          <t>2164190</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
@@ -15189,17 +15189,17 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>1301701</t>
+          <t>1301793</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>1301701</t>
+          <t>1301793</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>2164190</t>
+          <t>2164200</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0502</t>
+          <t>26-Aug-25 0500</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
@@ -15236,17 +15236,17 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>1301793</t>
+          <t>1289554</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>1301793</t>
+          <t>1289554</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>2164200</t>
+          <t>2140569</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0500</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
@@ -15283,17 +15283,17 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>1289554</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>1289554</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>2140569</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
@@ -15330,17 +15330,17 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
@@ -15377,17 +15377,17 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
@@ -15424,17 +15424,17 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1252766</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1252766</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>2138051</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
@@ -15471,17 +15471,17 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>1252766</t>
+          <t>1289618</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>1252766</t>
+          <t>1289618</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>2138051</t>
+          <t>2140565</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
@@ -15518,17 +15518,17 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>1289618</t>
+          <t>1381883</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>1289618</t>
+          <t>1381883</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>2140565</t>
+          <t>2216262</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Aug-25 0426</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
@@ -15565,17 +15565,17 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>1381883</t>
+          <t>1334824</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>1381883</t>
+          <t>1334824</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>2216262</t>
+          <t>2190605</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0426</t>
+          <t>26-Aug-25 0425</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
@@ -15612,17 +15612,17 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>1334824</t>
+          <t>1334776</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>1334824</t>
+          <t>1334776</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>2190605</t>
+          <t>2190613</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0425</t>
+          <t>26-Aug-25 0423</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
@@ -15659,17 +15659,17 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>1334776</t>
+          <t>1334577</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>1334776</t>
+          <t>1334577</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>2190613</t>
+          <t>2190595</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0423</t>
+          <t>26-Aug-25 0422</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
@@ -15706,17 +15706,17 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>1334577</t>
+          <t>1302204</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>1334577</t>
+          <t>1302204</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>2190595</t>
+          <t>2164230</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0422</t>
+          <t>26-Aug-25 0420</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
@@ -15753,17 +15753,17 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>1302204</t>
+          <t>1302284</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>1302204</t>
+          <t>1302284</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>2164230</t>
+          <t>2164234</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0420</t>
+          <t>26-Aug-25 0419</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
@@ -15800,17 +15800,17 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>1302284</t>
+          <t>1301859</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>1302284</t>
+          <t>1301859</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>2164234</t>
+          <t>2164198</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
@@ -15847,17 +15847,17 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>1301859</t>
+          <t>1301849</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>1301859</t>
+          <t>1301849</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>2164198</t>
+          <t>2164202</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -15894,17 +15894,17 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>1301849</t>
+          <t>1301436</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>1301849</t>
+          <t>1301436</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>2164202</t>
+          <t>2164167</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0419</t>
+          <t>26-Aug-25 0415</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
@@ -15941,17 +15941,17 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>1301436</t>
+          <t>1301224</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>1301436</t>
+          <t>1301224</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>2164167</t>
+          <t>2164145</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0415</t>
+          <t>26-Aug-25 0414</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
@@ -15988,17 +15988,17 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>1301224</t>
+          <t>1301736</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>1301224</t>
+          <t>1301736</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>2164145</t>
+          <t>2164185</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
@@ -16035,17 +16035,17 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>1301736</t>
+          <t>1289684</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>1301736</t>
+          <t>1289684</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>2164185</t>
+          <t>2140573</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0414</t>
+          <t>26-Aug-25 0409</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr">
@@ -16082,17 +16082,17 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>1289684</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>1289684</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>2140573</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0409</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
@@ -16129,17 +16129,17 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1287069</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1287069</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>2137953</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -16176,17 +16176,17 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>1287069</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>1287069</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>2137953</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G345" s="2" t="inlineStr">
@@ -16223,17 +16223,17 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1393873</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1393873</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>2209607</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Aug-25 0234</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
@@ -16270,17 +16270,17 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>1393873</t>
+          <t>1393899</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>1393873</t>
+          <t>1393899</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>2209607</t>
+          <t>2209562</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
@@ -16317,17 +16317,17 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>1393899</t>
+          <t>1393966</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>1393899</t>
+          <t>1393966</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>2209562</t>
+          <t>2209946</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0234</t>
+          <t>26-Aug-25 0233</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
@@ -16364,17 +16364,17 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>1393966</t>
+          <t>1334771</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>1393966</t>
+          <t>1334771</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>2209946</t>
+          <t>2190607</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0233</t>
+          <t>26-Aug-25 0231</t>
         </is>
       </c>
       <c r="G349" s="2" t="inlineStr">
@@ -16411,17 +16411,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>1334771</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>1334771</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>2190607</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0231</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
@@ -16458,17 +16458,17 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1319064</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1319064</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>2179227</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Aug-25 0228</t>
         </is>
       </c>
       <c r="G351" s="2" t="inlineStr">
@@ -16505,17 +16505,17 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>1319064</t>
+          <t>1343632</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>1319064</t>
+          <t>1343632</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>2179227</t>
+          <t>2164158</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0228</t>
+          <t>26-Aug-25 0227</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
@@ -16552,17 +16552,17 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>1343632</t>
+          <t>1301878</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>1343632</t>
+          <t>1301878</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>2164158</t>
+          <t>2164204</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0227</t>
+          <t>26-Aug-25 0226</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
@@ -16599,17 +16599,17 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>1301878</t>
+          <t>1302436</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>1301878</t>
+          <t>1302436</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>2164204</t>
+          <t>2164236</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -16646,17 +16646,17 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>1302436</t>
+          <t>1301715</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>1302436</t>
+          <t>1301715</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>2164236</t>
+          <t>2164192</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -16693,17 +16693,17 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>1301715</t>
+          <t>1305841</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>1301715</t>
+          <t>1305841</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>2164192</t>
+          <t>2150984</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -16740,17 +16740,17 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>1305841</t>
+          <t>1302002</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>1305841</t>
+          <t>1302002</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>2150984</t>
+          <t>2164212</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0226</t>
+          <t>26-Aug-25 0225</t>
         </is>
       </c>
       <c r="G357" s="2" t="inlineStr">
@@ -16787,17 +16787,17 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>1302002</t>
+          <t>1301670</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>1302002</t>
+          <t>1301670</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>2164212</t>
+          <t>2164188</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -16834,17 +16834,17 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>1301670</t>
+          <t>1301469</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>1301670</t>
+          <t>1301469</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>2164188</t>
+          <t>2164174</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0225</t>
+          <t>26-Aug-25 0224</t>
         </is>
       </c>
       <c r="G359" s="2" t="inlineStr">
@@ -16881,17 +16881,17 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>1301469</t>
+          <t>1301564</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>1301469</t>
+          <t>1301564</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>2164174</t>
+          <t>2164179</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0224</t>
+          <t>26-Aug-25 0219</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
@@ -16928,17 +16928,17 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>1301564</t>
+          <t>1301060</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>1301564</t>
+          <t>1301060</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>2164179</t>
+          <t>2164138</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0219</t>
+          <t>26-Aug-25 0217</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
@@ -16975,17 +16975,17 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>1301060</t>
+          <t>1301082</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>1301060</t>
+          <t>1301082</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>2164138</t>
+          <t>2164140</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -17022,17 +17022,17 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>1301082</t>
+          <t>1287853</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>1301082</t>
+          <t>1287853</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>2164140</t>
+          <t>2138121</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0217</t>
+          <t>26-Aug-25 0216</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
@@ -17069,17 +17069,17 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>1287853</t>
+          <t>1252800</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>1287853</t>
+          <t>1252800</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>2138121</t>
+          <t>2138042</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0216</t>
+          <t>26-Aug-25 0214</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
@@ -17116,17 +17116,17 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>1252800</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>1252800</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>2138042</t>
+          <t>2130202</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0214</t>
+          <t>26-Aug-25 0213</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
@@ -17163,17 +17163,17 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1393880</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1393880</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>2130202</t>
+          <t>2210162</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0213</t>
+          <t>26-Aug-22 2022</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
@@ -17210,17 +17210,17 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>1393880</t>
+          <t>1334792</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>1393880</t>
+          <t>1334792</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>2210162</t>
+          <t>2190609</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -17235,7 +17235,7 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 2022</t>
+          <t>26-Aug-22 2019</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
@@ -17257,17 +17257,17 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>1334792</t>
+          <t>1302183</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>1334792</t>
+          <t>1302183</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>2190609</t>
+          <t>2164228</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 2019</t>
+          <t>26-Aug-22 2002</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
@@ -17304,17 +17304,17 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>1302183</t>
+          <t>1393989</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>1302183</t>
+          <t>1393989</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>2164228</t>
+          <t>2210165</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 2002</t>
+          <t>26-Aug-22 0421</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
@@ -17351,17 +17351,17 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>1393989</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>1393989</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>2210165</t>
+          <t>2216095</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0421</t>
+          <t>26-Aug-22 0148</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
@@ -17398,17 +17398,17 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1301464</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1301464</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>2164172</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Aug-22 0116</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
@@ -17445,17 +17445,17 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>1301464</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>1301464</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>2164172</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0116</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
@@ -17492,17 +17492,17 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>2211543</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Aug-21 2220</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
@@ -17539,17 +17539,17 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1399080</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1399080</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>2121335</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Aug-21 0925</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
@@ -17586,17 +17586,17 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>1399080</t>
+          <t>1398759</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>1399080</t>
+          <t>1398759</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>2121335</t>
+          <t>2211016</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0925</t>
+          <t>26-Aug-21 0924</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
@@ -17633,17 +17633,17 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>1398759</t>
+          <t>1394906</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>1398759</t>
+          <t>1394906</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>2211016</t>
+          <t>2211013</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0924</t>
+          <t>26-Aug-21 0923</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
@@ -17680,17 +17680,17 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>1394906</t>
+          <t>1395080</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>1394906</t>
+          <t>1395080</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>2211013</t>
+          <t>2211014</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
@@ -17727,17 +17727,17 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>1395080</t>
+          <t>1398819</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>1395080</t>
+          <t>1398819</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>2211014</t>
+          <t>2211018</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0923</t>
+          <t>26-Aug-21 0922</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
@@ -17774,17 +17774,17 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>1398819</t>
+          <t>1394216</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>1398819</t>
+          <t>1394216</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>2211018</t>
+          <t>2193992</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
@@ -17821,17 +17821,17 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>1394216</t>
+          <t>1394229</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>1394216</t>
+          <t>1394229</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>2193992</t>
+          <t>2193996</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
@@ -17868,17 +17868,17 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>1394229</t>
+          <t>1395038</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>1394229</t>
+          <t>1395038</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>2193996</t>
+          <t>2211008</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0922</t>
+          <t>26-Aug-21 0920</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
@@ -17915,17 +17915,17 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>1395038</t>
+          <t>1398954</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>1395038</t>
+          <t>1398954</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>2211008</t>
+          <t>2211015</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
@@ -17962,17 +17962,17 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>1398954</t>
+          <t>1398785</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>1398954</t>
+          <t>1398785</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>2211015</t>
+          <t>2210943</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0920</t>
+          <t>26-Aug-21 0919</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
@@ -18009,17 +18009,17 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>1398785</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>1398785</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>2210943</t>
+          <t>2211489</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -18056,17 +18056,17 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1394050</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1394050</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>2211489</t>
+          <t>2209550</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -18103,17 +18103,17 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>1394050</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>1394050</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>2209550</t>
+          <t>2095869</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0919</t>
+          <t>26-Aug-19 0146</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr">
@@ -18150,17 +18150,17 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>1226304</t>
+          <t>1115315</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>1226304</t>
+          <t>1115315</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>2095869</t>
+          <t>2057287</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -18175,7 +18175,7 @@
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-19 0146</t>
+          <t>26-Aug-05 0745</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
@@ -18189,53 +18189,6 @@
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="2" t="inlineStr">
-        <is>
-          <t>1115315</t>
-        </is>
-      </c>
-      <c r="B388" s="2" t="inlineStr">
-        <is>
-          <t>1115315</t>
-        </is>
-      </c>
-      <c r="C388" s="2" t="inlineStr">
-        <is>
-          <t>2057287</t>
-        </is>
-      </c>
-      <c r="D388" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F388" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-05 0745</t>
-        </is>
-      </c>
-      <c r="G388" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H388" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I388" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -178,18 +178,18 @@
     <col min="1" max="1" width="33.84375" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
     <col min="3" max="3" width="14.8203125" customWidth="true"/>
-    <col min="4" max="4" width="32.30078125" customWidth="true"/>
+    <col min="4" max="4" width="23.0078125" customWidth="true"/>
     <col min="5" max="5" width="11.01953125" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="16.40234375" customWidth="true"/>
-    <col min="8" max="8" width="16.40234375" customWidth="true"/>
+    <col min="8" max="8" width="14.92578125" customWidth="true"/>
     <col min="9" max="9" width="11.37890625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 167 item(s) at 2026-10-05</t>
+          <t>Displaying 113 item(s) at 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -243,37 +243,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1716942</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1716942</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36691413</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1700</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1700</t>
+          <t/>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1700</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1700</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1700</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1700</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1716726</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1716726</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2411101</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1651</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1716712</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1716712</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2391440</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1651</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1716630</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1716630</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2410967</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1647</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1647</t>
+          <t>26-Oct-05 1800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,37 +666,37 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1712819</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1712819</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>AL_36629175</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1646</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -713,37 +713,37 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1712818</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1712818</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>AL_36629211</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1646</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1712817</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1712817</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>AL_36629205</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1646</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -807,37 +807,37 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1712816</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1712816</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>AL_36629190</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1645</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -854,37 +854,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1716532</t>
+          <t>1712815</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1716532</t>
+          <t>1712815</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2411042</t>
+          <t>AL_36629181</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1639</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -901,37 +901,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1716424</t>
+          <t>1712814</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1716424</t>
+          <t>1712814</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2391920</t>
+          <t>AL_36629220</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1628</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -948,37 +948,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1716366</t>
+          <t>1712813</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1716366</t>
+          <t>1712813</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2396170</t>
+          <t>AL_36629184</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1624</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -995,37 +995,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1716323</t>
+          <t>1712812</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1716323</t>
+          <t>1712812</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2391883</t>
+          <t>AL_36629187</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1619</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1042,37 +1042,37 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1716170</t>
+          <t>1712811</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1716170</t>
+          <t>1712811</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2410952</t>
+          <t>AL_36629226</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1604</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1089,37 +1089,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1716090</t>
+          <t>1712810</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1716090</t>
+          <t>1712810</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2409318</t>
+          <t>AL_36629223</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1556</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1136,37 +1136,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1716071</t>
+          <t>1712809</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1716071</t>
+          <t>1712809</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2410233</t>
+          <t>AL_36629199</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1554</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1183,37 +1183,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1716052</t>
+          <t>1712808</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1716052</t>
+          <t>1712808</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2407817</t>
+          <t>AL_36629217</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1552</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1230,37 +1230,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1715933</t>
+          <t>1712807</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1715933</t>
+          <t>1712807</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2390109</t>
+          <t>AL_36629202</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1544</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1277,37 +1277,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1715901</t>
+          <t>1712806</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1715901</t>
+          <t>1712806</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2390694</t>
+          <t>AL_36629229</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1542</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1324,37 +1324,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1715886</t>
+          <t>1712805</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1715886</t>
+          <t>1712805</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2391127</t>
+          <t>AL_36629233</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1540</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1371,37 +1371,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1715860</t>
+          <t>1712804</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1715860</t>
+          <t>1712804</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2408711</t>
+          <t>AL_36629178</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1536</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1418,37 +1418,37 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1715832</t>
+          <t>1712802</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1715832</t>
+          <t>1712802</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2375053</t>
+          <t>AL_36629214</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1530</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1465,37 +1465,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1715677</t>
+          <t>1712803</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1715677</t>
+          <t>1712803</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2391709</t>
+          <t>AL_36629196</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1512</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1512,37 +1512,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1715599</t>
+          <t>1712801</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1715599</t>
+          <t>1712801</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2391335</t>
+          <t>AL_36629208</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1503</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1559,37 +1559,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1715403</t>
+          <t>1712800</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1715403</t>
+          <t>1712800</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2363258</t>
+          <t>AL_36629193</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1437</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1606,37 +1606,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1715028</t>
+          <t>1712799</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1715028</t>
+          <t>1712799</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2391074</t>
+          <t>AL_36629169</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1402</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1653,37 +1653,37 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1714765</t>
+          <t>1712798</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1714765</t>
+          <t>1712798</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2391386</t>
+          <t>AL_36629166</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1308</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1700,37 +1700,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1714756</t>
+          <t>1712796</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1714756</t>
+          <t>1712796</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2391879</t>
+          <t>AL_36629172</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1306</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1747,37 +1747,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1714161</t>
+          <t>1712797</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1714161</t>
+          <t>1712797</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2401162</t>
+          <t>AL_36629157</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1120</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,37 +1794,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1714109</t>
+          <t>1712795</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1714109</t>
+          <t>1712795</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2401180</t>
+          <t>AL_36629163</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1110</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1841,37 +1841,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1714055</t>
+          <t>1712794</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1714055</t>
+          <t>1712794</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2401134</t>
+          <t>AL_36629148</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1101</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1888,37 +1888,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1714045</t>
+          <t>1712793</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1714045</t>
+          <t>1712793</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2401132</t>
+          <t>AL_36629160</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1059</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1935,37 +1935,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1713962</t>
+          <t>1712792</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1713962</t>
+          <t>1712792</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2391891</t>
+          <t>AL_36629151</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1044</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1982,37 +1982,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1713757</t>
+          <t>1712791</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1713757</t>
+          <t>1712791</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2391670</t>
+          <t>AL_36629154</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1015</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2029,37 +2029,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1713617</t>
+          <t>1712790</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1713617</t>
+          <t>1712790</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2391397</t>
+          <t>AL_36629124</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0954</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2076,37 +2076,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1713394</t>
+          <t>1712789</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1713394</t>
+          <t>1712789</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2391610</t>
+          <t>AL_36629145</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0921</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2123,17 +2123,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1712819</t>
+          <t>1712788</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1712819</t>
+          <t>1712788</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>AL_36629175</t>
+          <t>AL_36629130</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1712818</t>
+          <t>1712787</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1712818</t>
+          <t>1712787</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>AL_36629211</t>
+          <t>AL_36629142</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1712817</t>
+          <t>1712786</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1712817</t>
+          <t>1712786</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AL_36629205</t>
+          <t>AL_36629136</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1712816</t>
+          <t>1712785</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1712816</t>
+          <t>1712785</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>AL_36629190</t>
+          <t>AL_36629127</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1712815</t>
+          <t>1712784</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1712815</t>
+          <t>1712784</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>AL_36629181</t>
+          <t>AL_36629139</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1712814</t>
+          <t>1712783</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1712814</t>
+          <t>1712783</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>AL_36629220</t>
+          <t>AL_36629112</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1712813</t>
+          <t>1712782</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1712813</t>
+          <t>1712782</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>AL_36629184</t>
+          <t>AL_36629133</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1712812</t>
+          <t>1712780</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1712812</t>
+          <t>1712780</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>AL_36629187</t>
+          <t>AL_36629118</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2499,17 +2499,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1712811</t>
+          <t>1712781</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1712811</t>
+          <t>1712781</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>AL_36629226</t>
+          <t>AL_36629109</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2546,17 +2546,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1712810</t>
+          <t>1712779</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1712810</t>
+          <t>1712779</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>AL_36629223</t>
+          <t>AL_36629121</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1712809</t>
+          <t>1712778</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1712809</t>
+          <t>1712778</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>AL_36629199</t>
+          <t>AL_36629115</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1712808</t>
+          <t>1712776</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1712808</t>
+          <t>1712776</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>AL_36629217</t>
+          <t>AL_36629100</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1712807</t>
+          <t>1712777</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1712807</t>
+          <t>1712777</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>AL_36629202</t>
+          <t>AL_36629094</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2734,17 +2734,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1712806</t>
+          <t>1712775</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1712806</t>
+          <t>1712775</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>AL_36629229</t>
+          <t>AL_36629106</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2781,17 +2781,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1712805</t>
+          <t>1712773</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1712805</t>
+          <t>1712773</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>AL_36629233</t>
+          <t>AL_36629097</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2828,17 +2828,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1712804</t>
+          <t>1712774</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1712804</t>
+          <t>1712774</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>AL_36629178</t>
+          <t>AL_36629091</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2875,17 +2875,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1712802</t>
+          <t>1712772</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1712802</t>
+          <t>1712772</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>AL_36629214</t>
+          <t>AL_36629103</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2922,17 +2922,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1712803</t>
+          <t>1712771</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1712803</t>
+          <t>1712771</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>AL_36629196</t>
+          <t>AL_36629073</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1712801</t>
+          <t>1712770</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1712801</t>
+          <t>1712770</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>AL_36629208</t>
+          <t>AL_36629085</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3016,17 +3016,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1712800</t>
+          <t>1712769</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1712800</t>
+          <t>1712769</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>AL_36629193</t>
+          <t>AL_36629082</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1712799</t>
+          <t>1712768</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1712799</t>
+          <t>1712768</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>AL_36629169</t>
+          <t>AL_36629079</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3110,17 +3110,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1712798</t>
+          <t>1712767</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1712798</t>
+          <t>1712767</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>AL_36629166</t>
+          <t>AL_36629088</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3157,17 +3157,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1712796</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1712796</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>AL_36629172</t>
+          <t>AL_36629076</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1712797</t>
+          <t>1712765</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1712797</t>
+          <t>1712765</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>AL_36629157</t>
+          <t>AL_36629064</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1712795</t>
+          <t>1712764</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1712795</t>
+          <t>1712764</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>AL_36629163</t>
+          <t>AL_36629070</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1712794</t>
+          <t>1712763</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1712794</t>
+          <t>1712763</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>AL_36629148</t>
+          <t>AL_36629067</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3345,17 +3345,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1712793</t>
+          <t>1712762</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1712793</t>
+          <t>1712762</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>AL_36629160</t>
+          <t>AL_36629055</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3392,17 +3392,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1712792</t>
+          <t>1712761</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1712792</t>
+          <t>1712761</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>AL_36629151</t>
+          <t>AL_36629061</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1712791</t>
+          <t>1712760</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1712791</t>
+          <t>1712760</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>AL_36629154</t>
+          <t>AL_36629058</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3486,17 +3486,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1712790</t>
+          <t>1712759</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1712790</t>
+          <t>1712759</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>AL_36629124</t>
+          <t>AL_36629031</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3533,17 +3533,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>1712789</t>
+          <t>1712758</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1712789</t>
+          <t>1712758</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>AL_36629145</t>
+          <t>AL_36629037</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3580,17 +3580,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>1712788</t>
+          <t>1712757</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1712788</t>
+          <t>1712757</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>AL_36629130</t>
+          <t>AL_36629021</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3627,17 +3627,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1712787</t>
+          <t>1712756</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>1712787</t>
+          <t>1712756</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>AL_36629142</t>
+          <t>AL_36629040</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3674,17 +3674,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1712786</t>
+          <t>1712755</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1712786</t>
+          <t>1712755</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>AL_36629136</t>
+          <t>AL_36629006</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3721,17 +3721,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1712785</t>
+          <t>1712754</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1712785</t>
+          <t>1712754</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>AL_36629127</t>
+          <t>AL_36629034</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3768,17 +3768,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1712784</t>
+          <t>1712753</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1712784</t>
+          <t>1712753</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>AL_36629139</t>
+          <t>AL_36629018</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1712783</t>
+          <t>1712752</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1712783</t>
+          <t>1712752</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>AL_36629112</t>
+          <t>AL_36629043</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3862,17 +3862,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1712782</t>
+          <t>1712751</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1712782</t>
+          <t>1712751</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>AL_36629133</t>
+          <t>AL_36629015</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3909,17 +3909,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1712780</t>
+          <t>1712750</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1712780</t>
+          <t>1712750</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>AL_36629118</t>
+          <t>AL_36629003</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3956,17 +3956,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1712781</t>
+          <t>1712749</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1712781</t>
+          <t>1712749</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>AL_36629109</t>
+          <t>AL_36629052</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4003,17 +4003,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1712779</t>
+          <t>1712748</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>1712779</t>
+          <t>1712748</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>AL_36629121</t>
+          <t>AL_36629046</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4050,17 +4050,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>1712778</t>
+          <t>1712747</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1712778</t>
+          <t>1712747</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>AL_36629115</t>
+          <t>AL_36629009</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4097,17 +4097,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1712776</t>
+          <t>1712746</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1712776</t>
+          <t>1712746</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>AL_36629100</t>
+          <t>AL_36629024</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1712777</t>
+          <t>1712745</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>1712777</t>
+          <t>1712745</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>AL_36629094</t>
+          <t>AL_36629027</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4191,17 +4191,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>1712775</t>
+          <t>1712744</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>1712775</t>
+          <t>1712744</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>AL_36629106</t>
+          <t>AL_36629049</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4238,37 +4238,37 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>1712773</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>1712773</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>AL_36629097</t>
+          <t>2021736</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-01 1049</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -4285,37 +4285,37 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1712774</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>1712774</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>AL_36629091</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-01 1049</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -4332,37 +4332,37 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>1712772</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1712772</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>AL_36629103</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -4379,37 +4379,37 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>1712771</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>1712771</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>AL_36629073</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -4426,37 +4426,37 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>1712770</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>1712770</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>AL_36629085</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -4473,37 +4473,37 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>1712769</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1712769</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>AL_36629082</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -4520,37 +4520,37 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>1712768</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>1712768</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>AL_36629079</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -4567,37 +4567,37 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>1712767</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>1712767</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>AL_36629088</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -4614,37 +4614,37 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>AL_36629076</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -4661,37 +4661,37 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>1712765</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>1712765</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>AL_36629064</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -4708,37 +4708,37 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>1712764</t>
+          <t>1213460</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>1712764</t>
+          <t>1213460</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>AL_36629070</t>
+          <t>2118692</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0554</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -4755,37 +4755,37 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>1712763</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>1712763</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>AL_36629067</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -4802,37 +4802,37 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>1712762</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>1712762</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>AL_36629055</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -4849,37 +4849,37 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>1712761</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>1712761</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>AL_36629061</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -4896,37 +4896,37 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>1712760</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>1712760</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>AL_36629058</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -4943,37 +4943,37 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>1712759</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>1712759</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>AL_36629031</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -4990,37 +4990,37 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>1712758</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>1712758</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>AL_36629037</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5037,37 +5037,37 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>1712757</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>1712757</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>AL_36629021</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5084,37 +5084,37 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>1712756</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>1712756</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>AL_36629040</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5131,37 +5131,37 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>1712755</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>1712755</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>AL_36629006</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -5178,37 +5178,37 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>1712754</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>1712754</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>AL_36629034</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -5225,37 +5225,37 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>1712753</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>1712753</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>AL_36629018</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -5272,37 +5272,37 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>1712752</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>1712752</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>AL_36629043</t>
+          <t>2130202</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-25 0213</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -5319,37 +5319,37 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>1712751</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>1712751</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>AL_36629015</t>
+          <t>2216095</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-22 0148</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -5366,37 +5366,37 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>1712750</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>1712750</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>AL_36629003</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -5413,37 +5413,37 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>1712749</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>1712749</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>AL_36629052</t>
+          <t>2211543</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-21 2220</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -5460,37 +5460,37 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>1712748</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>1712748</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>AL_36629046</t>
+          <t>2211489</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-21 0919</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -5507,37 +5507,37 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>1712747</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>1712747</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>AL_36629009</t>
+          <t>2095869</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Aug-19 0146</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -5546,2544 +5546,6 @@
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>1712746</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>1712746</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>AL_36629024</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>armazenamento-lote</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 0759</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 0759</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>1712745</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>1712745</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>AL_36629027</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>armazenamento-lote</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 0759</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 0759</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>1712744</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>1712744</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>AL_36629049</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>armazenamento-lote</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 0759</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 0759</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>1712743</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>1712743</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>AL_36629000</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>armazenamento-lote</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 0759</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 1549</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>995738</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>995738</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>2021736</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1049</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>2081638</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1049</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>1675920</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>1675920</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>36402427</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>embarque-desembarque-navios</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-30 1120</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 1552</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-05 1552</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>1671658</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>1671658</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>36371187</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>embarque-desembarque-navios</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-30 0147</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>1671632</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>1671632</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>36371098</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>embarque-desembarque-navios</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-30 0143</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>1671611</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>1671611</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>36371032</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>embarque-desembarque-navios</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-30 0139</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>1671527</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>1671527</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>36370796</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>embarque-desembarque-navios</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-30 0130</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>1671513</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>1671513</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>36370762</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>embarque-desembarque-navios</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-30 0129</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1747</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-01 1748</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>1461360</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>1461360</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>2211058</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-26 0146</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>1472148</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>1472148</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>2210694</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-26 0132</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>1469269</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>1469269</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>2238639</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-24 1732</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>1469557</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>1469557</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>2238668</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-24 1732</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>1461547</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>1461547</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>2211031</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-24 1731</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>1469831</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>1469831</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>2238644</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-24 1731</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>1475031</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>1475031</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>2239463</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-24 1730</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>1469673</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>1469673</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>2238690</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-24 1730</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>1461139</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>1461139</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>2211059</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-21 1946</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>1461135</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>1461135</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>2211065</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-21 1946</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>1461327</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>1461327</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>2211075</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-21 1901</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>1469610</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>1469610</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>2238613</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-21 1602</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>1469585</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>1469585</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>2238630</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-21 1547</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>1469580</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>1469580</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>2238608</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-21 1545</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>1461113</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>1461113</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>2211071</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-16 0146</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>1460995</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>1460995</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>2211119</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>26-Sep-06 0746</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>2163612</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0710</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>2190259</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0621</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>1329954</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>1329954</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>2134524</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0616</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>1331904</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>1331904</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>2160058</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0615</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>1261550</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>1261550</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>2114903</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0557</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>2118299</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0556</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>1213607</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>1213607</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>2079627</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0555</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>1214064</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>1214064</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>2081539</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0555</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>1213460</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>1213460</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>2118692</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0554</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>2193252</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0535</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>1192446</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>1192446</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>2091350</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0534</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>1330785</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>1330785</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>2139702</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0531</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>2164666</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0530</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>2118702</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0509</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>1293782</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>1293782</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>2140753</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0458</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>2134235</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0457</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>2103956</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0436</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>2081236</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0408</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>2114825</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0407</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>2199030</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0229</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>1282347</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>1282347</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>2130202</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0213</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>1409819</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>1409819</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>2216095</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-22 0148</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>2216108</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-22 0045</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>1408476</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>1408476</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>2211543</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-21 2220</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>2211489</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-21 0919</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>2095869</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-19 0146</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -178,18 +178,18 @@
     <col min="1" max="1" width="33.84375" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
     <col min="3" max="3" width="14.8203125" customWidth="true"/>
-    <col min="4" max="4" width="23.0078125" customWidth="true"/>
+    <col min="4" max="4" width="27.7734375" customWidth="true"/>
     <col min="5" max="5" width="11.01953125" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="16.40234375" customWidth="true"/>
-    <col min="8" max="8" width="14.92578125" customWidth="true"/>
+    <col min="8" max="8" width="16.40234375" customWidth="true"/>
     <col min="9" max="9" width="11.37890625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 113 item(s) at 2026-10-05</t>
+          <t>Displaying 195 item(s) at 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -243,17 +243,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 1800</t>
+          <t>26-Oct-06 0745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,42 +666,42 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1712819</t>
+          <t>1721133</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1712819</t>
+          <t>1721133</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>AL_36629175</t>
+          <t>A_587389</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0733</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -713,42 +713,42 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1712818</t>
+          <t>1720953</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1712818</t>
+          <t>1720953</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AL_36629211</t>
+          <t>PS_426213</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0637</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0638</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1712817</t>
+          <t>1720946</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1712817</t>
+          <t>1720946</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AL_36629205</t>
+          <t>PS_426216</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0635</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0636</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -807,42 +807,42 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1712816</t>
+          <t>1720936</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1712816</t>
+          <t>1720936</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>AL_36629190</t>
+          <t>PS_426214</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0634</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -854,42 +854,42 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1712815</t>
+          <t>1720933</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1712815</t>
+          <t>1720933</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AL_36629181</t>
+          <t>PE_426233</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0633</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -901,42 +901,42 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1712814</t>
+          <t>1720931</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1712814</t>
+          <t>1720931</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>AL_36629220</t>
+          <t>PE_426232</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0633</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -948,42 +948,42 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1712813</t>
+          <t>1720929</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1712813</t>
+          <t>1720929</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>AL_36629184</t>
+          <t>PS_426219</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0632</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0633</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -995,42 +995,42 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1712812</t>
+          <t>1720927</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1712812</t>
+          <t>1720927</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>AL_36629187</t>
+          <t>PE_426231</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0631</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0631</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0633</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1042,42 +1042,42 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1712811</t>
+          <t>1720925</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1712811</t>
+          <t>1720925</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>AL_36629226</t>
+          <t>PS_426211</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0631</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0633</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1089,42 +1089,42 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1712810</t>
+          <t>1720864</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1712810</t>
+          <t>1720864</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>AL_36629223</t>
+          <t>PS_426204</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0618</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0618</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0619</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1136,42 +1136,42 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1712809</t>
+          <t>1720862</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1712809</t>
+          <t>1720862</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>AL_36629199</t>
+          <t>PE_426222</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0618</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0618</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0619</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1712808</t>
+          <t>1720858</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1712808</t>
+          <t>1720858</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>AL_36629217</t>
+          <t>PE_426221</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0617</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0617</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0619</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1230,42 +1230,42 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1712807</t>
+          <t>1720854</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1712807</t>
+          <t>1720854</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>AL_36629202</t>
+          <t>PS_426212</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0615</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0615</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0616</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1277,42 +1277,42 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1712806</t>
+          <t>1720851</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1712806</t>
+          <t>1720851</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>AL_36629229</t>
+          <t>PE_426220</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0615</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0615</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0616</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1324,42 +1324,42 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1712805</t>
+          <t>1720846</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1712805</t>
+          <t>1720846</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>AL_36629233</t>
+          <t>PS_426209</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0613</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0613</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0614</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1371,42 +1371,42 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1712804</t>
+          <t>1720842</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1712804</t>
+          <t>1720842</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>AL_36629178</t>
+          <t>PE_426219</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0613</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0613</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0614</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1418,42 +1418,42 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1712802</t>
+          <t>1720837</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1712802</t>
+          <t>1720837</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>AL_36629214</t>
+          <t>PE_426218</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0612</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0612</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 0613</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1465,37 +1465,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1712803</t>
+          <t>1720811</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1712803</t>
+          <t>1720811</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>AL_36629196</t>
+          <t>2407852</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0603</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1512,37 +1512,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1712801</t>
+          <t>1720781</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1712801</t>
+          <t>1720781</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>AL_36629208</t>
+          <t>2411187</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0553</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1559,37 +1559,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1712800</t>
+          <t>1720725</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1712800</t>
+          <t>1720725</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>AL_36629193</t>
+          <t>2391347</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0531</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1606,37 +1606,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1712799</t>
+          <t>1720713</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1712799</t>
+          <t>1720713</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>AL_36629169</t>
+          <t>2408684</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0526</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1653,37 +1653,37 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1712798</t>
+          <t>1720706</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1712798</t>
+          <t>1720706</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>AL_36629166</t>
+          <t>2401115</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0524</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1700,37 +1700,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1712796</t>
+          <t>1720528</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1712796</t>
+          <t>1720528</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>AL_36629172</t>
+          <t>2391762</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0415</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1747,37 +1747,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1712797</t>
+          <t>1720510</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1712797</t>
+          <t>1720510</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>AL_36629157</t>
+          <t>2407824</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0411</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,37 +1794,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1712795</t>
+          <t>1720486</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1712795</t>
+          <t>1720486</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>AL_36629163</t>
+          <t>2391865</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0404</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1841,37 +1841,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1712794</t>
+          <t>1720420</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1712794</t>
+          <t>1720420</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>AL_36629148</t>
+          <t>2411032</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0352</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1888,37 +1888,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1712793</t>
+          <t>1720417</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1712793</t>
+          <t>1720417</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>AL_36629160</t>
+          <t>2411033</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0352</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1935,37 +1935,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1712792</t>
+          <t>1720308</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1712792</t>
+          <t>1720308</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>AL_36629151</t>
+          <t>2391862</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0314</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1982,37 +1982,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1712791</t>
+          <t>1720174</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1712791</t>
+          <t>1720174</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>AL_36629154</t>
+          <t>2407805</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0229</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2029,37 +2029,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1712790</t>
+          <t>1720165</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1712790</t>
+          <t>1720165</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>AL_36629124</t>
+          <t>2407806</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0227</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2076,37 +2076,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1712789</t>
+          <t>1720157</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1712789</t>
+          <t>1720157</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>AL_36629145</t>
+          <t>2411028</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0225</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2123,37 +2123,37 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1712788</t>
+          <t>1720028</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1712788</t>
+          <t>1720028</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>AL_36629130</t>
+          <t>2391707</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0202</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2170,37 +2170,37 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1712787</t>
+          <t>1719945</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1712787</t>
+          <t>1719945</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>AL_36629142</t>
+          <t>2391705</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0145</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2217,37 +2217,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1712786</t>
+          <t>1719935</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1712786</t>
+          <t>1719935</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AL_36629136</t>
+          <t>2402816</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0144</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2264,37 +2264,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1712785</t>
+          <t>1719805</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1712785</t>
+          <t>1719805</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>AL_36629127</t>
+          <t>2391687</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0105</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2311,37 +2311,37 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1712784</t>
+          <t>1719783</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1712784</t>
+          <t>1719783</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>AL_36629139</t>
+          <t>2401200</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0055</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2358,37 +2358,37 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1712783</t>
+          <t>1719782</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1712783</t>
+          <t>1719782</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>AL_36629112</t>
+          <t>2391850</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0053</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2405,37 +2405,37 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1712782</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1712782</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>AL_36629133</t>
+          <t>2391854</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0051</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2452,37 +2452,37 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1712780</t>
+          <t>1719749</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1712780</t>
+          <t>1719749</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>AL_36629118</t>
+          <t>2405502</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0044</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2499,37 +2499,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1712781</t>
+          <t>1719676</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1712781</t>
+          <t>1719676</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>AL_36629109</t>
+          <t>2410998</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0028</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2546,37 +2546,37 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1712779</t>
+          <t>1719655</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1712779</t>
+          <t>1719655</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>AL_36629121</t>
+          <t>2401117</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0023</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2593,37 +2593,37 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1712778</t>
+          <t>1719587</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1712778</t>
+          <t>1719587</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>AL_36629115</t>
+          <t>2391701</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-06 0008</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2640,37 +2640,37 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1712776</t>
+          <t>1719508</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1712776</t>
+          <t>1719508</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>AL_36629100</t>
+          <t>2391470</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2352</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2687,37 +2687,37 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1712777</t>
+          <t>1719482</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1712777</t>
+          <t>1719482</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>AL_36629094</t>
+          <t>2410978</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2346</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2734,37 +2734,37 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1712775</t>
+          <t>1719457</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1712775</t>
+          <t>1719457</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>AL_36629106</t>
+          <t>2401244</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2341</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2781,37 +2781,37 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1712773</t>
+          <t>1719414</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1712773</t>
+          <t>1719414</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>AL_36629097</t>
+          <t>2401243</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2332</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2828,37 +2828,37 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1712774</t>
+          <t>1719338</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1712774</t>
+          <t>1719338</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>AL_36629091</t>
+          <t>2401238</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2308</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2875,37 +2875,37 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1712772</t>
+          <t>1719336</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1712772</t>
+          <t>1719336</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>AL_36629103</t>
+          <t>2401237</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2308</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2922,37 +2922,37 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1712771</t>
+          <t>1719279</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1712771</t>
+          <t>1719279</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>AL_36629073</t>
+          <t>2410977</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2254</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2969,37 +2969,37 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1712770</t>
+          <t>1719200</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1712770</t>
+          <t>1719200</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>AL_36629085</t>
+          <t>2361658</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2229</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3016,37 +3016,37 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1712769</t>
+          <t>1719058</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1712769</t>
+          <t>1719058</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>AL_36629082</t>
+          <t>2411000</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2152</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3063,37 +3063,37 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1712768</t>
+          <t>1718990</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1712768</t>
+          <t>1718990</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>AL_36629079</t>
+          <t>2411075</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2140</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3110,37 +3110,37 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1712767</t>
+          <t>1718977</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1712767</t>
+          <t>1718977</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>AL_36629088</t>
+          <t>2391498</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2138</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3157,37 +3157,37 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1718968</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1718968</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>AL_36629076</t>
+          <t>2362011</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2136</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3204,37 +3204,37 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1712765</t>
+          <t>1718920</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1712765</t>
+          <t>1718920</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>AL_36629064</t>
+          <t>2408699</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2127</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3251,37 +3251,37 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1712764</t>
+          <t>1718644</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1712764</t>
+          <t>1718644</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>AL_36629070</t>
+          <t>2391538</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2107</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3298,37 +3298,37 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1712763</t>
+          <t>1718604</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1712763</t>
+          <t>1718604</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>AL_36629067</t>
+          <t>2361498</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2100</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3345,37 +3345,37 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1712762</t>
+          <t>1718465</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1712762</t>
+          <t>1718465</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>AL_36629055</t>
+          <t>2361669</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2038</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3392,37 +3392,37 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1712761</t>
+          <t>1718453</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1712761</t>
+          <t>1718453</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>AL_36629061</t>
+          <t>2391535</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2036</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3439,37 +3439,37 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1712760</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1712760</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>AL_36629058</t>
+          <t>2411072</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2034</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3486,37 +3486,37 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1712759</t>
+          <t>1718430</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1712759</t>
+          <t>1718430</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>AL_36629031</t>
+          <t>2408708</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2033</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3533,37 +3533,37 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>1712758</t>
+          <t>1718385</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1712758</t>
+          <t>1718385</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>AL_36629037</t>
+          <t>2365092</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2028</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3580,37 +3580,37 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>1712757</t>
+          <t>1718384</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1712757</t>
+          <t>1718384</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>AL_36629021</t>
+          <t>2391536</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2028</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3627,37 +3627,37 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1712756</t>
+          <t>1718361</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>1712756</t>
+          <t>1718361</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>AL_36629040</t>
+          <t>2391358</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2025</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3674,37 +3674,37 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1712755</t>
+          <t>1718334</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1712755</t>
+          <t>1718334</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>AL_36629006</t>
+          <t>2396173</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2022</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3721,37 +3721,37 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1712754</t>
+          <t>1718307</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1712754</t>
+          <t>1718307</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>AL_36629034</t>
+          <t>2391485</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2018</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3768,37 +3768,37 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1712753</t>
+          <t>1718201</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1712753</t>
+          <t>1718201</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>AL_36629018</t>
+          <t>2397741</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 2002</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1712752</t>
+          <t>1717945</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1712752</t>
+          <t>1717945</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>AL_36629043</t>
+          <t>AL_36698129</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1930</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1930</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3862,17 +3862,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1712751</t>
+          <t>1717944</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1712751</t>
+          <t>1717944</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>AL_36629015</t>
+          <t>AL_36698132</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1930</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1930</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3909,37 +3909,37 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1712750</t>
+          <t>1717852</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1712750</t>
+          <t>1717852</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>AL_36629003</t>
+          <t>2410942</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1915</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -3956,37 +3956,37 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1712749</t>
+          <t>1717785</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1712749</t>
+          <t>1717785</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>AL_36629052</t>
+          <t>2411151</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1900</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4003,37 +4003,37 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1712748</t>
+          <t>1717773</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>1712748</t>
+          <t>1717773</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>AL_36629046</t>
+          <t>2411147</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1857</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4050,17 +4050,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>1712747</t>
+          <t>1717755</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1712747</t>
+          <t>1717755</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>AL_36629009</t>
+          <t>AL_36697075</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1855</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1855</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4097,17 +4097,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1712746</t>
+          <t>1717754</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1712746</t>
+          <t>1717754</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>AL_36629024</t>
+          <t>AL_36697072</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1855</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1855</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4144,37 +4144,37 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1712745</t>
+          <t>1717751</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>1712745</t>
+          <t>1717751</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>AL_36629027</t>
+          <t>2390110</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1854</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4191,37 +4191,37 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>1712744</t>
+          <t>1717648</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>1712744</t>
+          <t>1717648</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>AL_36629049</t>
+          <t>2411140</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t>26-Oct-05 1843</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-05 0759</t>
+          <t/>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1717645</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1717645</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>2396172</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-01 1049</t>
+          <t>26-Oct-05 1842</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4285,17 +4285,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1717613</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1717613</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>2411132</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-01 1049</t>
+          <t>26-Oct-05 1838</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4332,17 +4332,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1717610</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1717610</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>2411139</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-05 1837</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4379,17 +4379,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1717572</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1717572</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2411134</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Oct-05 1832</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4426,17 +4426,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1717563</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1717563</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2411138</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Oct-05 1831</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -4473,17 +4473,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1717550</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1717550</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2391321</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Oct-05 1828</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -4520,37 +4520,37 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1712819</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1712819</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>AL_36629175</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -4567,37 +4567,37 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1712818</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1712818</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>AL_36629211</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -4614,37 +4614,37 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1712817</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1712817</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>AL_36629205</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -4661,37 +4661,37 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1712816</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1712816</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>AL_36629190</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -4708,37 +4708,37 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>1213460</t>
+          <t>1712815</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>1213460</t>
+          <t>1712815</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>2118692</t>
+          <t>AL_36629181</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0554</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -4755,37 +4755,37 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1712814</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1712814</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>AL_36629220</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -4802,37 +4802,37 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1712813</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1712813</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>AL_36629184</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -4849,37 +4849,37 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1712812</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1712812</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>AL_36629187</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -4896,37 +4896,37 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1712811</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1712811</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>AL_36629226</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -4943,37 +4943,37 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1712810</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1712810</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>AL_36629223</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -4990,37 +4990,37 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1712809</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1712809</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>AL_36629199</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5037,37 +5037,37 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1712808</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1712808</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>AL_36629217</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5084,37 +5084,37 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1712807</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1712807</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>AL_36629202</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5131,37 +5131,37 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1712806</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1712806</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>AL_36629229</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -5178,37 +5178,37 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1712805</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1712805</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>AL_36629233</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -5225,37 +5225,37 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1712804</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1712804</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>AL_36629178</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -5272,37 +5272,37 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1712802</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1712802</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>2130202</t>
+          <t>AL_36629214</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0213</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -5319,37 +5319,37 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1712803</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1712803</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>AL_36629196</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -5366,37 +5366,37 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1712801</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1712801</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>AL_36629208</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -5413,37 +5413,37 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1712800</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1712800</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>AL_36629193</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -5460,37 +5460,37 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1712799</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1712799</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>2211489</t>
+          <t>AL_36629169</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0919</t>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-05 0759</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -5507,45 +5507,3899 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>1712798</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1712798</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629166</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>1712796</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1712796</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629172</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>1712797</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1712797</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629157</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>1712795</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1712795</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629163</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>1712794</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1712794</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629148</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>1712793</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1712793</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629160</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>1712792</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1712792</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629151</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>1712791</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1712791</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629154</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>1712790</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1712790</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629124</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>1712789</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1712789</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629145</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>1712788</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1712788</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629130</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>1712787</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1712787</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629142</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>1712786</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1712786</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629136</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>1712785</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1712785</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629127</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>1712784</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1712784</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629139</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>1712783</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1712783</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629112</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>1712782</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1712782</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629133</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>1712780</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1712780</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629118</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>1712781</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1712781</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629109</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>1712779</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1712779</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629121</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>1712778</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1712778</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629115</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>1712776</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1712776</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629100</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>1712777</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1712777</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629094</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>1712775</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1712775</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629106</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>1712773</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1712773</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629097</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>1712774</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1712774</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629091</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>1712772</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1712772</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629103</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>1712771</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1712771</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629073</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>1712770</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1712770</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629085</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>1712769</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1712769</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629082</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>1712768</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1712768</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629079</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>1712767</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1712767</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629088</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>1712766</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1712766</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629076</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>1712765</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1712765</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629064</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>1712764</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1712764</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629070</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>1712763</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1712763</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629067</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>1712762</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1712762</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629055</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>1712761</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1712761</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629061</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>1712760</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1712760</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629058</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>1712759</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1712759</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629031</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>1712758</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1712758</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629037</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>1712757</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1712757</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629021</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>1712756</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1712756</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629040</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>1712755</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1712755</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629006</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>1712754</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1712754</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629034</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>1712753</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1712753</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629018</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>1712752</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1712752</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629043</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>1712751</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1712751</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629015</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>1712750</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1712750</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629003</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>1712749</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1712749</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629052</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>1712748</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1712748</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629046</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>1712747</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1712747</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629009</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>1712746</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1712746</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629024</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>1712745</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1712745</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629027</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>1712744</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>1712744</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>AL_36629049</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-05 0759</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>995738</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>995738</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>2021736</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-01 1049</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>2081638</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-01 1049</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>2163612</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0710</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>2190259</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0621</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>2134524</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0616</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>2160058</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0615</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>2114903</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0557</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>2118299</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0556</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>1213607</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>1213607</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>2079627</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0555</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>1214064</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>1214064</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>2081539</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0555</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>1213460</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>1213460</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>2118692</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0554</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>2193252</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0535</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>1192446</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>1192446</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>2091350</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0534</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>1330785</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>1330785</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>2139702</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0531</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>1343646</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>1343646</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>2164666</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0530</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>1213221</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>1213221</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>2118702</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0509</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>1293782</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>1293782</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>2140753</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0458</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>2134235</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0457</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>2103956</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0436</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>2081236</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0408</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>2114825</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0407</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>2199030</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0229</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>1282347</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>1282347</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>2130202</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0213</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>1409819</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>1409819</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>2216095</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-22 0148</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>2216108</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-22 0045</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>1408476</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>1408476</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>2211543</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 2220</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>2211489</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 0919</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>2095869</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>26-Aug-19 0146</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 54 item(s) at 2026-10-06</t>
+          <t>Displaying 38 item(s) at 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -243,22 +243,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1731126</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1731126</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>A_591910</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -278,7 +278,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-07 0921</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0915</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1700</t>
+          <t>26-Oct-07 0915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,22 +666,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36732054</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t>26-Oct-07 0915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -713,22 +713,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1723640</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1723640</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2411214</t>
+          <t>36772991</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1400</t>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-07 0100</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1723553</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1723553</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2387832</t>
+          <t>2021736</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1347</t>
+          <t>26-Oct-06 1744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1723385</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1723385</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2405503</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1320</t>
+          <t>26-Oct-06 1744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,22 +854,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1723357</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1723357</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2401144</t>
+          <t>36732054</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1314</t>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1723316</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1723316</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2408695</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1304</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1722910</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1722910</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2391355</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1145</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1722798</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1722798</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2411185</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1133</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1722731</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1722731</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2411121</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1129</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1722430</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1722430</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2411205</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1056</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1722402</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1722402</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2391457</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1052</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2394462</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1040</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1722164</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1722164</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2391928</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1020</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1722098</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1722098</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2411018</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1012</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1722072</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1722072</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2401142</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1009</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1722052</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1722052</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2401186</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1005</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1721703</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1721703</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2391635</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 0914</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-01 1049</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-01 1049</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>2130202</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Aug-25 0213</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>2216095</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Aug-22 0148</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1213460</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1213460</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2118692</t>
+          <t>2211543</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0554</t>
+          <t>26-Aug-21 2220</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2211489</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Aug-21 0919</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>2095869</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Aug-19 0146</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2068,711 +2068,6 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>1330785</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>1330785</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2139702</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0531</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>2164666</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0530</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2118702</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0509</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>1293782</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>1293782</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>2140753</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0458</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>2134235</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0457</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>2103956</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0436</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>2081236</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0408</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>2114825</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0407</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>2199030</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0229</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>1282347</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>1282347</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>2130202</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0213</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>1409819</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>1409819</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>2216095</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-22 0148</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>2216108</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-22 0045</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>1408476</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>1408476</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>2211543</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-21 2220</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>2211489</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-21 0919</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>2095869</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-19 0146</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -177,7 +177,7 @@
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
-    <col min="3" max="3" width="11.3828125" customWidth="true"/>
+    <col min="3" max="3" width="12.6171875" customWidth="true"/>
     <col min="4" max="4" width="32.30078125" customWidth="true"/>
     <col min="5" max="5" width="7.8359375" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 38 item(s) at 2026-10-07</t>
+          <t>Displaying 40 item(s) at 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -243,22 +243,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1731126</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1731126</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>A_591910</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0921</t>
+          <t>26-Oct-08 1101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -278,7 +278,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0921</t>
+          <t/>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0916</t>
+          <t>26-Oct-08 1101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0916</t>
+          <t>26-Oct-08 1100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0915</t>
+          <t>26-Oct-08 1100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0915</t>
+          <t>26-Oct-08 1100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0915</t>
+          <t>26-Oct-08 1100</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0915</t>
+          <t>26-Oct-08 1100</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0915</t>
+          <t>26-Oct-08 1100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0915</t>
+          <t>26-Oct-08 1100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,22 +666,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1739893</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1739893</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>PE_428078</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0915</t>
+          <t>26-Oct-08 1048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-08 1048</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-08 1048</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -713,22 +713,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>1734127</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>1734127</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>36772991</t>
+          <t>A_592392</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t>26-Oct-07 1536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t/>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0100</t>
+          <t>26-Oct-07 1626</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>36772991</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1744</t>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-07 0100</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>2021736</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -854,22 +854,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36732054</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t>26-Oct-06 1744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -901,22 +901,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>36732054</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2130202</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0213</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>2130202</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Aug-25 0213</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>2216095</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Aug-22 0148</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2211489</t>
+          <t>2211543</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0919</t>
+          <t>26-Aug-21 2220</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2029,45 +2029,92 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2211489</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 0919</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>2095869</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>26-Aug-19 0146</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -177,7 +177,7 @@
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
-    <col min="3" max="3" width="12.6171875" customWidth="true"/>
+    <col min="3" max="3" width="11.3828125" customWidth="true"/>
     <col min="4" max="4" width="32.30078125" customWidth="true"/>
     <col min="5" max="5" width="7.8359375" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 40 item(s) at 2026-10-08</t>
+          <t>Displaying 41 item(s) at 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -243,17 +243,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1101</t>
+          <t>26-Oct-08 1731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1101</t>
+          <t>26-Oct-08 1731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1100</t>
+          <t>26-Oct-08 1730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1100</t>
+          <t>26-Oct-08 1730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1100</t>
+          <t>26-Oct-08 1730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1100</t>
+          <t>26-Oct-08 1730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1100</t>
+          <t>26-Oct-08 1730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1100</t>
+          <t>26-Oct-08 1730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1100</t>
+          <t>26-Oct-08 1730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,22 +666,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1739893</t>
+          <t>1742961</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1739893</t>
+          <t>1742961</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PE_428078</t>
+          <t>A_593309</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1048</t>
+          <t>26-Oct-08 1654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1048</t>
+          <t/>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1048</t>
+          <t>26-Oct-08 1655</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1734127</t>
+          <t>1741599</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1734127</t>
+          <t>1741599</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A_592392</t>
+          <t>A_592793</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 1536</t>
+          <t>26-Oct-08 1444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 1626</t>
+          <t>26-Oct-08 1444</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>1734127</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>1734127</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36772991</t>
+          <t>A_592392</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t>26-Oct-07 1536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t/>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0100</t>
+          <t>26-Oct-07 1626</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -807,22 +807,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>36772991</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1744</t>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-07 0100</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>2021736</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -901,22 +901,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>36732054</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t>26-Oct-06 1744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -948,22 +948,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>36732054</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2130202</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0213</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1282347</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>2130202</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Aug-25 0213</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>2216095</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Aug-22 0148</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2211489</t>
+          <t>2211543</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0919</t>
+          <t>26-Aug-21 2220</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2076,45 +2076,92 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2211489</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 0919</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>2095869</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>26-Aug-19 0146</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 41 item(s) at 2026-10-08</t>
+          <t>Displaying 39 item(s) at 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -243,17 +243,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1731</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1731</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1730</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,22 +384,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1748518</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1748518</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>A_592311</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1730</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -419,7 +419,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1730</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1730</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1730</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1730</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1730</t>
+          <t>26-Oct-09 0930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,22 +666,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1742961</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1742961</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>A_593309</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1654</t>
+          <t>26-Oct-09 0915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1655</t>
+          <t/>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1741599</t>
+          <t>1734127</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1741599</t>
+          <t>1734127</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A_592793</t>
+          <t>A_592392</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1444</t>
+          <t>26-Oct-07 1536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-08 1444</t>
+          <t>26-Oct-07 1626</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1734127</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1734127</t>
+          <t>1728391</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>A_592392</t>
+          <t>36772991</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 1536</t>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 2359</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 1626</t>
+          <t>26-Oct-07 0100</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -807,22 +807,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36772991</t>
+          <t>2021736</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t>26-Oct-06 1744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t/>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0100</t>
+          <t/>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -901,22 +901,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1723914</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>36732054</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1744</t>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-06 1440</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -948,22 +948,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36732054</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>2216095</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Aug-22 0148</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1282347</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2130202</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0213</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>2211543</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Aug-21 2220</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>2211489</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Aug-21 0919</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>2095869</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Aug-19 0146</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2068,100 +2068,6 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2211489</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-21 0919</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>2095869</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-19 0146</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -177,19 +177,19 @@
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
-    <col min="3" max="3" width="11.3828125" customWidth="true"/>
-    <col min="4" max="4" width="32.30078125" customWidth="true"/>
-    <col min="5" max="5" width="7.8359375" customWidth="true"/>
+    <col min="3" max="3" width="12.6171875" customWidth="true"/>
+    <col min="4" max="4" width="27.7734375" customWidth="true"/>
+    <col min="5" max="5" width="11.01953125" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="16.40234375" customWidth="true"/>
     <col min="8" max="8" width="16.40234375" customWidth="true"/>
-    <col min="9" max="9" width="11.37890625" customWidth="true"/>
+    <col min="9" max="9" width="41.48046875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 39 item(s) at 2026-10-09</t>
+          <t>Displaying 62 item(s) at 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -243,22 +243,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1770335</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1770335</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>A_595658</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -278,7 +278,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-13 0855</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,22 +384,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1748518</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1748518</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>A_592311</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -419,7 +419,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t/>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0930</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0915</t>
+          <t>26-Oct-13 0845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,42 +713,42 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1734127</t>
+          <t>1765876</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1734127</t>
+          <t>1765876</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>A_592392</t>
+          <t>PS_430376</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 1536</t>
+          <t>26-Oct-12 0457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0457</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 1626</t>
+          <t/>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>1765861</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1728391</t>
+          <t>1765861</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36772991</t>
+          <t>PE_430377</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t>26-Oct-12 0453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 2359</t>
+          <t>26-Oct-12 0453</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-07 0100</t>
+          <t/>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -807,37 +807,37 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1765847</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1765847</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>PE_430376</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1744</t>
+          <t>26-Oct-12 0448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0448</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -854,37 +854,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1765608</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1765608</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>PE_430375</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1744</t>
+          <t>26-Oct-12 0334</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0334</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -901,42 +901,42 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1765189</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1723914</t>
+          <t>1765189</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>36732054</t>
+          <t>PS_430374</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>embarque-desembarque-navios</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t>26-Oct-12 0212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t>26-Oct-12 0212</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-06 1440</t>
+          <t/>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -948,37 +948,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1765159</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1765159</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>PS_430373</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-12 0205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0205</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -995,37 +995,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1765120</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1765120</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>PE_430374</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Oct-12 0151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0151</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1042,37 +1042,37 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1765100</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1765100</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>PE_430373</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Oct-12 0147</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0147</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1089,37 +1089,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1765021</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1765021</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>PS_430300</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Oct-12 0110</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0110</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1136,37 +1136,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1765011</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1765011</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>PS_430372</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Oct-12 0104</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-12 0104</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1183,37 +1183,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1761573</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1761573</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>PE_430112</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Oct-11 0452</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0452</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1230,37 +1230,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1761428</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1761428</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>PS_430111</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-11 0306</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0306</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1277,37 +1277,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1761409</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1761409</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>PS_430110</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-11 0256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0256</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1324,37 +1324,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1761400</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1761400</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>PE_430111</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Oct-11 0252</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0252</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1371,37 +1371,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1761397</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1761397</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>PE_430110</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Oct-11 0248</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0248</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1418,37 +1418,37 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1761318</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1761318</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>PS_430109</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Oct-11 0207</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0207</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1465,37 +1465,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1761303</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1761303</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>PS_430108</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Oct-11 0203</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0203</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1512,37 +1512,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1761293</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1761293</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>PE_430109</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Oct-11 0157</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0157</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1559,37 +1559,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1761289</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1761289</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>PE_430108</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Oct-11 0154</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-11 0154</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1606,37 +1606,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1761009</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1761009</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>PE_430092</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Oct-10 2246</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 2246</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1653,37 +1653,37 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1761007</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1761007</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>PE_430091</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Oct-10 2245</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 2245</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1700,37 +1700,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1761005</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1761005</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>PE_430090</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Oct-10 2245</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 2245</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1747,37 +1747,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1761003</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1761003</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>PE_430089</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Oct-10 2245</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 2245</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,22 +1794,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1758532</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1758532</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>PE_429796</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Oct-10 1432</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 1432</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 1433</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1841,37 +1841,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1754443</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1754443</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>PE_429467</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Oct-10 0112</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 0112</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1888,37 +1888,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1754440</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1754440</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>PS_429457</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Oct-10 0111</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 0111</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1935,37 +1935,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1754437</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1754437</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>PE_429466</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Oct-10 0111</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-10 0111</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2211489</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0919</t>
+          <t>26-Oct-09 1745</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2029,45 +2029,1173 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>995738</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>995738</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2021736</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-09 0948</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>8353b3aa-6acc-4a5a-a61a-52763cfefeac</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2163612</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0710</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2190259</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0621</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2134524</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0616</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2160058</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0615</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2114903</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0557</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2118299</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0556</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>1213607</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1213607</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2079627</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0555</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>1214064</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1214064</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2081539</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0555</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2193252</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0535</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>1192446</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1192446</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2091350</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0534</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>1330785</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1330785</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2139702</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0531</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>1343646</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1343646</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2164666</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0530</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>1213221</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1213221</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2118702</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0509</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>1293782</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1293782</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2140753</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0458</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2134235</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0457</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2103956</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0436</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2081236</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0408</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2114825</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0407</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2199030</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0229</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>1409819</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1409819</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2216095</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-22 0148</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2216108</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-22 0045</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>1408476</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1408476</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2211543</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 2220</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2211489</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 0919</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>2095869</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>26-Aug-19 0146</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -177,19 +177,19 @@
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
-    <col min="3" max="3" width="12.6171875" customWidth="true"/>
-    <col min="4" max="4" width="27.7734375" customWidth="true"/>
-    <col min="5" max="5" width="11.01953125" customWidth="true"/>
+    <col min="3" max="3" width="11.3828125" customWidth="true"/>
+    <col min="4" max="4" width="23.0078125" customWidth="true"/>
+    <col min="5" max="5" width="7.8359375" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
-    <col min="7" max="7" width="16.40234375" customWidth="true"/>
-    <col min="8" max="8" width="16.40234375" customWidth="true"/>
+    <col min="7" max="7" width="12.484375" customWidth="true"/>
+    <col min="8" max="8" width="14.92578125" customWidth="true"/>
     <col min="9" max="9" width="41.48046875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 62 item(s) at 2026-10-13</t>
+          <t>Displaying 35 item(s) at 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -243,22 +243,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1770335</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1770335</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>A_595658</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0855</t>
+          <t>26-Oct-13 1716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -278,7 +278,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0855</t>
+          <t/>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1715</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-13 1715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 0845</t>
+          <t>26-Oct-09 1745</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,37 +713,37 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1765876</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1765876</t>
+          <t>995738</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PS_430376</t>
+          <t>2021736</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0457</t>
+          <t>26-Oct-09 0948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0457</t>
+          <t/>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -753,44 +753,44 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>8353b3aa-6acc-4a5a-a61a-52763cfefeac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1765861</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1765861</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>PE_430377</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0453</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0453</t>
+          <t/>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -807,37 +807,37 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1765847</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1765847</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PE_430376</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0448</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0448</t>
+          <t/>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -854,37 +854,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1765608</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1765608</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PE_430375</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0334</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0334</t>
+          <t/>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -901,37 +901,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1765189</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1765189</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PS_430374</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0212</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0212</t>
+          <t/>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -948,37 +948,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1765159</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1765159</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PS_430373</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0205</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0205</t>
+          <t/>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -995,37 +995,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1765120</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1765120</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>PE_430374</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0151</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0151</t>
+          <t/>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1042,37 +1042,37 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1765100</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1765100</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>PE_430373</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0147</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0147</t>
+          <t/>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1089,37 +1089,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1765021</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1765021</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>PS_430300</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0110</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0110</t>
+          <t/>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1136,37 +1136,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1765011</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1765011</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>PS_430372</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0104</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-12 0104</t>
+          <t/>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1183,37 +1183,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1761573</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1761573</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>PE_430112</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0452</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0452</t>
+          <t/>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1230,37 +1230,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1761428</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1761428</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PS_430111</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0306</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0306</t>
+          <t/>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1277,37 +1277,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1761409</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1761409</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>PS_430110</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0256</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0256</t>
+          <t/>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1324,37 +1324,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1761400</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1761400</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>PE_430111</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0252</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0252</t>
+          <t/>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1371,37 +1371,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1761397</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1761397</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>PE_430110</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0248</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0248</t>
+          <t/>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1418,37 +1418,37 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1761318</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1761318</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>PS_430109</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0207</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0207</t>
+          <t/>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1465,37 +1465,37 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1761303</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1761303</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PS_430108</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0203</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0203</t>
+          <t/>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1512,37 +1512,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1761293</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1761293</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>PE_430109</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0157</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0157</t>
+          <t/>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1559,37 +1559,37 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1761289</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1761289</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>PE_430108</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0154</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-11 0154</t>
+          <t/>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1606,37 +1606,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1761009</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1761009</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>PE_430092</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2246</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2246</t>
+          <t/>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1653,37 +1653,37 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1761007</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1761007</t>
+          <t>1409819</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PE_430091</t>
+          <t>2216095</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2245</t>
+          <t>26-Aug-22 0148</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2245</t>
+          <t/>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1700,37 +1700,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1761005</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1761005</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PE_430090</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2245</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2245</t>
+          <t/>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1747,37 +1747,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1761003</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1761003</t>
+          <t>1408476</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>PE_430089</t>
+          <t>2211543</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2245</t>
+          <t>26-Aug-21 2220</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 2245</t>
+          <t/>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,22 +1794,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1758532</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1758532</t>
+          <t>1395121</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PE_429796</t>
+          <t>2211489</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 1432</t>
+          <t>26-Aug-21 0919</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 1432</t>
+          <t/>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 1433</t>
+          <t/>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1841,37 +1841,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1754443</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1754443</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PE_429467</t>
+          <t>2095869</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 0112</t>
+          <t>26-Aug-19 0146</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-10 0112</t>
+          <t/>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1880,1322 +1880,6 @@
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>1754440</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>1754440</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>PS_429457</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>pesagem-veiculo-carga-out</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-10 0111</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-10 0111</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>1754437</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>1754437</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>PE_429466</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>pesagem-veiculo-carga-in</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-10 0111</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-10 0111</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>2081638</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-09 1745</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>995738</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>995738</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>2021736</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-09 0948</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>8353b3aa-6acc-4a5a-a61a-52763cfefeac</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2163612</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0710</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>2190259</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0621</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>1329954</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>1329954</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2134524</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0616</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>1331904</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>1331904</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>2160058</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0615</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>1261550</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>1261550</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>2114903</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0557</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>2118299</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0556</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>1213607</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>1213607</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>2079627</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0555</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>1214064</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>1214064</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>2081539</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0555</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>2193252</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0535</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>1192446</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>1192446</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>2091350</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0534</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>1330785</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>1330785</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>2139702</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0531</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>2164666</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0530</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>2118702</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0509</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>1293782</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>1293782</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>2140753</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0458</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>2134235</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0457</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>2103956</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0436</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>2081236</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0408</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>2114825</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0407</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>2199030</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0229</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>1409819</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>1409819</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>2216095</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-22 0148</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>2216108</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-22 0045</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>1408476</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>1408476</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>2211543</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-21 2220</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>1395121</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>2211489</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-21 0919</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>2095869</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-19 0146</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -177,19 +177,19 @@
   <cols>
     <col min="1" max="1" width="32.7265625" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
-    <col min="3" max="3" width="11.3828125" customWidth="true"/>
-    <col min="4" max="4" width="23.0078125" customWidth="true"/>
+    <col min="3" max="3" width="12.6171875" customWidth="true"/>
+    <col min="4" max="4" width="27.7734375" customWidth="true"/>
     <col min="5" max="5" width="7.8359375" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="12.484375" customWidth="true"/>
-    <col min="8" max="8" width="14.92578125" customWidth="true"/>
-    <col min="9" max="9" width="41.48046875" customWidth="true"/>
+    <col min="8" max="8" width="16.40234375" customWidth="true"/>
+    <col min="9" max="9" width="11.37890625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 35 item(s) at 2026-10-13</t>
+          <t>Displaying 44 item(s) at 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -243,17 +243,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2441812</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1716</t>
+          <t>26-Oct-15 1346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2441818</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1716</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2441809</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1715</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2412160</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1715</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1609702</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2259079</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1715</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1715</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1500640</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2230025</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1715</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1715</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-13 1715</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>2441817</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 1745</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>995738</t>
+          <t>1481887</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2021736</t>
+          <t>2249769</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-09 0948</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -753,24 +753,24 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8353b3aa-6acc-4a5a-a61a-52763cfefeac</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1508792</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>2210996</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2441821</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1499538</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2246512</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2441823</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Oct-15 1345</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1790328</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1790328</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Oct-15 1148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-15 1148</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1042,22 +1042,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>PS_431587</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-14 1251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-14 1450</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1089,22 +1089,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>PE_431571</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-14 1223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-14 1737</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Oct-14 1047</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1330785</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>2139702</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Aug-25 0531</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1293782</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2211489</t>
+          <t>2140753</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0919</t>
+          <t>26-Aug-25 0458</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1841,45 +1841,468 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2134235</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0457</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2103956</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0436</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2081236</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0408</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2114825</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0407</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2199030</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0229</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>1409819</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1409819</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2216095</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-22 0148</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2216108</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-22 0045</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>1408476</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1408476</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2211543</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 2220</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1395121</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2211489</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-21 0919</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>2095869</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>26-Aug-19 0146</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -175,13 +175,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.7265625" customWidth="true"/>
+    <col min="1" max="1" width="33.84375" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
     <col min="3" max="3" width="12.6171875" customWidth="true"/>
-    <col min="4" max="4" width="27.7734375" customWidth="true"/>
-    <col min="5" max="5" width="7.8359375" customWidth="true"/>
+    <col min="4" max="4" width="30.33984375" customWidth="true"/>
+    <col min="5" max="5" width="11.01953125" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
-    <col min="7" max="7" width="12.484375" customWidth="true"/>
+    <col min="7" max="7" width="16.40234375" customWidth="true"/>
     <col min="8" max="8" width="16.40234375" customWidth="true"/>
     <col min="9" max="9" width="11.37890625" customWidth="true"/>
   </cols>
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 44 item(s) at 2026-10-15</t>
+          <t>Displaying 163 item(s) at 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -243,22 +243,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1819857</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1819857</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2441812</t>
+          <t>A_655272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1346</t>
+          <t>26-Oct-19 0823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -278,7 +278,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0823</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -290,22 +290,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1819856</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1819856</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2441818</t>
+          <t>A_651935</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0823</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -325,7 +325,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0823</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -337,37 +337,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1819855</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1819855</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2441809</t>
+          <t>37688105</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0823</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1804795</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1804795</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2412160</t>
+          <t>2441726</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0818</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1813488</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1609702</t>
+          <t>1813488</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2259079</t>
+          <t>2443401</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1804802</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1804802</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2447168</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1804821</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1500640</t>
+          <t>1804821</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2230025</t>
+          <t>2442368</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1804796</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1804796</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2442355</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1804848</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1804848</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2442428</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1804867</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1804867</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2441817</t>
+          <t>2442367</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1481887</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2249769</t>
+          <t>2374686</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1813988</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1508792</t>
+          <t>1813988</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2210996</t>
+          <t>2444115</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2441823</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1499538</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2246512</t>
+          <t>2441817</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1804804</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1804804</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2441823</t>
+          <t>2447139</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1345</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1790328</t>
+          <t>1804798</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1790328</t>
+          <t>1804798</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>2442068</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1148</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-15 1148</t>
+          <t/>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1042,22 +1042,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1804831</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1804831</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>PS_431587</t>
+          <t>2442366</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1251</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1450</t>
+          <t/>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1089,22 +1089,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>PE_431571</t>
+          <t>2441818</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1223</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1737</t>
+          <t/>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>2441812</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1047</t>
+          <t>26-Oct-19 0816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2441809</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1804836</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1804836</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2447167</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1804803</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1804803</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2442258</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1804794</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1804794</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2447166</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>2412160</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1804834</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1804834</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2447137</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1330785</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2139702</t>
+          <t>2447082</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0531</t>
+          <t>26-Oct-19 0815</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1747,22 +1747,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1794,22 +1794,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1293782</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2140753</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0458</t>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1935,37 +1935,37 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1804691</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1804691</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>37492119</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Oct-16 2253</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 2253</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1982,37 +1982,37 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1804612</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1804612</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>37491790</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Oct-16 2230</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 2230</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2029,37 +2029,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1804484</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1804484</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>37490656</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Oct-16 2212</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 2212</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2076,37 +2076,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1804482</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1409819</t>
+          <t>1804482</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2216095</t>
+          <t>37490614</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0148</t>
+          <t>26-Oct-16 2210</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 2210</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2123,37 +2123,37 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1804481</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1804481</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>37490603</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Oct-16 2209</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 2209</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2170,37 +2170,37 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1804480</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1408476</t>
+          <t>1804480</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2211543</t>
+          <t>37490602</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 2220</t>
+          <t>26-Oct-16 2209</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 2209</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2217,37 +2217,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1804479</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1804479</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2211489</t>
+          <t>37490601</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-21 0919</t>
+          <t>26-Oct-16 2209</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 2209</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2264,45 +2264,5732 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>1804477</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1804477</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>37490580</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2207</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2207</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>1804475</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1804475</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>37490573</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2206</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2206</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>1804473</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1804473</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>37490566</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2205</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2205</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>1804472</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1804472</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>37490563</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2205</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2205</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>1804470</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1804470</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>37490551</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2201</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2201</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>1804469</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1804469</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>37490536</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2200</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2200</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>1804467</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1804467</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>37490516</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2159</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2159</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>1804466</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1804466</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>37490512</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2159</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2159</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>1804465</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1804465</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>37490509</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2158</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2158</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>1804463</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1804463</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>37490500</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2158</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2158</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>1804461</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1804461</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>37490473</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2157</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2157</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>1804459</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1804459</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>37490468</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2157</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2157</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>1804458</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1804458</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>37490466</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>1804457</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1804457</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>37490465</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>1804456</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1804456</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>37490464</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>1804455</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1804455</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>37490463</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2156</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>1804453</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1804453</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>37490442</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2155</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2155</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>1804452</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1804452</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>37490435</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2155</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2155</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>1804451</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1804451</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>37490429</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2154</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2154</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>1804450</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>1804450</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>37490428</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2154</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2154</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>1804449</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1804449</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>37490426</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2153</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2153</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>1804447</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1804447</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>37490421</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2153</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2153</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>1804446</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1804446</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>37490409</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>1804445</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1804445</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>37490408</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>1804444</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1804444</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>37490407</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>1804443</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1804443</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>37490406</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>1804442</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1804442</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>37490405</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>1804441</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1804441</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>37490400</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>1804440</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1804440</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>37490404</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>1804439</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1804439</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>37490402</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>1804437</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1804437</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>37490401</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>1804438</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1804438</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>37490403</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>1804436</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1804436</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>37490390</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>1804432</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1804432</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>37490393</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>1804433</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1804433</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>37490399</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>1804434</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1804434</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>37490398</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>1804435</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1804435</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>37490394</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>1804429</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1804429</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>37490396</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>1804431</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1804431</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>37490397</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>1804430</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1804430</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>37490395</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>1804428</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1804428</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>37490392</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>1804426</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1804426</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>37490389</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>1804427</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1804427</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>37490391</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>atribuicao-troca-navio</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2152</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>1804424</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1804424</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>37490384</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2151</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2151</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>1804423</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1804423</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>37490383</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2151</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2151</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>1804416</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1804416</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>37490357</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2150</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2150</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>1804415</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1804415</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>37490356</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2150</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2150</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>1804412</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1804412</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>37490345</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2149</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2149</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>1804411</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1804411</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>37490344</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2149</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2149</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>1804410</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1804410</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>37490342</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2149</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2149</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>1804409</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1804409</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>37490341</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2148</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2148</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>1804408</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1804408</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>37490339</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2148</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2148</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>1804407</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1804407</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>37490338</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2148</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2148</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>1804404</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1804404</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>37490332</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2147</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2147</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>1804403</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1804403</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>37490330</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2147</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2147</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>1804402</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1804402</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>37490328</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2146</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2146</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>1804401</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1804401</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>37490324</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2145</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2145</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>1804399</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1804399</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>37490316</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2144</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2144</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>1804396</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1804396</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>37490296</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2140</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2140</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>1804394</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1804394</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>37490274</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2139</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2139</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>1804393</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1804393</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>37490219</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2138</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2138</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>1804392</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1804392</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>37490218</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2138</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2138</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>1804390</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1804390</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>37490163</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2137</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2137</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>1804389</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1804389</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>37490162</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2137</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2137</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>1804388</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1804388</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>37490161</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2137</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2137</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>1804386</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1804386</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>37490159</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2136</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2136</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>1804385</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1804385</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>37490155</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2136</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2136</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>1804383</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1804383</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>37490154</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2135</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2135</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>1804382</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1804382</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>37490151</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2135</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2135</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>1804381</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1804381</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>37490150</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2135</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2135</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>1804380</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1804380</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>37490144</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2134</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2134</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>1804379</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1804379</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>37490143</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2134</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2134</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>1804378</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1804378</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>37490141</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2134</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2134</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>1804375</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1804375</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>37490132</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2132</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>1804374</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1804374</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>37490117</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2131</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>1804370</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1804370</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>37490096</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2125</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>1804369</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1804369</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>37490094</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2125</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>1804368</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1804368</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>37490090</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2124</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>1804367</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1804367</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>37490088</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2123</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>1804366</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1804366</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>37490086</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2123</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>1804365</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1804365</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>37490085</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2122</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>1804364</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1804364</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>37490083</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2122</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>1804363</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1804363</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>37490061</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2119</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>1804362</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1804362</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>37490055</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2117</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>1804361</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1804361</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>37490053</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2117</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>1804358</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1804358</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>37490046</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2115</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>1804357</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1804357</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>37490045</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2115</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2115</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>1804356</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1804356</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>37490041</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2115</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2115</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>1804355</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1804355</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>37490039</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2114</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2114</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>1804354</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1804354</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>37490037</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2113</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>1804351</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1804351</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>37490028</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2112</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>1804348</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1804348</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>37490013</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2110</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>1804347</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1804347</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>37490003</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2109</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2109</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>1804346</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1804346</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>37490002</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2108</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2108</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>1804345</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1804345</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>37490001</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2108</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2108</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>1804344</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1804344</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>37489999</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2107</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0823</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>1804343</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1804343</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>37489996</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2106</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2106</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>1804342</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1804342</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>37489995</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2106</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 2106</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>1802018</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1802018</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>407146</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>transito-simplificado-conteiner</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 1643</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 1643</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 1643</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>1796889</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1796889</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>E_433077</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>acesso-veiculos-in</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 0512</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 0513</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>1781423</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1781423</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>PS_431587</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-out</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1251</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0822</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>1781236</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1781236</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>PE_431571</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-in</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1223</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0822</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>2081638</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1047</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>2163612</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0710</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>2190259</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0621</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>2134524</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0616</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>2160058</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0615</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>2114903</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0557</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>2118299</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0556</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>1213607</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1213607</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>2079627</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0555</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>1214064</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1214064</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>2081539</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0555</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>2193252</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0535</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>1192446</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1192446</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>2091350</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0534</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>1343646</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1343646</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>2164666</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0530</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>1213221</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1213221</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>2118702</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0509</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>2134235</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0457</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1258735</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>2103956</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0436</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1213551</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>2081236</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0408</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1213256</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>2114825</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0407</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>2199030</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0229</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1409462</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>2216108</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-22 0045</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>1226304</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>2095869</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>inspecao-nao-invasiva</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>ERRO</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>26-Aug-19 0146</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 163 item(s) at 2026-10-19</t>
+          <t>Displaying 136 item(s) at 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -243,17 +243,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1819857</t>
+          <t>1822300</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1819857</t>
+          <t>1822300</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>A_655272</t>
+          <t>A_657322</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t>26-Oct-19 1405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -278,7 +278,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t>26-Oct-19 1405</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1819856</t>
+          <t>1822299</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1819856</t>
+          <t>1822299</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>A_651935</t>
+          <t>A_655510</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t>26-Oct-19 1405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -325,7 +325,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t>26-Oct-19 1405</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -337,37 +337,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1819855</t>
+          <t>1813488</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1819855</t>
+          <t>1813488</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>37688105</t>
+          <t>2443401</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t>26-Oct-19 1402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1804795</t>
+          <t>1804867</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1804795</t>
+          <t>1804867</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2441726</t>
+          <t>2442367</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0818</t>
+          <t>26-Oct-19 1402</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1813488</t>
+          <t>1804798</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1813488</t>
+          <t>1804798</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2443401</t>
+          <t>2442068</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0818</t>
+          <t>26-Oct-19 1402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1804802</t>
+          <t>1804821</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1804802</t>
+          <t>1804821</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2447168</t>
+          <t>2442368</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0817</t>
+          <t>26-Oct-19 1401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1804821</t>
+          <t>1804794</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1804821</t>
+          <t>1804794</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2442368</t>
+          <t>2447166</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0817</t>
+          <t>26-Oct-19 1401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1804796</t>
+          <t>1804836</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1804796</t>
+          <t>1804836</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2442355</t>
+          <t>2447167</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0817</t>
+          <t>26-Oct-19 1401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1804848</t>
+          <t>1804834</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1804848</t>
+          <t>1804834</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2442428</t>
+          <t>2447137</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0817</t>
+          <t>26-Oct-19 1401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1804867</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1804867</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2442367</t>
+          <t>2441817</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0817</t>
+          <t>26-Oct-19 1401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2374686</t>
+          <t>2447082</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0817</t>
+          <t>26-Oct-19 1401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1813988</t>
+          <t>1804802</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1813988</t>
+          <t>1804802</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2444115</t>
+          <t>2447168</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0817</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2441821</t>
+          <t>2441812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2441823</t>
+          <t>2374686</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1804848</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1804848</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2441817</t>
+          <t>2442428</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1804798</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1804798</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2442068</t>
+          <t>2441818</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1804831</t>
+          <t>1813988</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1804831</t>
+          <t>1813988</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2442366</t>
+          <t>2444115</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2441818</t>
+          <t>2441823</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1565683</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2441812</t>
+          <t>2297940</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0816</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2412160</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1804795</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1804795</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2441809</t>
+          <t>2441726</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1804836</t>
+          <t>1804803</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1804836</t>
+          <t>1804803</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2447167</t>
+          <t>2442258</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1804803</t>
+          <t>1804831</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1804803</t>
+          <t>1804831</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2442258</t>
+          <t>2442366</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1804794</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1804794</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2447166</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2412160</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1804796</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1804796</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>2442355</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1804834</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1804834</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2447137</t>
+          <t>2441809</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2441821</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1400</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1653,22 +1653,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1820940</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1820940</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2447082</t>
+          <t>PE_435092</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0815</t>
+          <t>26-Oct-19 1055</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 1055</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1820122</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1820122</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>A_654985</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1747,42 +1747,42 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1820120</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1820120</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37689370</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t/>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1794,22 +1794,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1820119</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1820119</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>A_652333</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1841,42 +1841,42 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1820118</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1820118</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37689367</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t/>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1888,42 +1888,42 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1820117</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1820117</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37689361</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t/>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1935,42 +1935,42 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1804691</t>
+          <t>1820116</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1804691</t>
+          <t>1820116</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>37492119</t>
+          <t>A_655361</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2253</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2253</t>
+          <t/>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1804612</t>
+          <t>1820115</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1804612</t>
+          <t>1820115</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>37491790</t>
+          <t>37689366</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2230</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2230</t>
+          <t>26-Oct-19 0915</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1804484</t>
+          <t>1820103</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1804484</t>
+          <t>1820103</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>37490656</t>
+          <t>37689304</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2212</t>
+          <t>26-Oct-19 0912</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2212</t>
+          <t>26-Oct-19 0912</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2076,22 +2076,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1804482</t>
+          <t>1820102</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1804482</t>
+          <t>1820102</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>37490614</t>
+          <t>S_435009</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-out</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2210</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2210</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2123,17 +2123,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1804481</t>
+          <t>1820100</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1804481</t>
+          <t>1820100</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>37490603</t>
+          <t>37689298</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2209</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2209</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1804480</t>
+          <t>1820099</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1804480</t>
+          <t>1820099</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>37490602</t>
+          <t>37689296</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2209</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2209</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1804479</t>
+          <t>1820098</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1804479</t>
+          <t>1820098</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>37490601</t>
+          <t>37689295</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2209</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2209</t>
+          <t>26-Oct-19 0911</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2264,22 +2264,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1804477</t>
+          <t>1820097</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1804477</t>
+          <t>1820097</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>37490580</t>
+          <t>E_435029</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-in</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2207</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2207</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1804475</t>
+          <t>1820095</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1804475</t>
+          <t>1820095</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>37490573</t>
+          <t>37689290</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2206</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2206</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1804473</t>
+          <t>1820094</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1804473</t>
+          <t>1820094</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>37490566</t>
+          <t>37689291</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2205</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2205</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1804472</t>
+          <t>1820093</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1804472</t>
+          <t>1820093</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>37490563</t>
+          <t>37689289</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2205</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2205</t>
+          <t>26-Oct-19 0910</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1804470</t>
+          <t>1820092</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1804470</t>
+          <t>1820092</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>37490551</t>
+          <t>37689286</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2201</t>
+          <t>26-Oct-19 0909</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2201</t>
+          <t>26-Oct-19 0909</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2499,22 +2499,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1804469</t>
+          <t>1820091</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1804469</t>
+          <t>1820091</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>37490536</t>
+          <t>S_435019</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-out</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2200</t>
+          <t>26-Oct-19 0908</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2200</t>
+          <t>26-Oct-19 0908</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2546,42 +2546,42 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1804467</t>
+          <t>1820089</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1804467</t>
+          <t>1820089</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>37490516</t>
+          <t>A_600479</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2159</t>
+          <t>26-Oct-19 0908</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2159</t>
+          <t/>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0908</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1804466</t>
+          <t>1820075</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1804466</t>
+          <t>1820075</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>37490512</t>
+          <t>37689199</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2159</t>
+          <t>26-Oct-19 0905</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2159</t>
+          <t>26-Oct-19 0905</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2640,42 +2640,42 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1804465</t>
+          <t>1820074</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1804465</t>
+          <t>1820074</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>37490509</t>
+          <t>A_655351</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2158</t>
+          <t>26-Oct-19 0902</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2158</t>
+          <t/>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0902</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1804463</t>
+          <t>1820025</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1804463</t>
+          <t>1820025</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>37490500</t>
+          <t>37688706</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2158</t>
+          <t>26-Oct-19 0853</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2158</t>
+          <t>26-Oct-19 0853</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2734,17 +2734,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1804461</t>
+          <t>1820023</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1804461</t>
+          <t>1820023</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>37490473</t>
+          <t>37688704</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2157</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2157</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2781,17 +2781,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1804459</t>
+          <t>1820022</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1804459</t>
+          <t>1820022</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>37490468</t>
+          <t>37688703</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2157</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2157</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2828,17 +2828,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1804458</t>
+          <t>1820020</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1804458</t>
+          <t>1820020</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>37490466</t>
+          <t>37688695</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2875,17 +2875,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1804457</t>
+          <t>1820019</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1804457</t>
+          <t>1820019</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>37490465</t>
+          <t>37688699</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2922,17 +2922,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1804456</t>
+          <t>1820018</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1804456</t>
+          <t>1820018</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>37490464</t>
+          <t>37688696</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1804455</t>
+          <t>1820017</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1804455</t>
+          <t>1820017</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>37490463</t>
+          <t>37688697</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2156</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3016,17 +3016,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1804453</t>
+          <t>1820016</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1804453</t>
+          <t>1820016</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>37490442</t>
+          <t>37688694</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2155</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2155</t>
+          <t>26-Oct-19 0852</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1804452</t>
+          <t>1820015</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1804452</t>
+          <t>1820015</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>37490435</t>
+          <t>37688693</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2155</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2155</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3110,17 +3110,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1804451</t>
+          <t>1820014</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1804451</t>
+          <t>1820014</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>37490429</t>
+          <t>37688692</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2154</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2154</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3157,17 +3157,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1804450</t>
+          <t>1820013</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1804450</t>
+          <t>1820013</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>37490428</t>
+          <t>37688691</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2154</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2154</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1804449</t>
+          <t>1820012</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1804449</t>
+          <t>1820012</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>37490426</t>
+          <t>37688690</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2153</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2153</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1804447</t>
+          <t>1820011</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1804447</t>
+          <t>1820011</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>37490421</t>
+          <t>37688689</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2153</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2153</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1804446</t>
+          <t>1820010</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1804446</t>
+          <t>1820010</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>37490409</t>
+          <t>37688688</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3345,17 +3345,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1804445</t>
+          <t>1820009</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1804445</t>
+          <t>1820009</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>37490408</t>
+          <t>37688687</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3392,22 +3392,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1804444</t>
+          <t>1820008</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1804444</t>
+          <t>1820008</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>37490407</t>
+          <t>S_435012</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-out</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3439,22 +3439,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1804443</t>
+          <t>1820006</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1804443</t>
+          <t>1820006</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>37490406</t>
+          <t>E_435024</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-in</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0851</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3486,17 +3486,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1804442</t>
+          <t>1819988</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1804442</t>
+          <t>1819988</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>37490405</t>
+          <t>37688606</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0847</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0847</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3533,22 +3533,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>1804441</t>
+          <t>1819987</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1804441</t>
+          <t>1819987</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>37490400</t>
+          <t>37688605</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0845</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0845</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3580,22 +3580,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>1804440</t>
+          <t>1819984</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1804440</t>
+          <t>1819984</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>37490404</t>
+          <t>37688597</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0843</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0843</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3627,22 +3627,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1804439</t>
+          <t>1819983</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>1804439</t>
+          <t>1819983</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>37490402</t>
+          <t>37688592</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0843</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0843</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3674,22 +3674,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1804437</t>
+          <t>1819982</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1804437</t>
+          <t>1819982</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>37490401</t>
+          <t>37688591</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0842</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0842</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3721,22 +3721,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1804438</t>
+          <t>1819981</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1804438</t>
+          <t>1819981</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>37490403</t>
+          <t>37688590</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0841</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0841</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3768,22 +3768,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1804436</t>
+          <t>1819980</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1804436</t>
+          <t>1819980</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>37490390</t>
+          <t>E_435022</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>acesso-veiculos-in</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0841</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-19 0841</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3815,42 +3815,42 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1804432</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1804432</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>37490393</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t/>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3862,42 +3862,42 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1804433</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>1804433</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>37490399</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t/>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3909,42 +3909,42 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1804434</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>1804434</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>37490398</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t/>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3956,42 +3956,42 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1804435</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>1804435</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>37490394</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t/>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4003,42 +4003,42 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1804429</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>1804429</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>37490396</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t/>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4050,22 +4050,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>1804431</t>
+          <t>1804691</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>1804431</t>
+          <t>1804691</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>37490397</t>
+          <t>37492119</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-16 2253</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-16 2253</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4097,22 +4097,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1804430</t>
+          <t>1804612</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>1804430</t>
+          <t>1804612</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>37490395</t>
+          <t>37491790</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-16 2230</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-16 2230</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4144,22 +4144,22 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1804428</t>
+          <t>1804444</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>1804428</t>
+          <t>1804444</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>37490392</t>
+          <t>37490407</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>atribuicao-troca-navio</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4191,17 +4191,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>1804426</t>
+          <t>1804441</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>1804426</t>
+          <t>1804441</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>37490389</t>
+          <t>37490400</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>1804427</t>
+          <t>1804440</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>1804427</t>
+          <t>1804440</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>37490391</t>
+          <t>37490404</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4285,22 +4285,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1804424</t>
+          <t>1804439</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>1804424</t>
+          <t>1804439</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>37490384</t>
+          <t>37490402</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2151</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2151</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -4332,22 +4332,22 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>1804423</t>
+          <t>1804437</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>1804423</t>
+          <t>1804437</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>37490383</t>
+          <t>37490401</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2151</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2151</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -4379,22 +4379,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>1804416</t>
+          <t>1804438</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>1804416</t>
+          <t>1804438</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>37490357</t>
+          <t>37490403</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2150</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2150</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -4426,22 +4426,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>1804415</t>
+          <t>1804436</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>1804415</t>
+          <t>1804436</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>37490356</t>
+          <t>37490390</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2150</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2150</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -4473,22 +4473,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>1804412</t>
+          <t>1804432</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>1804412</t>
+          <t>1804432</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>37490345</t>
+          <t>37490393</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2149</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2149</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -4520,22 +4520,22 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>1804411</t>
+          <t>1804433</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>1804411</t>
+          <t>1804433</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>37490344</t>
+          <t>37490399</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2149</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2149</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -4567,22 +4567,22 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>1804410</t>
+          <t>1804434</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>1804410</t>
+          <t>1804434</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>37490342</t>
+          <t>37490398</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2149</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2149</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -4614,22 +4614,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>1804409</t>
+          <t>1804435</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>1804409</t>
+          <t>1804435</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>37490341</t>
+          <t>37490394</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2148</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2148</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -4661,22 +4661,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>1804408</t>
+          <t>1804431</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>1804408</t>
+          <t>1804431</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>37490339</t>
+          <t>37490397</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2148</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2148</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -4708,22 +4708,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>1804407</t>
+          <t>1804429</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>1804407</t>
+          <t>1804429</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>37490338</t>
+          <t>37490396</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2148</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2148</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -4755,22 +4755,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>1804404</t>
+          <t>1804430</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>1804404</t>
+          <t>1804430</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>37490332</t>
+          <t>37490395</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2147</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2147</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -4802,22 +4802,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>1804403</t>
+          <t>1804428</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>1804403</t>
+          <t>1804428</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>37490330</t>
+          <t>37490392</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2147</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2147</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>1804402</t>
+          <t>1804426</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>1804402</t>
+          <t>1804426</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>37490328</t>
+          <t>37490389</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2146</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2146</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>1804401</t>
+          <t>1804427</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>1804401</t>
+          <t>1804427</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>37490324</t>
+          <t>37490391</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>atribuicao-troca-navio</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2145</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2145</t>
+          <t>26-Oct-16 2152</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -4943,17 +4943,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>1804399</t>
+          <t>1804393</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>1804399</t>
+          <t>1804393</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>37490316</t>
+          <t>37490219</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2144</t>
+          <t>26-Oct-16 2138</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2144</t>
+          <t>26-Oct-16 2138</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -4990,17 +4990,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>1804396</t>
+          <t>1804392</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>1804396</t>
+          <t>1804392</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>37490296</t>
+          <t>37490218</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2140</t>
+          <t>26-Oct-16 2138</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2140</t>
+          <t>26-Oct-16 2138</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5037,17 +5037,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>1804394</t>
+          <t>1804390</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>1804394</t>
+          <t>1804390</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>37490274</t>
+          <t>37490163</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2139</t>
+          <t>26-Oct-16 2137</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2139</t>
+          <t>26-Oct-16 2137</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5084,17 +5084,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>1804393</t>
+          <t>1804386</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>1804393</t>
+          <t>1804386</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>37490219</t>
+          <t>37490159</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-16 2136</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-16 2136</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>1804392</t>
+          <t>1804385</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>1804392</t>
+          <t>1804385</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>37490218</t>
+          <t>37490155</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-16 2136</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-16 2136</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -5178,17 +5178,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>1804390</t>
+          <t>1804383</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>1804390</t>
+          <t>1804383</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>37490163</t>
+          <t>37490154</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-16 2135</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-16 2135</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>1804389</t>
+          <t>1804357</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>1804389</t>
+          <t>1804357</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>37490162</t>
+          <t>37490045</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-16 2115</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-16 2115</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -5272,17 +5272,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>1804388</t>
+          <t>1804356</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>1804388</t>
+          <t>1804356</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>37490161</t>
+          <t>37490041</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-16 2115</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-16 2115</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -5319,17 +5319,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>1804386</t>
+          <t>1804355</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>1804386</t>
+          <t>1804355</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>37490159</t>
+          <t>37490039</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-16 2114</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-16 2114</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>1804385</t>
+          <t>1804347</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>1804385</t>
+          <t>1804347</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>37490155</t>
+          <t>37490003</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-16 2109</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-16 2109</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>1804383</t>
+          <t>1804346</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>1804383</t>
+          <t>1804346</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>37490154</t>
+          <t>37490002</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-16 2108</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-16 2108</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -5460,17 +5460,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>1804382</t>
+          <t>1804345</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>1804382</t>
+          <t>1804345</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>37490151</t>
+          <t>37490001</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-16 2108</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-16 2108</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -5507,17 +5507,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>1804381</t>
+          <t>1804343</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>1804381</t>
+          <t>1804343</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>37490150</t>
+          <t>37489996</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-16 2106</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-16 2106</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -5554,17 +5554,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>1804380</t>
+          <t>1804342</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>1804380</t>
+          <t>1804342</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>37490144</t>
+          <t>37489995</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2134</t>
+          <t>26-Oct-16 2106</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2134</t>
+          <t>26-Oct-16 2106</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -5601,42 +5601,42 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>1804379</t>
+          <t>1802018</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>1804379</t>
+          <t>1802018</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>37490143</t>
+          <t>407146</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>transito-simplificado-conteiner</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2134</t>
+          <t>26-Oct-16 1643</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2134</t>
+          <t>26-Oct-16 1643</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 1643</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -5648,42 +5648,42 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>1804378</t>
+          <t>1796889</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>1804378</t>
+          <t>1796889</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>37490141</t>
+          <t>E_433077</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>acesso-veiculos-in</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2134</t>
+          <t>26-Oct-16 0512</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2134</t>
+          <t/>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-16 0513</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -5695,42 +5695,42 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>1804375</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>1804375</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>37490132</t>
+          <t>PS_431587</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2132</t>
+          <t>26-Oct-14 1251</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0822</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -5742,42 +5742,42 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>1804374</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>1804374</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>37490117</t>
+          <t>PE_431571</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2131</t>
+          <t>26-Oct-14 1223</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-19 0822</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -5789,37 +5789,37 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>1804370</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>1804370</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>37490096</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2125</t>
+          <t>26-Oct-14 1047</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -5836,37 +5836,37 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>1804369</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>1804369</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>37490094</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2125</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -5883,37 +5883,37 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>1804368</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>1804368</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>37490090</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2124</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -5930,37 +5930,37 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>1804367</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>1804367</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>37490088</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2123</t>
+          <t>26-Aug-25 0616</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -5977,37 +5977,37 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>1804366</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>1804366</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>37490086</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2123</t>
+          <t>26-Aug-25 0615</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6024,37 +6024,37 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>1804365</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>1804365</t>
+          <t>1261550</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>37490085</t>
+          <t>2114903</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2122</t>
+          <t>26-Aug-25 0557</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6071,37 +6071,37 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>1804364</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>1804364</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>37490083</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2122</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6118,37 +6118,37 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>1804363</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>1804363</t>
+          <t>1213607</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>37490061</t>
+          <t>2079627</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2119</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -6165,37 +6165,37 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>1804362</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>1804362</t>
+          <t>1214064</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>37490055</t>
+          <t>2081539</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2117</t>
+          <t>26-Aug-25 0555</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6212,37 +6212,37 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>1804361</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>1804361</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>37490053</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2117</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -6259,37 +6259,37 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>1804358</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>1804358</t>
+          <t>1192446</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>37490046</t>
+          <t>2091350</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t>26-Aug-25 0534</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -6306,37 +6306,37 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>1804357</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>1804357</t>
+          <t>1343646</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>37490045</t>
+          <t>2164666</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t>26-Aug-25 0530</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t/>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -6353,37 +6353,37 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>1804356</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>1804356</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>37490041</t>
+          <t>2118702</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t>26-Aug-25 0509</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t/>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -6400,37 +6400,37 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>1804355</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>1804355</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>37490039</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2114</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2114</t>
+          <t/>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -6447,37 +6447,37 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>1804354</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>1804354</t>
+          <t>1258735</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>37490037</t>
+          <t>2103956</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2113</t>
+          <t>26-Aug-25 0436</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -6494,37 +6494,37 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>1804351</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>1804351</t>
+          <t>1213551</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>37490028</t>
+          <t>2081236</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2112</t>
+          <t>26-Aug-25 0408</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -6541,37 +6541,37 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>1804348</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>1804348</t>
+          <t>1213256</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>37490013</t>
+          <t>2114825</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2110</t>
+          <t>26-Aug-25 0407</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0823</t>
+          <t/>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -6588,37 +6588,37 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>1804347</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>1804347</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>37490003</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2109</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2109</t>
+          <t/>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -6635,37 +6635,37 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>1804346</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>1804346</t>
+          <t>1409462</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>37490002</t>
+          <t>2216108</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t>26-Aug-22 0045</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t/>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -6682,37 +6682,37 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>1804345</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>1804345</t>
+          <t>1226304</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>37490001</t>
+          <t>2095869</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t>26-Aug-19 0146</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t/>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -6721,1275 +6721,6 @@
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>1804344</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>1804344</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>37489999</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>posicao-conteiner</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 2107</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-19 0823</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>1804343</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>1804343</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>37489996</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>posicao-conteiner</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 2106</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 2106</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>1804342</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>1804342</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>37489995</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>posicao-conteiner</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>ENVIADO</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 2106</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 2106</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>1802018</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>1802018</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>407146</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>transito-simplificado-conteiner</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 1643</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 1643</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 1643</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>1796889</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>1796889</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>E_433077</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>acesso-veiculos-in</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 0512</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 0513</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>1781423</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>1781423</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>PS_431587</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>pesagem-veiculo-carga-out</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-14 1251</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-19 0822</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>1781236</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>1781236</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>PE_431571</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>pesagem-veiculo-carga-in</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-14 1223</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-19 0822</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>2081638</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-14 1047</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>2163612</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0710</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>2190259</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0621</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>1329954</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>1329954</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>2134524</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0616</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>1331904</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>1331904</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>2160058</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0615</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>1261550</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>1261550</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>2114903</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0557</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>2118299</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0556</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>1213607</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>1213607</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>2079627</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0555</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>1214064</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>1214064</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>2081539</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0555</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>2193252</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0535</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>1192446</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>1192446</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>2091350</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0534</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>1343646</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>2164666</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0530</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>2118702</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0509</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>2134235</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0457</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>1258735</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>2103956</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0436</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>1213551</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>2081236</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0408</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>1213256</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>2114825</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0407</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>2199030</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0229</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>1409462</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>2216108</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-22 0045</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>1226304</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>2095869</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-19 0146</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -175,21 +175,21 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.7265625" customWidth="true"/>
-    <col min="2" max="2" width="11.015625" customWidth="true"/>
-    <col min="3" max="3" width="12.6171875" customWidth="true"/>
-    <col min="4" max="4" width="30.33984375" customWidth="true"/>
-    <col min="5" max="5" width="11.01953125" customWidth="true"/>
+    <col min="1" max="1" width="33.84375" customWidth="true"/>
+    <col min="2" max="2" width="11.01953125" customWidth="true"/>
+    <col min="3" max="3" width="15.0625" customWidth="true"/>
+    <col min="4" max="4" width="27.7734375" customWidth="true"/>
+    <col min="5" max="5" width="15.6640625" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="16.40234375" customWidth="true"/>
     <col min="8" max="8" width="16.40234375" customWidth="true"/>
-    <col min="9" max="9" width="11.37890625" customWidth="true"/>
+    <col min="9" max="9" width="43.078125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 77 item(s) at 2026-10-20</t>
+          <t>Displaying 124 item(s) at 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -243,37 +243,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1828652</t>
+          <t>1848353</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1828652</t>
+          <t>BAT9D98</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37805579</t>
+          <t>BAT9D98</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0908</t>
+          <t>26-Oct-22 1011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0908</t>
+          <t/>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -290,32 +290,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1804802</t>
+          <t>1848351</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1804802</t>
+          <t>BAT9D98</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2447168</t>
+          <t>BAT9D98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0902</t>
+          <t>26-Oct-22 1011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,22 +337,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1804804</t>
+          <t>1848337</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1804804</t>
+          <t>1848337</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2447139</t>
+          <t>37964134</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -362,17 +362,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0902</t>
+          <t>26-Oct-22 1009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1009</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1009</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -384,32 +384,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1813488</t>
+          <t>1848330</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1813488</t>
+          <t>FIF5F07</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2443401</t>
+          <t>FIF5F07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,22 +431,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1804836</t>
+          <t>1848321</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1804836</t>
+          <t>1848321</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2447167</t>
+          <t>37964100</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -456,17 +456,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1006</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1007</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -478,32 +478,32 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1804867</t>
+          <t>1848307</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1804867</t>
+          <t>TQH2C34</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2442367</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,32 +525,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1804796</t>
+          <t>1848288</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1804796</t>
+          <t>ATP6A22</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2442355</t>
+          <t>27536</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,22 +572,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1813988</t>
+          <t>1848287</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1813988</t>
+          <t>1848287</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2444115</t>
+          <t>37963958</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -597,17 +597,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1002</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1003</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1804798</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1804798</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2442068</t>
+          <t>2441821</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1804803</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1804803</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2442258</t>
+          <t>2441817</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1001</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1804848</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1804848</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2442428</t>
+          <t>2441818</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2374686</t>
+          <t>2447082</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0901</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1804834</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1804834</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2447137</t>
+          <t>2441809</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1804831</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1804831</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2442366</t>
+          <t>2441823</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2441821</t>
+          <t>2412160</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2441823</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1804821</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1804821</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2442368</t>
+          <t>2374686</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2441812</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1804794</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1804794</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2447166</t>
+          <t>2441812</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2441818</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 1000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1183,22 +1183,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1804795</t>
+          <t>1846738</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1804795</t>
+          <t>1846738</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2441726</t>
+          <t>37957803</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0653</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0653</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1230,22 +1230,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1846734</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1846734</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2441817</t>
+          <t>37957791</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1277,22 +1277,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1846733</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1846733</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>37957790</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1324,22 +1324,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1846732</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1846732</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2412160</t>
+          <t>37957787</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1371,22 +1371,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1846731</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1565683</t>
+          <t>1846731</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2297940</t>
+          <t>37957784</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1846730</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1846730</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>37957786</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1465,22 +1465,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1846728</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1846728</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2447082</t>
+          <t>37957785</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1490,17 +1490,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0652</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1512,22 +1512,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1846573</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1846573</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2441809</t>
+          <t>37955870</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1559,22 +1559,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1846572</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1846572</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>37955869</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0900</t>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1606,22 +1606,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1827918</t>
+          <t>1846571</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1827918</t>
+          <t>1846571</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>A_655363</t>
+          <t>37955868</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0641</t>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-20 0902</t>
+          <t>26-Oct-22 0617</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1820023</t>
+          <t>1846508</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1820023</t>
+          <t>1846508</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>37688704</t>
+          <t>37955297</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1673,22 +1673,22 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0852</t>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0852</t>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0556</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1846507</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1846507</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37955296</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1747,22 +1747,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1846506</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1846506</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37955295</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 0555</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1794,22 +1794,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1846408</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1846408</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37954977</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-22 0540</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0540</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-22 0540</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1846407</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1846407</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37954972</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t>26-Oct-22 0539</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0539</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t>26-Oct-22 0539</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1846322</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1846322</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37954737</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t>26-Oct-22 0522</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0522</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t>26-Oct-22 0522</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1804691</t>
+          <t>1846314</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1804691</t>
+          <t>1846314</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>37492119</t>
+          <t>37954712</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2253</t>
+          <t>26-Oct-22 0520</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2253</t>
+          <t>26-Oct-22 0520</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0520</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1804612</t>
+          <t>1846311</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1804612</t>
+          <t>1846311</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>37491790</t>
+          <t>37954685</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2002,22 +2002,22 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2230</t>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2230</t>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1804444</t>
+          <t>1846308</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1804444</t>
+          <t>1846308</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>37490407</t>
+          <t>37954683</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2049,22 +2049,22 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2152</t>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1804393</t>
+          <t>1846306</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1804393</t>
+          <t>1846306</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>37490219</t>
+          <t>37954681</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2096,22 +2096,22 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2123,17 +2123,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1804392</t>
+          <t>1846303</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1804392</t>
+          <t>1846303</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>37490218</t>
+          <t>37954673</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2143,22 +2143,22 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2138</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0519</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1804390</t>
+          <t>1846302</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1804390</t>
+          <t>1846302</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>37490163</t>
+          <t>37954672</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2190,22 +2190,22 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2137</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1804386</t>
+          <t>1846299</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1804386</t>
+          <t>1846299</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>37490159</t>
+          <t>37954667</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1804385</t>
+          <t>1846297</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1804385</t>
+          <t>1846297</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>37490155</t>
+          <t>37954664</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2284,22 +2284,22 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2136</t>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0518</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1804383</t>
+          <t>1846271</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1804383</t>
+          <t>1846271</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>37490154</t>
+          <t>37954552</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2331,22 +2331,22 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2135</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0512</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1804357</t>
+          <t>1846270</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1804357</t>
+          <t>1846270</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>37490045</t>
+          <t>37954550</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2378,22 +2378,22 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1804356</t>
+          <t>1846264</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1804356</t>
+          <t>1846264</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>37490041</t>
+          <t>37954537</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2425,22 +2425,22 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2115</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1804355</t>
+          <t>1846263</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1804355</t>
+          <t>1846263</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>37490039</t>
+          <t>37954536</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2472,22 +2472,22 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2114</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2114</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2499,17 +2499,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1804347</t>
+          <t>1846261</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1804347</t>
+          <t>1846261</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>37490003</t>
+          <t>37954533</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2519,22 +2519,22 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2109</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2109</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2546,17 +2546,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1804346</t>
+          <t>1846260</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1804346</t>
+          <t>1846260</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>37490002</t>
+          <t>37954530</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2566,22 +2566,22 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1804345</t>
+          <t>1846257</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1804345</t>
+          <t>1846257</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>37490001</t>
+          <t>37954527</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2108</t>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1804343</t>
+          <t>1846256</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1804343</t>
+          <t>1846256</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>37489996</t>
+          <t>37954523</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2660,22 +2660,22 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2106</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2106</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0511</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1804342</t>
+          <t>1846253</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1804342</t>
+          <t>1846253</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>37489995</t>
+          <t>37954518</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2106</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 2106</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2734,22 +2734,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1802018</t>
+          <t>1846250</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1802018</t>
+          <t>1846250</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>407146</t>
+          <t>37954514</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>transito-simplificado-conteiner</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 1643</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 1643</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 1643</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2781,22 +2781,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1796889</t>
+          <t>1846249</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1796889</t>
+          <t>1846249</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>E_433077</t>
+          <t>37954512</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-in</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 0512</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 0513</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2828,22 +2828,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1846248</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1846248</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>PS_431587</t>
+          <t>37954511</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1251</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0822</t>
+          <t>26-Oct-22 0510</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2875,22 +2875,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1846208</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1846208</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>PE_431571</t>
+          <t>37954389</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1223</t>
+          <t>26-Oct-22 0501</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0501</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-19 0822</t>
+          <t>26-Oct-22 0501</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2922,22 +2922,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1846168</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1846168</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>37954280</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1047</t>
+          <t>26-Oct-22 0456</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0456</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0457</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1846053</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1846053</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>37953804</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2994,17 +2994,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-22 0436</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0436</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0436</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3016,22 +3016,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1846052</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1846052</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>37953801</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0436</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3063,22 +3063,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1846051</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1846051</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>37953800</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0616</t>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0436</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3110,22 +3110,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1846050</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1846050</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>37953799</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0615</t>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0436</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3157,22 +3157,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1846049</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1846049</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>37953798</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3182,17 +3182,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0557</t>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0435</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0436</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3204,22 +3204,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1846004</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1846004</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>37953566</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3229,17 +3229,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Oct-22 0424</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0424</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0424</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3251,22 +3251,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1845977</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1213607</t>
+          <t>1845977</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2079627</t>
+          <t>37953487</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-22 0418</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0418</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0418</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1845927</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1214064</t>
+          <t>1845927</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2081539</t>
+          <t>37953331</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0555</t>
+          <t>26-Oct-22 0411</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0411</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0411</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3345,22 +3345,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1845922</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1845922</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>37953317</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Oct-22 0410</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0410</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0411</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3392,22 +3392,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1845869</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1192446</t>
+          <t>1845869</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2091350</t>
+          <t>37953132</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0534</t>
+          <t>26-Oct-22 0402</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0402</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0402</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3439,22 +3439,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1845866</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1343646</t>
+          <t>1845866</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2164666</t>
+          <t>37953122</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0530</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3486,22 +3486,22 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1213221</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2118702</t>
+          <t>37953116</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0509</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3533,22 +3533,22 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>37953111</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3580,22 +3580,22 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1258735</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2103956</t>
+          <t>37953053</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0436</t>
+          <t>26-Oct-22 0359</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0359</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0400</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3627,22 +3627,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1845831</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>1213551</t>
+          <t>1845831</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>2081236</t>
+          <t>37953008</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0408</t>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3674,22 +3674,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>1213256</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>2114825</t>
+          <t>37953007</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3699,17 +3699,17 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0407</t>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3721,22 +3721,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1845824</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>1368153</t>
+          <t>1845824</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>2199030</t>
+          <t>37952996</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0229</t>
+          <t>26-Oct-22 0356</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0356</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0356</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3768,22 +3768,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>1409462</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>2216108</t>
+          <t>37950234</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3793,17 +3793,17 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-22 0045</t>
+          <t>26-Oct-22 0224</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0224</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 0224</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3815,45 +3815,2207 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>1226304</t>
+          <t>1844791</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1226304</t>
+          <t>1844791</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>2095869</t>
+          <t>PS_437371</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>pesagem-veiculo-carga-out</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-22 0112</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-22 0112</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>1844492</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1844492</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>37947002</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>posicao-conteiner</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-22 0004</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-22 0004</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-22 0004</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>1843562</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1843562</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>PE_437215</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-in</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 2045</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 2045</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 2046</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>1840497</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1840497</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>37888117</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>carregamento-lotes</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1403</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1403</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1403</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>1840492</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1840492</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>GL_37888107</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>geracao-lotes</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1403</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1403</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>1840491</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1840491</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>AL_37888107</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1403</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1403</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>1840204</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1840204</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>37886870</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>carregamento-lotes</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1329</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1329</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1329</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>1839730</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1839730</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>GL_37882901</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>geracao-lotes</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1216</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1217</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1245</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>1839648</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1839648</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>GL_37882492</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>geracao-lotes</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1208</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1208</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>1839647</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1839647</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>AL_37882492</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>armazenamento-lote</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1208</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1208</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>1837327</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1837327</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>PE_436659</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-in</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 0739</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 0739</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>1803805</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1803805</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>2442325</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
           <t>inspecao-nao-invasiva</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-19 0146</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2340</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>7530a97e-0ba1-438d-8177-90d94424c237</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>1808089</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1808089</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>2442351</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2336</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>6d03ee38-4aea-413b-b62e-f8e4970cc8a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>1819515</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1819515</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>2447208</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2329</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>935f6223-189a-41b1-8965-5637cc0282e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>1819169</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1819169</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>2447354</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2328</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>ad6b18cd-29b4-4818-9c2e-4d2411966b20</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>1819756</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1819756</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>2447238</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2314</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>8fbb020d-1c14-4253-9940-f1a84654ae32</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>1757829</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1757829</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>2431325</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2304</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>fe83c35f-1cf3-48fb-b05e-1241fe337ad9</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>1819461</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1819461</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>2449412</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2233</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>d66f0f38-9d6c-4b0f-88e6-17dec2af75af</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>1706745</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1706745</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>2391734</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2147</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>da9052cc-ec30-4175-b299-a31095c5c1fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>1819339</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1819339</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>2447343</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2104</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>ff2026b8-8c67-4358-a4bf-10dec3e6947e</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>1806032</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1806032</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>2447206</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 2016</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>382c3db5-7d89-4872-aa54-6e9910d95900</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>1832939</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1832939</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>PE_436197</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-in</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1906</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1906</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1906</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>1810172</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1810172</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>2447261</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1821</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>17347f28-ea5d-4925-8c99-7cb294ed7c3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>1810258</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1810258</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>2447260</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1820</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>affbf807-9a80-48b1-97de-2b818e1eddd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>1816520</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1816520</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>2447225</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1741</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>8a8b7e92-36a8-48e5-be7b-ba2649fc072d</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>1817593</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1817593</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>2447236</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1713</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>8eb78726-2bf0-462a-9e58-0d0f8bb6f019</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>1816157</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1816157</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>2447242</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1618</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>b3a4751b-59d3-45db-b3e0-c58d6cfd9161</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>1821098</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1821098</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>2447309</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 1610</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>3777a0cf-f5a9-42f5-a6d1-95d7ca6a050f</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>1827918</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1827918</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>A_655363</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>acesso-veiculos-appt</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-20 0641</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-21 1420</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>1809786</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1809786</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>429696</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>agenda-navios-aeronaves</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1459</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1459</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>1809785</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1809785</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>429696</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>agenda-navios-aeronaves</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1459</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1459</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>1809765</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1809765</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>429696</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>agenda-navios-aeronaves</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1455</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1455</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>1809760</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1809760</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>429696</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>agenda-navios-aeronaves</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1454</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1454</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>1809754</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1809754</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>429696</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>agenda-navios-aeronaves</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1453</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1453</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>1796889</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1796889</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>E_433077</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>acesso-veiculos-in</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 0512</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 0513</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>1781423</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1781423</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>PS_431587</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-out</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1251</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0822</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>1781236</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1781236</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>PE_431571</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-in</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1223</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-19 0822</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>2081638</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1047</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>2163612</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0710</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>2190259</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0621</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1329954</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>2134524</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0616</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1331904</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>2160058</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0615</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1261550</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>2114903</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0557</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>2118299</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0556</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>2193252</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0535</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>2134235</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0457</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1368153</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>2199030</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0229</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -179,7 +179,7 @@
     <col min="2" max="2" width="11.015625" customWidth="true"/>
     <col min="3" max="3" width="15.0625" customWidth="true"/>
     <col min="4" max="4" width="30.33984375" customWidth="true"/>
-    <col min="5" max="5" width="15.6640625" customWidth="true"/>
+    <col min="5" max="5" width="7.8359375" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="16.40234375" customWidth="true"/>
     <col min="8" max="8" width="16.40234375" customWidth="true"/>
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 90 item(s) at 2026-10-27</t>
+          <t>Displaying 69 item(s) at 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -243,17 +243,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2374686</t>
+          <t>2441817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0916</t>
+          <t>26-Oct-27 1201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -290,17 +290,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1804822</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2441818</t>
+          <t>2447082</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2441823</t>
+          <t>2441812</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,17 +384,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2441812</t>
+          <t>2441818</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1775553</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2447082</t>
+          <t>2441809</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1804818</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>2374686</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1774224</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2441809</t>
+          <t>2412160</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2441823</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2441817</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2412160</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1329954</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2134524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1331904</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2160058</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0915</t>
+          <t>26-Oct-27 1200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -948,42 +948,42 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1886641</t>
+          <t>1878121</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TAJ3D95</t>
+          <t>1878121</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27661</t>
+          <t>38265249</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>credenciamento-veiculos</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0914</t>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -995,42 +995,42 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1883023</t>
+          <t>1876501</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1883023</t>
+          <t>1876501</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>PE_442192</t>
+          <t>GL_38237010</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0111</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0111</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1042,42 +1042,42 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1883021</t>
+          <t>1862940</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1883021</t>
+          <t>1862940</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>PS_442167</t>
+          <t>38149268</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0111</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0111</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1089,42 +1089,42 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1883019</t>
+          <t>1856916</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1883019</t>
+          <t>1856916</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>PS_442173</t>
+          <t>GL_38101654</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0111</t>
+          <t>26-Oct-23 1446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0111</t>
+          <t>26-Oct-23 1446</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1446</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1136,22 +1136,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1882919</t>
+          <t>1856846</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1882919</t>
+          <t>1856846</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>PS_442159</t>
+          <t>GL_38101121</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0053</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0054</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1183,22 +1183,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1882911</t>
+          <t>1856843</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1882911</t>
+          <t>1856843</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>A_678630</t>
+          <t>GL_38101116</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0052</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0052</t>
+          <t>26-Oct-23 1430</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1230,42 +1230,42 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1882724</t>
+          <t>1856839</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1882724</t>
+          <t>1856839</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>E_442140</t>
+          <t>GL_38101110</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-in</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0009</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 0009</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1277,22 +1277,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1880845</t>
+          <t>1856836</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1880845</t>
+          <t>1856836</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>A_678483</t>
+          <t>GL_38101105</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1924</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1924</t>
+          <t>26-Oct-23 1430</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1324,22 +1324,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1880755</t>
+          <t>1856833</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1880755</t>
+          <t>1856833</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>A_674109</t>
+          <t>GL_38101100</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1909</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1909</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1371,42 +1371,42 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1880754</t>
+          <t>1856830</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1880754</t>
+          <t>1856830</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>38282484</t>
+          <t>GL_38101094</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1908</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1909</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1418,42 +1418,42 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1880753</t>
+          <t>1856827</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1880753</t>
+          <t>1856827</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>E_441894</t>
+          <t>GL_38101086</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-in</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1908</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1908</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1465,42 +1465,42 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1880751</t>
+          <t>1856824</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1880751</t>
+          <t>1856824</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>E_441893</t>
+          <t>GL_38101082</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-in</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1908</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1908</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1512,22 +1512,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1880749</t>
+          <t>1856814</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1880749</t>
+          <t>1856814</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>A_677653</t>
+          <t>GL_38101016</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1908</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1908</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1559,42 +1559,42 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1880748</t>
+          <t>1856811</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1880748</t>
+          <t>1856811</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S_441884</t>
+          <t>GL_38101011</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-out</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1907</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1907</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1606,22 +1606,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1880746</t>
+          <t>1856804</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1880746</t>
+          <t>1856804</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>A_674103</t>
+          <t>GL_38100982</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-appt</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1906</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1906</t>
+          <t>26-Oct-23 1445</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1653,42 +1653,42 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1880745</t>
+          <t>1856800</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1880745</t>
+          <t>1856800</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S_441872</t>
+          <t>GL_38100973</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-out</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1906</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1906</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1445</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1700,42 +1700,42 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1880743</t>
+          <t>1856797</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1880743</t>
+          <t>1856797</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>E_441892</t>
+          <t>GL_38100967</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-in</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1906</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1906</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1430</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1747,22 +1747,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1879574</t>
+          <t>1856794</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1879574</t>
+          <t>1856794</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>38279011</t>
+          <t>GL_38100960</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1804</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1804</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1794,22 +1794,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1878121</t>
+          <t>1856791</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1878121</t>
+          <t>1856791</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>38265249</t>
+          <t>GL_38100955</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-23 1430</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1877962</t>
+          <t>1856788</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1877962</t>
+          <t>1856788</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PS_441667</t>
+          <t>GL_38100950</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1454</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1454</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1877090</t>
+          <t>1856785</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1877090</t>
+          <t>1856785</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>38242164</t>
+          <t>GL_38100945</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1228</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1231</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1876501</t>
+          <t>1856780</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1876501</t>
+          <t>1856780</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>GL_38237010</t>
+          <t>GL_38100932</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1982,42 +1982,42 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1873409</t>
+          <t>1856778</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1873409</t>
+          <t>1856778</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>38218948</t>
+          <t>GL_38100916</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 0052</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 0052</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2029,22 +2029,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1862940</t>
+          <t>1856774</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1862940</t>
+          <t>1856774</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>38149268</t>
+          <t>GL_38100900</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1856916</t>
+          <t>1856771</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1856916</t>
+          <t>1856771</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>GL_38101654</t>
+          <t>GL_38100893</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1446</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1446</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1446</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2123,22 +2123,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1856846</t>
+          <t>1852263</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1856846</t>
+          <t>1852263</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>GL_38101121</t>
+          <t>384677</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>transito-simplificado-conteiner</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2148,17 +2148,17 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1721</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1721</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1722</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2170,22 +2170,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1856843</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1856843</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>GL_38101116</t>
+          <t>37953116</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2217,22 +2217,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1856839</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1856839</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>GL_38101110</t>
+          <t>37953111</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2264,22 +2264,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1856836</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1856836</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>GL_38101105</t>
+          <t>37953053</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2289,17 +2289,17 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 0359</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2311,22 +2311,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1856833</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1856833</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>GL_38101100</t>
+          <t>37953007</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1856830</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1856830</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>GL_38101094</t>
+          <t>37950234</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 0224</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2405,22 +2405,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1856827</t>
+          <t>1844492</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1856827</t>
+          <t>1844492</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>GL_38101086</t>
+          <t>37947002</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-22 0004</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2452,22 +2452,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1856824</t>
+          <t>1840497</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1856824</t>
+          <t>1840497</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>GL_38101082</t>
+          <t>37888117</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2499,17 +2499,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1856814</t>
+          <t>1840492</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1856814</t>
+          <t>1840492</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GL_38101016</t>
+          <t>GL_37888107</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t/>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2546,22 +2546,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1856811</t>
+          <t>1840491</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1856811</t>
+          <t>1840491</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>GL_38101011</t>
+          <t>AL_37888107</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t/>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2593,22 +2593,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1856804</t>
+          <t>1840204</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1856804</t>
+          <t>1840204</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>GL_38100982</t>
+          <t>37886870</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1445</t>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1856800</t>
+          <t>1839730</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1856800</t>
+          <t>1839730</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>GL_38100973</t>
+          <t>GL_37882901</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2665,17 +2665,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-21 1216</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-21 1217</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1445</t>
+          <t>26-Oct-21 1245</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2687,17 +2687,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1856797</t>
+          <t>1839648</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1856797</t>
+          <t>1839648</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>GL_38100967</t>
+          <t>GL_37882492</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2734,22 +2734,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1856794</t>
+          <t>1839647</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1856794</t>
+          <t>1839647</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>GL_38100960</t>
+          <t>AL_37882492</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2781,22 +2781,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1856791</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1856791</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>GL_38100955</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2828,22 +2828,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1856788</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1856788</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>GL_38100950</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2875,22 +2875,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1856785</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1856785</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>GL_38100945</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2922,22 +2922,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1856780</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1856780</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>GL_38100932</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1856778</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1856778</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>GL_38100916</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2994,17 +2994,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3016,22 +3016,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1856774</t>
+          <t>1796889</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1856774</t>
+          <t>1796889</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>GL_38100900</t>
+          <t>E_433077</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>acesso-veiculos-in</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-16 0512</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-16 0513</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3063,22 +3063,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1856771</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1856771</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>GL_38100893</t>
+          <t>PS_431587</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-14 1251</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t/>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1030</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3110,22 +3110,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1852263</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1852263</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>384677</t>
+          <t>PE_431571</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>transito-simplificado-conteiner</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1721</t>
+          <t>26-Oct-14 1223</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1721</t>
+          <t/>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1722</t>
+          <t>26-Oct-27 1030</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3157,22 +3157,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1845864</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1845864</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>37953116</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3182,17 +3182,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0401</t>
+          <t>26-Oct-14 1047</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3204,22 +3204,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1845862</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1845862</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>37953111</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3229,17 +3229,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0401</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3251,22 +3251,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1845846</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1845846</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>37953053</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0359</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1845830</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1845830</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>37953007</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0357</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3345,22 +3345,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1845285</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1845285</t>
+          <t>1372502</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>37950234</t>
+          <t>2193252</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0224</t>
+          <t>26-Aug-25 0535</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3392,22 +3392,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1844492</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1844492</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>37947002</t>
+          <t>2134235</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0004</t>
+          <t>26-Aug-25 0457</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t/>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3439,22 +3439,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1840497</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1840497</t>
+          <t>1368153</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>37888117</t>
+          <t>2199030</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>inspecao-nao-invasiva</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3464,1007 +3464,20 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Aug-25 0229</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t/>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t/>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>1840492</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>1840492</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>GL_37888107</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>geracao-lotes</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1403</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1403</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>1840491</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>1840491</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>AL_37888107</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>armazenamento-lote</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1403</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1403</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>1840204</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>1840204</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>37886870</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>carregamento-lotes</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1329</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1329</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1329</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>1839730</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>1839730</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>GL_37882901</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>geracao-lotes</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1216</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1217</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1245</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>1839648</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>1839648</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>GL_37882492</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>geracao-lotes</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1208</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1208</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>1839647</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>1839647</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>AL_37882492</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>armazenamento-lote</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1208</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-21 1208</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>1809786</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>1809786</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>429696</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>agenda-navios-aeronaves</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1459</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1459</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>1809785</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>1809785</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>429696</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>agenda-navios-aeronaves</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1459</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1459</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>1809765</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>1809765</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>429696</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>agenda-navios-aeronaves</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1455</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1455</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>1809760</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>1809760</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>429696</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>agenda-navios-aeronaves</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1454</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1454</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>1809754</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>1809754</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>429696</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>agenda-navios-aeronaves</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1453</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-17 1453</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>1796889</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>1796889</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>E_433077</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>acesso-veiculos-in</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 0512</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-16 0513</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>1781423</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>1781423</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>PS_431587</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>pesagem-veiculo-carga-out</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-14 1251</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-26 0957</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>1781236</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>1781236</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>PE_431571</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>pesagem-veiculo-carga-in</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-14 1223</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-26 0956</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>1252055</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>2081638</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>26-Oct-14 1047</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>1319101</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>2163612</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0710</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>1370908</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>2190259</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0621</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>1214944</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>2118299</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0556</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>1372502</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>2193252</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0535</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>1278565</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>2134235</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0457</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>1368153</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>2199030</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>inspecao-nao-invasiva</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>26-Aug-25 0229</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -179,7 +179,7 @@
     <col min="2" max="2" width="11.015625" customWidth="true"/>
     <col min="3" max="3" width="15.0625" customWidth="true"/>
     <col min="4" max="4" width="30.33984375" customWidth="true"/>
-    <col min="5" max="5" width="7.8359375" customWidth="true"/>
+    <col min="5" max="5" width="15.6640625" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="16.40234375" customWidth="true"/>
     <col min="8" max="8" width="16.40234375" customWidth="true"/>
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 69 item(s) at 2026-10-27</t>
+          <t>Displaying 69 item(s) at 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -243,37 +243,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1899123</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1899123</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2441817</t>
+          <t>S_443817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-out</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1201</t>
+          <t>26-Oct-28 1357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-28 1357</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -290,37 +290,37 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1899122</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1804822</t>
+          <t>1899122</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2447082</t>
+          <t>PS_443817</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-28 1357</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -337,32 +337,32 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1899112</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>RHT1B43</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2441812</t>
+          <t>RHT1B43</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -384,32 +384,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1899108</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>RHT1B43</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2441818</t>
+          <t>RHT1B43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>credenciamento-veiculos</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>INCOMPLETO</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -431,12 +431,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1897572</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1775553</t>
+          <t>1897572</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1804818</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2374686</t>
+          <t>2441821</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1774224</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2412160</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2441823</t>
+          <t>2441817</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2441823</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1261550</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2114903</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2441821</t>
+          <t>2441818</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1329954</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2134524</t>
+          <t>2441812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1345</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,22 +854,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1898957</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1898957</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>S_443828</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>acesso-veiculos-out</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-28 1341</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-28 1342</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -901,22 +901,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1889211</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1331904</t>
+          <t>1889211</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2160058</t>
+          <t>38364427</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1200</t>
+          <t>26-Oct-27 1501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-27 1501</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-27 1515</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1878121</t>
+          <t>1889180</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1878121</t>
+          <t>1889180</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38265249</t>
+          <t>38364273</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-27 1457</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-27 1457</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-27 1500</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1876501</t>
+          <t>1889031</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1876501</t>
+          <t>1889031</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>GL_38237010</t>
+          <t>38362675</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-27 1438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-27 1439</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-27 1439</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1862940</t>
+          <t>1878121</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1862940</t>
+          <t>1878121</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>38149268</t>
+          <t>38265249</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,17 +1067,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1089,17 +1089,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1856916</t>
+          <t>1876501</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1856916</t>
+          <t>1876501</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>GL_38101654</t>
+          <t>GL_38237010</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1446</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1446</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1446</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1136,22 +1136,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1856846</t>
+          <t>1862940</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1856846</t>
+          <t>1862940</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>GL_38101121</t>
+          <t>38149268</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1856843</t>
+          <t>1856916</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1856843</t>
+          <t>1856916</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GL_38101116</t>
+          <t>GL_38101654</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-23 1446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1230,17 +1230,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1856839</t>
+          <t>1856846</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1856839</t>
+          <t>1856846</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>GL_38101110</t>
+          <t>GL_38101121</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1856836</t>
+          <t>1856843</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1856836</t>
+          <t>1856843</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>GL_38101105</t>
+          <t>GL_38101116</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1324,17 +1324,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1856833</t>
+          <t>1856839</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1856833</t>
+          <t>1856839</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>GL_38101100</t>
+          <t>GL_38101110</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1856830</t>
+          <t>1856836</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1856830</t>
+          <t>1856836</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>GL_38101094</t>
+          <t>GL_38101105</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1856827</t>
+          <t>1856833</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1856827</t>
+          <t>1856833</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>GL_38101086</t>
+          <t>GL_38101100</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1856824</t>
+          <t>1856830</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1856824</t>
+          <t>1856830</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>GL_38101082</t>
+          <t>GL_38101094</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1490,17 +1490,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1856814</t>
+          <t>1856827</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1856814</t>
+          <t>1856827</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>GL_38101016</t>
+          <t>GL_38101086</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1856811</t>
+          <t>1856824</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1856811</t>
+          <t>1856824</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>GL_38101011</t>
+          <t>GL_38101082</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1856804</t>
+          <t>1856814</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1856804</t>
+          <t>1856814</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>GL_38100982</t>
+          <t>GL_38101016</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1445</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1856800</t>
+          <t>1856811</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1856800</t>
+          <t>1856811</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>GL_38100973</t>
+          <t>GL_38101011</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1445</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1856797</t>
+          <t>1856804</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1856797</t>
+          <t>1856804</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>GL_38100967</t>
+          <t>GL_38100982</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1856794</t>
+          <t>1856800</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1856794</t>
+          <t>1856800</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>GL_38100960</t>
+          <t>GL_38100973</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1856791</t>
+          <t>1856797</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1856791</t>
+          <t>1856797</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>GL_38100955</t>
+          <t>GL_38100967</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1430</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1856788</t>
+          <t>1856794</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1856788</t>
+          <t>1856794</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>GL_38100950</t>
+          <t>GL_38100960</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1856785</t>
+          <t>1856791</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1856785</t>
+          <t>1856791</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>GL_38100945</t>
+          <t>GL_38100955</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1856780</t>
+          <t>1856788</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1856780</t>
+          <t>1856788</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>GL_38100932</t>
+          <t>GL_38100950</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1856778</t>
+          <t>1856785</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1856778</t>
+          <t>1856785</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>GL_38100916</t>
+          <t>GL_38100945</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1218</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1856774</t>
+          <t>1856780</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1856774</t>
+          <t>1856780</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>GL_38100900</t>
+          <t>GL_38100932</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1856771</t>
+          <t>1856778</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1856771</t>
+          <t>1856778</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>GL_38100893</t>
+          <t>GL_38100916</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2123,22 +2123,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1852263</t>
+          <t>1856774</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1852263</t>
+          <t>1856774</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>384677</t>
+          <t>GL_38100900</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>transito-simplificado-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2148,17 +2148,17 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1721</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1721</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1722</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2170,22 +2170,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1845864</t>
+          <t>1856771</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1845864</t>
+          <t>1856771</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>37953116</t>
+          <t>GL_38100893</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0401</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2217,22 +2217,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1845862</t>
+          <t>1852263</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1845862</t>
+          <t>1852263</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>37953111</t>
+          <t>384677</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>transito-simplificado-conteiner</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0401</t>
+          <t>26-Oct-22 1721</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-22 1721</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-22 1722</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1845846</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1845846</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>37953053</t>
+          <t>37953116</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0359</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1845830</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1845830</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>37953007</t>
+          <t>37953111</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0357</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1845285</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1845285</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>37950234</t>
+          <t>37953053</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0224</t>
+          <t>26-Oct-22 0359</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2405,17 +2405,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1844492</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1844492</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>37947002</t>
+          <t>37953007</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0004</t>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2452,22 +2452,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1840497</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1840497</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>37888117</t>
+          <t>37950234</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-22 0224</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2499,22 +2499,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1840492</t>
+          <t>1844492</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1840492</t>
+          <t>1844492</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GL_37888107</t>
+          <t>37947002</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-22 0004</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2546,22 +2546,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1840491</t>
+          <t>1840497</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1840491</t>
+          <t>1840497</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>AL_37888107</t>
+          <t>37888117</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2593,22 +2593,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1840204</t>
+          <t>1840492</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1840204</t>
+          <t>1840492</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>37886870</t>
+          <t>GL_37888107</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1329</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1329</t>
+          <t/>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1329</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2640,22 +2640,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1839730</t>
+          <t>1840491</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1839730</t>
+          <t>1840491</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>GL_37882901</t>
+          <t>AL_37888107</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2665,17 +2665,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1216</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1217</t>
+          <t/>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1245</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2687,22 +2687,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1839648</t>
+          <t>1840204</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1839648</t>
+          <t>1840204</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>GL_37882492</t>
+          <t>37886870</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1208</t>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1208</t>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2734,22 +2734,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1839647</t>
+          <t>1839730</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1839647</t>
+          <t>1839730</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>AL_37882492</t>
+          <t>GL_37882901</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1208</t>
+          <t>26-Oct-21 1216</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-21 1217</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1208</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2781,22 +2781,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1839648</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1839648</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>GL_37882492</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2828,22 +2828,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1839647</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1839647</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>AL_37882492</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3016,22 +3016,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1796889</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1796889</t>
+          <t>1809760</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>E_433077</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-in</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 0512</t>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 0513</t>
+          <t>26-Oct-17 1454</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3063,22 +3063,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1809754</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>PS_431587</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1251</t>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1030</t>
+          <t>26-Oct-17 1453</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3110,22 +3110,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1796889</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1796889</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>PE_431571</t>
+          <t>E_433077</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>acesso-veiculos-in</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1223</t>
+          <t>26-Oct-16 0512</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1030</t>
+          <t>26-Oct-16 0513</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3157,22 +3157,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1781423</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>PS_431587</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1047</t>
+          <t>26-Oct-14 1251</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-28 1003</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3204,22 +3204,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1781236</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>PE_431571</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-14 1223</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-28 1003</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1252055</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>2081638</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Oct-14 1047</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1319101</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>2163612</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Aug-25 0710</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3345,17 +3345,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1370908</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>2190259</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Aug-25 0621</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3392,17 +3392,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1214944</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>2118299</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Aug-25 0556</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3439,45 +3439,139 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>2193252</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0535</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>2134235</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0457</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
           <t>1368153</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>1368153</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>2199030</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>inspecao-nao-invasiva</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>26-Aug-25 0229</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -178,8 +178,8 @@
     <col min="1" max="1" width="32.7265625" customWidth="true"/>
     <col min="2" max="2" width="11.015625" customWidth="true"/>
     <col min="3" max="3" width="15.0625" customWidth="true"/>
-    <col min="4" max="4" width="30.33984375" customWidth="true"/>
-    <col min="5" max="5" width="15.6640625" customWidth="true"/>
+    <col min="4" max="4" width="32.30078125" customWidth="true"/>
+    <col min="5" max="5" width="11.01953125" customWidth="true"/>
     <col min="6" max="6" width="18.109375" customWidth="true"/>
     <col min="7" max="7" width="16.40234375" customWidth="true"/>
     <col min="8" max="8" width="16.40234375" customWidth="true"/>
@@ -189,7 +189,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Displaying 69 item(s) at 2026-10-28</t>
+          <t>Displaying 78 item(s) at 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -243,42 +243,42 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1899123</t>
+          <t>1906609</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1899123</t>
+          <t>1906609</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>S_443817</t>
+          <t>A_683198</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-out</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1357</t>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1357</t>
+          <t/>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -290,42 +290,42 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1899122</t>
+          <t>1906608</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1899122</t>
+          <t>1906608</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PS_443817</t>
+          <t>A_685083</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ENVIADO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1357</t>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1357</t>
+          <t/>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -337,37 +337,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1899112</t>
+          <t>1906607</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RHT1B43</t>
+          <t>1906607</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>RHT1B43</t>
+          <t>38472510</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>credenciamento-veiculos</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1355</t>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -384,32 +384,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1899108</t>
+          <t>1906606</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>RHT1B43</t>
+          <t>1906606</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RHT1B43</t>
+          <t>A_685579</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>credenciamento-veiculos</t>
+          <t>acesso-veiculos-appt</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>INCOMPLETO</t>
+          <t>ERRO</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1354</t>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -419,7 +419,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-29 0912</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -431,17 +431,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1897572</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1897572</t>
+          <t>1775562</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2441809</t>
+          <t>2441821</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1346</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -478,17 +478,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1775562</t>
+          <t>1775556</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2441821</t>
+          <t>2441817</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -525,17 +525,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1590463</t>
+          <t>1775558</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2238641</t>
+          <t>2441823</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1775556</t>
+          <t>1775552</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2441817</t>
+          <t>2441812</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -619,17 +619,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1897572</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1571590</t>
+          <t>1897572</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2294542</t>
+          <t>2441809</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1775558</t>
+          <t>1510932</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2441823</t>
+          <t>2255730</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>1510932</t>
+          <t>1590463</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2255730</t>
+          <t>2238641</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>1775557</t>
+          <t>1571590</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2441818</t>
+          <t>2294542</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -807,17 +807,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1775552</t>
+          <t>1775557</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2441812</t>
+          <t>2441818</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1345</t>
+          <t>26-Oct-29 0900</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -854,42 +854,42 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1898957</t>
+          <t>1904111</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1898957</t>
+          <t>1904111</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>S_443828</t>
+          <t>PS_444319</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-out</t>
+          <t>pesagem-veiculo-carga-out</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1341</t>
+          <t>26-Oct-29 0111</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-29 0111</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1342</t>
+          <t/>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -901,42 +901,42 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1889211</t>
+          <t>1904109</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>1889211</t>
+          <t>1904109</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>38364427</t>
+          <t>PE_444348</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>pesagem-veiculo-carga-in</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1501</t>
+          <t>26-Oct-29 0111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1501</t>
+          <t>26-Oct-29 0111</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1515</t>
+          <t/>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -948,17 +948,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1889180</t>
+          <t>1902594</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>1889180</t>
+          <t>1902594</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38364273</t>
+          <t>38446136</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1457</t>
+          <t>26-Oct-28 2125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1457</t>
+          <t>26-Oct-28 2125</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1500</t>
+          <t>26-Oct-28 2126</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1889031</t>
+          <t>1902503</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1889031</t>
+          <t>1902503</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>38362675</t>
+          <t>38445649</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1438</t>
+          <t>26-Oct-28 2115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1439</t>
+          <t>26-Oct-28 2115</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1439</t>
+          <t>26-Oct-28 2130</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1878121</t>
+          <t>1902475</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1878121</t>
+          <t>1902475</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>38265249</t>
+          <t>38445481</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1067,17 +1067,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-28 2112</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-28 2112</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1522</t>
+          <t>26-Oct-28 2115</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1089,22 +1089,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1876501</t>
+          <t>1902409</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>1876501</t>
+          <t>1902409</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>GL_38237010</t>
+          <t>38445146</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-28 2106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-28 2106</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-26 1047</t>
+          <t>26-Oct-28 2115</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1862940</t>
+          <t>1902396</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>1862940</t>
+          <t>1902396</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>38149268</t>
+          <t>38445042</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-28 2104</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-28 2104</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-24 1127</t>
+          <t>26-Oct-28 2104</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1183,22 +1183,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1856916</t>
+          <t>1902357</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1856916</t>
+          <t>1902357</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GL_38101654</t>
+          <t>38444806</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1446</t>
+          <t>26-Oct-28 2100</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2100</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2100</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1230,22 +1230,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1856846</t>
+          <t>1902301</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1856846</t>
+          <t>1902301</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>GL_38101121</t>
+          <t>38444413</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-28 2053</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2053</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2054</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1277,22 +1277,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1856843</t>
+          <t>1902296</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1856843</t>
+          <t>1902296</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>GL_38101116</t>
+          <t>38444380</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>embarque-desembarque-navios</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-28 2053</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2053</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2053</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1324,22 +1324,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1856839</t>
+          <t>1902290</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>1856839</t>
+          <t>1902290</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>GL_38101110</t>
+          <t>38444323</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1349,17 +1349,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-28 2051</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2051</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2052</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1371,22 +1371,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1856836</t>
+          <t>1902263</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1856836</t>
+          <t>1902263</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>GL_38101105</t>
+          <t>38444105</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-28 2048</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2048</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 2049</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1856833</t>
+          <t>1899249</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1856833</t>
+          <t>1899249</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>GL_38101100</t>
+          <t>38419604</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-28 1412</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 1412</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-28 1413</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1465,22 +1465,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1856830</t>
+          <t>1889211</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1856830</t>
+          <t>1889211</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>GL_38101094</t>
+          <t>38364427</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1490,17 +1490,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1428</t>
+          <t>26-Oct-27 1501</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-27 1501</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-27 1515</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1512,22 +1512,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1856827</t>
+          <t>1889180</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1856827</t>
+          <t>1889180</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>GL_38101086</t>
+          <t>38364273</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-27 1457</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-27 1457</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-27 1500</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1559,22 +1559,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1856824</t>
+          <t>1889031</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1856824</t>
+          <t>1889031</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>GL_38101082</t>
+          <t>38362675</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1427</t>
+          <t>26-Oct-27 1438</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-27 1439</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-27 1439</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1606,22 +1606,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1856814</t>
+          <t>1878121</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1856814</t>
+          <t>1878121</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>GL_38101016</t>
+          <t>38265249</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-26 1522</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1856811</t>
+          <t>1876501</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1856811</t>
+          <t>1876501</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>GL_38101011</t>
+          <t>GL_38237010</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1426</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-26 1047</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1856804</t>
+          <t>1862940</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1856804</t>
+          <t>1862940</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>GL_38100982</t>
+          <t>38149268</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1604</t>
+          <t>26-Oct-24 1127</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1747,17 +1747,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1856800</t>
+          <t>1856916</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>1856800</t>
+          <t>1856916</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>GL_38100973</t>
+          <t>GL_38101654</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1446</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1856797</t>
+          <t>1856846</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1856797</t>
+          <t>1856846</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>GL_38100967</t>
+          <t>GL_38101121</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1856794</t>
+          <t>1856843</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1856794</t>
+          <t>1856843</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>GL_38100960</t>
+          <t>GL_38101116</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1856791</t>
+          <t>1856839</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1856791</t>
+          <t>1856839</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>GL_38100955</t>
+          <t>GL_38101110</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>1856788</t>
+          <t>1856836</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1856788</t>
+          <t>1856836</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>GL_38100950</t>
+          <t>GL_38101105</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1856785</t>
+          <t>1856833</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1856785</t>
+          <t>1856833</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>GL_38100945</t>
+          <t>GL_38101100</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1218</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2029,17 +2029,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>1856780</t>
+          <t>1856830</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1856780</t>
+          <t>1856830</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>GL_38100932</t>
+          <t>GL_38101094</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1428</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>1856778</t>
+          <t>1856827</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1856778</t>
+          <t>1856827</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>GL_38100916</t>
+          <t>GL_38101086</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2123,17 +2123,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>1856774</t>
+          <t>1856824</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1856774</t>
+          <t>1856824</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>GL_38100900</t>
+          <t>GL_38101082</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1427</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1856771</t>
+          <t>1856814</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1856771</t>
+          <t>1856814</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>GL_38100893</t>
+          <t>GL_38101016</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-23 1425</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2217,22 +2217,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>1852263</t>
+          <t>1856811</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1852263</t>
+          <t>1856811</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>384677</t>
+          <t>GL_38101011</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>transito-simplificado-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1721</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1721</t>
+          <t>26-Oct-23 1426</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1722</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2264,22 +2264,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>1845864</t>
+          <t>1856804</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1845864</t>
+          <t>1856804</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>37953116</t>
+          <t>GL_38100982</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2289,17 +2289,17 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0401</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2311,22 +2311,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1845862</t>
+          <t>1856800</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1845862</t>
+          <t>1856800</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>37953111</t>
+          <t>GL_38100973</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0401</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1845846</t>
+          <t>1856797</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1845846</t>
+          <t>1856797</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>37953053</t>
+          <t>GL_38100967</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0359</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2405,22 +2405,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1845830</t>
+          <t>1856794</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1845830</t>
+          <t>1856794</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>37953007</t>
+          <t>GL_38100960</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0357</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2452,22 +2452,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1845285</t>
+          <t>1856791</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>1845285</t>
+          <t>1856791</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>37950234</t>
+          <t>GL_38100955</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0224</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2499,22 +2499,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1844492</t>
+          <t>1856788</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>1844492</t>
+          <t>1856788</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>37947002</t>
+          <t>GL_38100950</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>posicao-conteiner</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 0004</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-22 1809</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2546,22 +2546,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1840497</t>
+          <t>1856785</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1840497</t>
+          <t>1856785</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>37888117</t>
+          <t>GL_38100945</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-27 1218</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1840492</t>
+          <t>1856780</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1840492</t>
+          <t>1856780</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>GL_37888107</t>
+          <t>GL_38100932</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2640,22 +2640,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1840491</t>
+          <t>1856778</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1840491</t>
+          <t>1856778</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>AL_37888107</t>
+          <t>GL_38100916</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2665,17 +2665,17 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1403</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2687,22 +2687,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1840204</t>
+          <t>1856774</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1840204</t>
+          <t>1856774</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>37886870</t>
+          <t>GL_38100900</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>carregamento-lotes</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1329</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1329</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1329</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2734,17 +2734,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1839730</t>
+          <t>1856771</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1839730</t>
+          <t>1856771</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>GL_37882901</t>
+          <t>GL_38100893</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1216</t>
+          <t>26-Oct-23 1425</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1217</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-27 1604</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2781,22 +2781,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1839648</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1839648</t>
+          <t>1845864</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>GL_37882492</t>
+          <t>37953116</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>geracao-lotes</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1208</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-27 1603</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2828,22 +2828,22 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1839647</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1839647</t>
+          <t>1845862</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>AL_37882492</t>
+          <t>37953111</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>armazenamento-lote</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1208</t>
+          <t>26-Oct-22 0401</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-21 1208</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2875,22 +2875,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1809786</t>
+          <t>1845846</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37953053</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 0359</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2922,22 +2922,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1809785</t>
+          <t>1845830</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37953007</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 0357</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1459</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1809765</t>
+          <t>1845285</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37950234</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2994,17 +2994,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-22 0224</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1455</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3016,22 +3016,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1844492</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1809760</t>
+          <t>1844492</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37947002</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>posicao-conteiner</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t>26-Oct-22 0004</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1454</t>
+          <t>26-Oct-22 1809</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3063,22 +3063,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1840497</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1809754</t>
+          <t>1840497</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>429696</t>
+          <t>37888117</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>agenda-navios-aeronaves</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-17 1453</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3110,22 +3110,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>1796889</t>
+          <t>1840492</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1796889</t>
+          <t>1840492</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>E_433077</t>
+          <t>GL_37888107</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>acesso-veiculos-in</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 0512</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-16 0513</t>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3157,22 +3157,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1840491</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1781423</t>
+          <t>1840491</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>PS_431587</t>
+          <t>AL_37888107</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-out</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1251</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1003</t>
+          <t>26-Oct-21 1403</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3204,22 +3204,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1840204</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>1781236</t>
+          <t>1840204</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>PE_431571</t>
+          <t>37886870</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>pesagem-veiculo-carga-in</t>
+          <t>carregamento-lotes</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3229,17 +3229,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1223</t>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-21 1329</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-28 1003</t>
+          <t>26-Oct-28 1510</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3251,22 +3251,22 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1839730</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>1252055</t>
+          <t>1839730</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2081638</t>
+          <t>GL_37882901</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>26-Oct-14 1047</t>
+          <t>26-Oct-21 1216</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-21 1217</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1839648</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>1319101</t>
+          <t>1839648</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>2163612</t>
+          <t>GL_37882492</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>geracao-lotes</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0710</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-27 1603</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3345,22 +3345,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1839647</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>1370908</t>
+          <t>1839647</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>2190259</t>
+          <t>AL_37882492</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>armazenamento-lote</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0621</t>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-21 1208</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3392,22 +3392,22 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>1214944</t>
+          <t>1809786</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2118299</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0556</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3439,22 +3439,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>1372502</t>
+          <t>1809785</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2193252</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0535</t>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1459</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3486,22 +3486,22 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>1278565</t>
+          <t>1809765</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2134235</t>
+          <t>429696</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>inspecao-nao-invasiva</t>
+          <t>agenda-navios-aeronaves</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>26-Aug-25 0457</t>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>26-Oct-17 1455</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3533,45 +3533,562 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>1809760</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1809760</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>429696</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>agenda-navios-aeronaves</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1454</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1454</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>1809754</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>1809754</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>429696</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>agenda-navios-aeronaves</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1453</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-17 1453</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>1796889</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1796889</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>E_433077</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>acesso-veiculos-in</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 0512</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-16 0513</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>1781423</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1781423</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>PS_431587</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-out</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1251</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-28 1003</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>1781236</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1781236</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>PE_431571</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>pesagem-veiculo-carga-in</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1223</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-28 1003</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1252055</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>2081638</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>26-Oct-14 1047</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1319101</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>2163612</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0710</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1370908</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2190259</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0621</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1214944</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>2118299</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0556</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1372502</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>2193252</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0535</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1278565</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>2134235</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>inspecao-nao-invasiva</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>26-Aug-25 0457</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
           <t>1368153</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>1368153</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>2199030</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>inspecao-nao-invasiva</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>26-Aug-25 0229</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t/>
         </is>
